--- a/Resultados de la votación 2022.xlsx
+++ b/Resultados de la votación 2022.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="7" rupBuild="9303"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f5fa8a9efe53b17c/Documentos/TP FINAL DATOS/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_4465632CD9D7551C0AAEA588935375AF74BB0096" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720"/>
+    <workbookView minimized="1" xWindow="2868" yWindow="2184" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EscrutinioFinal" sheetId="1" r:id="rId1"/>
@@ -13,7 +19,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">EscrutinioFinal!$A$1:$Z$190</definedName>
     <definedName name="Z_6EC1DD54_015D_42A8_B0D3_45AB00E90794_.wvu.FilterData" localSheetId="0" hidden="1">EscrutinioFinal!$A$1:$Y$192</definedName>
   </definedNames>
-  <calcPr calcId="145621"/>
+  <calcPr calcId="191029"/>
   <customWorkbookViews>
     <customWorkbookView name="Filtro 1" guid="{6EC1DD54-015D-42A8-B0D3-45AB00E90794}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
   </customWorkbookViews>
@@ -21,9 +27,12 @@
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
         <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
     <ext uri="GoogleSheetsCustomDataVersion1">
@@ -1080,10 +1089,10 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="165" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@"/>
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@"/>
   </numFmts>
   <fonts count="10" x14ac:knownFonts="1">
     <font>
@@ -1325,7 +1334,7 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="75">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1349,13 +1358,13 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1370,7 +1379,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1397,7 +1406,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1454,7 +1463,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1475,13 +1484,13 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1493,10 +1502,10 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1520,16 +1529,16 @@
     <xf numFmtId="3" fontId="6" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1768,25 +1777,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Y999"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.7109375" customWidth="1"/>
-    <col min="2" max="2" width="10.42578125" customWidth="1"/>
-    <col min="3" max="3" width="12.85546875" customWidth="1"/>
-    <col min="4" max="4" width="10.85546875" customWidth="1"/>
-    <col min="5" max="5" width="13.28515625" customWidth="1"/>
-    <col min="6" max="6" width="35.7109375" customWidth="1"/>
-    <col min="7" max="7" width="49.28515625" customWidth="1"/>
-    <col min="8" max="8" width="13.140625" customWidth="1"/>
-    <col min="9" max="9" width="43.7109375" style="11" customWidth="1"/>
-    <col min="10" max="10" width="19.28515625" customWidth="1"/>
-    <col min="11" max="11" width="12.7109375" customWidth="1"/>
-    <col min="12" max="25" width="11.5703125" customWidth="1"/>
+    <col min="1" max="1" width="9.6640625" customWidth="1"/>
+    <col min="2" max="2" width="10.44140625" customWidth="1"/>
+    <col min="3" max="3" width="12.88671875" customWidth="1"/>
+    <col min="4" max="4" width="10.88671875" customWidth="1"/>
+    <col min="5" max="5" width="13.33203125" customWidth="1"/>
+    <col min="6" max="6" width="35.6640625" customWidth="1"/>
+    <col min="7" max="7" width="49.33203125" customWidth="1"/>
+    <col min="8" max="8" width="13.109375" customWidth="1"/>
+    <col min="9" max="9" width="43.6640625" style="11" customWidth="1"/>
+    <col min="10" max="10" width="19.33203125" customWidth="1"/>
+    <col min="11" max="11" width="12.6640625" customWidth="1"/>
+    <col min="12" max="25" width="11.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" ht="75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:25" ht="72" x14ac:dyDescent="0.3">
       <c r="A1" s="52" t="s">
         <v>344</v>
       </c>
@@ -1835,7 +1844,7 @@
       <c r="X1" s="2"/>
       <c r="Y1" s="2"/>
     </row>
-    <row r="2" spans="1:25" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:25" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A2" s="15">
         <v>9</v>
       </c>
@@ -1880,7 +1889,7 @@
       <c r="X2" s="2"/>
       <c r="Y2" s="2"/>
     </row>
-    <row r="3" spans="1:25" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:25" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A3" s="15">
         <v>25</v>
       </c>
@@ -1925,7 +1934,7 @@
       <c r="X3" s="2"/>
       <c r="Y3" s="2"/>
     </row>
-    <row r="4" spans="1:25" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:25" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A4" s="15">
         <v>2</v>
       </c>
@@ -1970,7 +1979,7 @@
       <c r="X4" s="2"/>
       <c r="Y4" s="2"/>
     </row>
-    <row r="5" spans="1:25" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:25" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="15">
         <v>7</v>
       </c>
@@ -2015,7 +2024,7 @@
       <c r="X5" s="2"/>
       <c r="Y5" s="2"/>
     </row>
-    <row r="6" spans="1:25" ht="30" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:25" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A6" s="15">
         <v>11</v>
       </c>
@@ -2060,7 +2069,7 @@
       <c r="X6" s="2"/>
       <c r="Y6" s="2"/>
     </row>
-    <row r="7" spans="1:25" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:25" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A7" s="18">
         <v>28</v>
       </c>
@@ -2105,7 +2114,7 @@
       <c r="X7" s="2"/>
       <c r="Y7" s="2"/>
     </row>
-    <row r="8" spans="1:25" ht="78.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:25" ht="78" x14ac:dyDescent="0.3">
       <c r="A8" s="19">
         <v>21</v>
       </c>
@@ -2150,7 +2159,7 @@
       <c r="X8" s="2"/>
       <c r="Y8" s="2"/>
     </row>
-    <row r="9" spans="1:25" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:25" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A9" s="19">
         <v>8</v>
       </c>
@@ -2195,7 +2204,7 @@
       <c r="X9" s="2"/>
       <c r="Y9" s="2"/>
     </row>
-    <row r="10" spans="1:25" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:25" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A10" s="18">
         <v>6</v>
       </c>
@@ -2238,7 +2247,7 @@
       <c r="X10" s="2"/>
       <c r="Y10" s="2"/>
     </row>
-    <row r="11" spans="1:25" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:25" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A11" s="19">
         <v>4</v>
       </c>
@@ -2283,7 +2292,7 @@
       <c r="X11" s="2"/>
       <c r="Y11" s="2"/>
     </row>
-    <row r="12" spans="1:25" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:25" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A12" s="19">
         <v>16</v>
       </c>
@@ -2327,7 +2336,7 @@
       <c r="X12" s="2"/>
       <c r="Y12" s="2"/>
     </row>
-    <row r="13" spans="1:25" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:25" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="19">
         <v>5</v>
       </c>
@@ -2371,7 +2380,7 @@
       <c r="X13" s="2"/>
       <c r="Y13" s="2"/>
     </row>
-    <row r="14" spans="1:25" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:25" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A14" s="19">
         <v>18</v>
       </c>
@@ -2416,7 +2425,7 @@
       <c r="X14" s="2"/>
       <c r="Y14" s="2"/>
     </row>
-    <row r="15" spans="1:25" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:25" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A15" s="19">
         <v>13</v>
       </c>
@@ -2461,7 +2470,7 @@
       <c r="X15" s="2"/>
       <c r="Y15" s="2"/>
     </row>
-    <row r="16" spans="1:25" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:25" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A16" s="19">
         <v>26</v>
       </c>
@@ -2506,7 +2515,7 @@
       <c r="X16" s="2"/>
       <c r="Y16" s="2"/>
     </row>
-    <row r="17" spans="1:25" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:25" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A17" s="19">
         <v>15</v>
       </c>
@@ -2550,7 +2559,7 @@
       <c r="X17" s="2"/>
       <c r="Y17" s="2"/>
     </row>
-    <row r="18" spans="1:25" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:25" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A18" s="19">
         <v>20</v>
       </c>
@@ -2595,7 +2604,7 @@
       <c r="X18" s="2"/>
       <c r="Y18" s="2"/>
     </row>
-    <row r="19" spans="1:25" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:25" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A19" s="19">
         <v>27</v>
       </c>
@@ -2640,7 +2649,7 @@
       <c r="X19" s="2"/>
       <c r="Y19" s="2"/>
     </row>
-    <row r="20" spans="1:25" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:25" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="19">
         <v>1</v>
       </c>
@@ -2684,7 +2693,7 @@
       <c r="X20" s="2"/>
       <c r="Y20" s="2"/>
     </row>
-    <row r="21" spans="1:25" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:25" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="19">
         <v>19</v>
       </c>
@@ -2728,7 +2737,7 @@
       <c r="X21" s="2"/>
       <c r="Y21" s="2"/>
     </row>
-    <row r="22" spans="1:25" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:25" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="19">
         <v>12</v>
       </c>
@@ -2773,7 +2782,7 @@
       <c r="X22" s="2"/>
       <c r="Y22" s="2"/>
     </row>
-    <row r="23" spans="1:25" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:25" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="19">
         <v>3</v>
       </c>
@@ -2818,7 +2827,7 @@
       <c r="X23" s="2"/>
       <c r="Y23" s="2"/>
     </row>
-    <row r="24" spans="1:25" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:25" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="19">
         <v>23</v>
       </c>
@@ -2863,7 +2872,7 @@
       <c r="X24" s="2"/>
       <c r="Y24" s="2"/>
     </row>
-    <row r="25" spans="1:25" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:25" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="19">
         <v>14</v>
       </c>
@@ -2908,7 +2917,7 @@
       <c r="X25" s="2"/>
       <c r="Y25" s="2"/>
     </row>
-    <row r="26" spans="1:25" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:25" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="19">
         <v>17</v>
       </c>
@@ -2953,7 +2962,7 @@
       <c r="X26" s="2"/>
       <c r="Y26" s="2"/>
     </row>
-    <row r="27" spans="1:25" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:25" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="19">
         <v>24</v>
       </c>
@@ -2998,7 +3007,7 @@
       <c r="X27" s="2"/>
       <c r="Y27" s="2"/>
     </row>
-    <row r="28" spans="1:25" ht="39" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:25" ht="39" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="18">
         <v>10</v>
       </c>
@@ -3048,7 +3057,7 @@
       <c r="X28" s="2"/>
       <c r="Y28" s="2"/>
     </row>
-    <row r="29" spans="1:25" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:25" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29" s="37">
         <v>22</v>
       </c>
@@ -3093,7 +3102,7 @@
       <c r="X29" s="2"/>
       <c r="Y29" s="2"/>
     </row>
-    <row r="30" spans="1:25" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:25" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="27">
         <v>18</v>
       </c>
@@ -3138,7 +3147,7 @@
       <c r="X30" s="2"/>
       <c r="Y30" s="2"/>
     </row>
-    <row r="31" spans="1:25" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:25" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="18">
         <v>7</v>
       </c>
@@ -3183,7 +3192,7 @@
       <c r="X31" s="2"/>
       <c r="Y31" s="2"/>
     </row>
-    <row r="32" spans="1:25" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:25" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="18">
         <v>5</v>
       </c>
@@ -3228,7 +3237,7 @@
       <c r="X32" s="2"/>
       <c r="Y32" s="2"/>
     </row>
-    <row r="33" spans="1:25" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:25" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="18">
         <v>21</v>
       </c>
@@ -3273,7 +3282,7 @@
       <c r="X33" s="2"/>
       <c r="Y33" s="2"/>
     </row>
-    <row r="34" spans="1:25" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:25" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="18">
         <v>13</v>
       </c>
@@ -3318,7 +3327,7 @@
       <c r="X34" s="2"/>
       <c r="Y34" s="2"/>
     </row>
-    <row r="35" spans="1:25" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:25" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="18">
         <v>10</v>
       </c>
@@ -3363,7 +3372,7 @@
       <c r="X35" s="2"/>
       <c r="Y35" s="2"/>
     </row>
-    <row r="36" spans="1:25" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:25" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="19">
         <v>16</v>
       </c>
@@ -3408,7 +3417,7 @@
       <c r="X36" s="2"/>
       <c r="Y36" s="2"/>
     </row>
-    <row r="37" spans="1:25" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:25" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="19">
         <v>29</v>
       </c>
@@ -3453,7 +3462,7 @@
       <c r="X37" s="2"/>
       <c r="Y37" s="2"/>
     </row>
-    <row r="38" spans="1:25" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:25" ht="47.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="19">
         <v>22</v>
       </c>
@@ -3498,7 +3507,7 @@
       <c r="X38" s="2"/>
       <c r="Y38" s="2"/>
     </row>
-    <row r="39" spans="1:25" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:25" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="19">
         <v>1</v>
       </c>
@@ -3543,7 +3552,7 @@
       <c r="X39" s="2"/>
       <c r="Y39" s="2"/>
     </row>
-    <row r="40" spans="1:25" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:25" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="19">
         <v>25</v>
       </c>
@@ -3588,7 +3597,7 @@
       <c r="X40" s="2"/>
       <c r="Y40" s="2"/>
     </row>
-    <row r="41" spans="1:25" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:25" ht="38.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="19">
         <v>8</v>
       </c>
@@ -3633,7 +3642,7 @@
       <c r="X41" s="2"/>
       <c r="Y41" s="2"/>
     </row>
-    <row r="42" spans="1:25" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:25" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="19">
         <v>9</v>
       </c>
@@ -3678,7 +3687,7 @@
       <c r="X42" s="2"/>
       <c r="Y42" s="2"/>
     </row>
-    <row r="43" spans="1:25" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:25" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="19">
         <v>4</v>
       </c>
@@ -3723,7 +3732,7 @@
       <c r="X43" s="2"/>
       <c r="Y43" s="2"/>
     </row>
-    <row r="44" spans="1:25" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:25" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="19">
         <v>3</v>
       </c>
@@ -3768,7 +3777,7 @@
       <c r="X44" s="2"/>
       <c r="Y44" s="2"/>
     </row>
-    <row r="45" spans="1:25" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:25" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="19">
         <v>20</v>
       </c>
@@ -3813,7 +3822,7 @@
       <c r="X45" s="2"/>
       <c r="Y45" s="2"/>
     </row>
-    <row r="46" spans="1:25" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:25" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="19">
         <v>14</v>
       </c>
@@ -3858,7 +3867,7 @@
       <c r="X46" s="2"/>
       <c r="Y46" s="2"/>
     </row>
-    <row r="47" spans="1:25" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:25" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="19">
         <v>17</v>
       </c>
@@ -3903,7 +3912,7 @@
       <c r="X47" s="2"/>
       <c r="Y47" s="2"/>
     </row>
-    <row r="48" spans="1:25" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:25" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="19">
         <v>2</v>
       </c>
@@ -3948,7 +3957,7 @@
       <c r="X48" s="2"/>
       <c r="Y48" s="2"/>
     </row>
-    <row r="49" spans="1:25" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:25" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="19">
         <v>28</v>
       </c>
@@ -3993,7 +4002,7 @@
       <c r="X49" s="2"/>
       <c r="Y49" s="2"/>
     </row>
-    <row r="50" spans="1:25" ht="69.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:25" ht="69.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="18">
         <v>19</v>
       </c>
@@ -4037,7 +4046,7 @@
       <c r="X50" s="2"/>
       <c r="Y50" s="2"/>
     </row>
-    <row r="51" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="19">
         <v>15</v>
       </c>
@@ -4082,7 +4091,7 @@
       <c r="X51" s="2"/>
       <c r="Y51" s="2"/>
     </row>
-    <row r="52" spans="1:25" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:25" ht="38.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="19">
         <v>11</v>
       </c>
@@ -4127,7 +4136,7 @@
       <c r="X52" s="2"/>
       <c r="Y52" s="2"/>
     </row>
-    <row r="53" spans="1:25" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:25" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="19">
         <v>24</v>
       </c>
@@ -4172,7 +4181,7 @@
       <c r="X53" s="2"/>
       <c r="Y53" s="2"/>
     </row>
-    <row r="54" spans="1:25" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:25" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="19">
         <v>6</v>
       </c>
@@ -4217,7 +4226,7 @@
       <c r="X54" s="2"/>
       <c r="Y54" s="2"/>
     </row>
-    <row r="55" spans="1:25" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:25" ht="41.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="18">
         <v>26</v>
       </c>
@@ -4267,7 +4276,7 @@
       <c r="X55" s="2"/>
       <c r="Y55" s="2"/>
     </row>
-    <row r="56" spans="1:25" ht="54" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:25" ht="54" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="19">
         <v>27</v>
       </c>
@@ -4312,7 +4321,7 @@
       <c r="X56" s="2"/>
       <c r="Y56" s="2"/>
     </row>
-    <row r="57" spans="1:25" ht="63.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:25" ht="63.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="19">
         <v>23</v>
       </c>
@@ -4357,7 +4366,7 @@
       <c r="X57" s="2"/>
       <c r="Y57" s="2"/>
     </row>
-    <row r="58" spans="1:25" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:25" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A58" s="44">
         <v>12</v>
       </c>
@@ -4400,7 +4409,7 @@
       <c r="X58" s="2"/>
       <c r="Y58" s="2"/>
     </row>
-    <row r="59" spans="1:25" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:25" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="27">
         <v>11</v>
       </c>
@@ -4445,7 +4454,7 @@
       <c r="X59" s="2"/>
       <c r="Y59" s="2"/>
     </row>
-    <row r="60" spans="1:25" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:25" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="18">
         <v>26</v>
       </c>
@@ -4490,7 +4499,7 @@
       <c r="X60" s="2"/>
       <c r="Y60" s="2"/>
     </row>
-    <row r="61" spans="1:25" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:25" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="18">
         <v>22</v>
       </c>
@@ -4535,7 +4544,7 @@
       <c r="X61" s="2"/>
       <c r="Y61" s="2"/>
     </row>
-    <row r="62" spans="1:25" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:25" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="18">
         <v>3</v>
       </c>
@@ -4580,7 +4589,7 @@
       <c r="X62" s="2"/>
       <c r="Y62" s="2"/>
     </row>
-    <row r="63" spans="1:25" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:25" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="18">
         <v>10</v>
       </c>
@@ -4625,7 +4634,7 @@
       <c r="X63" s="2"/>
       <c r="Y63" s="2"/>
     </row>
-    <row r="64" spans="1:25" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:25" ht="44.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="18">
         <v>1</v>
       </c>
@@ -4670,7 +4679,7 @@
       <c r="X64" s="2"/>
       <c r="Y64" s="2"/>
     </row>
-    <row r="65" spans="1:25" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:25" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="18">
         <v>19</v>
       </c>
@@ -4715,7 +4724,7 @@
       <c r="X65" s="2"/>
       <c r="Y65" s="2"/>
     </row>
-    <row r="66" spans="1:25" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:25" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="18">
         <v>15</v>
       </c>
@@ -4760,7 +4769,7 @@
       <c r="X66" s="2"/>
       <c r="Y66" s="2"/>
     </row>
-    <row r="67" spans="1:25" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:25" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="18">
         <v>7</v>
       </c>
@@ -4810,7 +4819,7 @@
       <c r="X67" s="2"/>
       <c r="Y67" s="2"/>
     </row>
-    <row r="68" spans="1:25" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:25" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="19">
         <v>2</v>
       </c>
@@ -4855,7 +4864,7 @@
       <c r="X68" s="2"/>
       <c r="Y68" s="2"/>
     </row>
-    <row r="69" spans="1:25" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:25" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="19">
         <v>28</v>
       </c>
@@ -4900,7 +4909,7 @@
       <c r="X69" s="2"/>
       <c r="Y69" s="2"/>
     </row>
-    <row r="70" spans="1:25" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:25" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="19">
         <v>23</v>
       </c>
@@ -4945,7 +4954,7 @@
       <c r="X70" s="2"/>
       <c r="Y70" s="2"/>
     </row>
-    <row r="71" spans="1:25" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:25" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="19">
         <v>30</v>
       </c>
@@ -4990,7 +4999,7 @@
       <c r="X71" s="2"/>
       <c r="Y71" s="2"/>
     </row>
-    <row r="72" spans="1:25" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:25" ht="36.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="19">
         <v>25</v>
       </c>
@@ -5034,7 +5043,7 @@
       <c r="X72" s="2"/>
       <c r="Y72" s="2"/>
     </row>
-    <row r="73" spans="1:25" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:25" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="19">
         <v>4</v>
       </c>
@@ -5078,7 +5087,7 @@
       <c r="X73" s="2"/>
       <c r="Y73" s="2"/>
     </row>
-    <row r="74" spans="1:25" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:25" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="19">
         <v>13</v>
       </c>
@@ -5123,7 +5132,7 @@
       <c r="X74" s="2"/>
       <c r="Y74" s="2"/>
     </row>
-    <row r="75" spans="1:25" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:25" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="19">
         <v>14</v>
       </c>
@@ -5168,7 +5177,7 @@
       <c r="X75" s="2"/>
       <c r="Y75" s="2"/>
     </row>
-    <row r="76" spans="1:25" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:25" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="19">
         <v>6</v>
       </c>
@@ -5213,7 +5222,7 @@
       <c r="X76" s="2"/>
       <c r="Y76" s="2"/>
     </row>
-    <row r="77" spans="1:25" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:25" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="19">
         <v>32</v>
       </c>
@@ -5257,7 +5266,7 @@
       <c r="X77" s="2"/>
       <c r="Y77" s="2"/>
     </row>
-    <row r="78" spans="1:25" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:25" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="19">
         <v>9</v>
       </c>
@@ -5302,7 +5311,7 @@
       <c r="X78" s="2"/>
       <c r="Y78" s="2"/>
     </row>
-    <row r="79" spans="1:25" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:25" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" s="19">
         <v>24</v>
       </c>
@@ -5347,7 +5356,7 @@
       <c r="X79" s="2"/>
       <c r="Y79" s="2"/>
     </row>
-    <row r="80" spans="1:25" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:25" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="19">
         <v>18</v>
       </c>
@@ -5392,7 +5401,7 @@
       <c r="X80" s="2"/>
       <c r="Y80" s="2"/>
     </row>
-    <row r="81" spans="1:25" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:25" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="19">
         <v>29</v>
       </c>
@@ -5437,7 +5446,7 @@
       <c r="X81" s="2"/>
       <c r="Y81" s="2"/>
     </row>
-    <row r="82" spans="1:25" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:25" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="19">
         <v>16</v>
       </c>
@@ -5482,7 +5491,7 @@
       <c r="X82" s="2"/>
       <c r="Y82" s="2"/>
     </row>
-    <row r="83" spans="1:25" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:25" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" s="19">
         <v>31</v>
       </c>
@@ -5526,7 +5535,7 @@
       <c r="X83" s="2"/>
       <c r="Y83" s="2"/>
     </row>
-    <row r="84" spans="1:25" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:25" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A84" s="19">
         <v>8</v>
       </c>
@@ -5570,7 +5579,7 @@
       <c r="X84" s="2"/>
       <c r="Y84" s="2"/>
     </row>
-    <row r="85" spans="1:25" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:25" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A85" s="19">
         <v>27</v>
       </c>
@@ -5615,7 +5624,7 @@
       <c r="X85" s="2"/>
       <c r="Y85" s="2"/>
     </row>
-    <row r="86" spans="1:25" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:25" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" s="19">
         <v>12</v>
       </c>
@@ -5658,7 +5667,7 @@
       <c r="X86" s="2"/>
       <c r="Y86" s="2"/>
     </row>
-    <row r="87" spans="1:25" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:25" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" s="19">
         <v>5</v>
       </c>
@@ -5703,7 +5712,7 @@
       <c r="X87" s="2"/>
       <c r="Y87" s="2"/>
     </row>
-    <row r="88" spans="1:25" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:25" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88" s="19">
         <v>17</v>
       </c>
@@ -5748,7 +5757,7 @@
       <c r="X88" s="2"/>
       <c r="Y88" s="2"/>
     </row>
-    <row r="89" spans="1:25" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:25" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A89" s="19">
         <v>20</v>
       </c>
@@ -5793,7 +5802,7 @@
       <c r="X89" s="2"/>
       <c r="Y89" s="2"/>
     </row>
-    <row r="90" spans="1:25" ht="35.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:25" ht="35.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A90" s="37">
         <v>21</v>
       </c>
@@ -5838,7 +5847,7 @@
       <c r="X90" s="2"/>
       <c r="Y90" s="2"/>
     </row>
-    <row r="91" spans="1:25" ht="51" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:25" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" s="27">
         <v>7</v>
       </c>
@@ -5883,7 +5892,7 @@
       <c r="X91" s="2"/>
       <c r="Y91" s="2"/>
     </row>
-    <row r="92" spans="1:25" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:25" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A92" s="18">
         <v>2</v>
       </c>
@@ -5928,7 +5937,7 @@
       <c r="X92" s="2"/>
       <c r="Y92" s="2"/>
     </row>
-    <row r="93" spans="1:25" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:25" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A93" s="18">
         <v>1</v>
       </c>
@@ -5973,7 +5982,7 @@
       <c r="X93" s="2"/>
       <c r="Y93" s="2"/>
     </row>
-    <row r="94" spans="1:25" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:25" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" s="18">
         <v>6</v>
       </c>
@@ -6018,7 +6027,7 @@
       <c r="X94" s="2"/>
       <c r="Y94" s="2"/>
     </row>
-    <row r="95" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A95" s="19">
         <v>8</v>
       </c>
@@ -6063,7 +6072,7 @@
       <c r="X95" s="2"/>
       <c r="Y95" s="2"/>
     </row>
-    <row r="96" spans="1:25" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:25" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A96" s="18">
         <v>5</v>
       </c>
@@ -6108,7 +6117,7 @@
       <c r="X96" s="2"/>
       <c r="Y96" s="2"/>
     </row>
-    <row r="97" spans="1:25" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:25" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A97" s="19">
         <v>4</v>
       </c>
@@ -6152,7 +6161,7 @@
       <c r="X97" s="2"/>
       <c r="Y97" s="2"/>
     </row>
-    <row r="98" spans="1:25" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:25" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A98" s="18">
         <v>10</v>
       </c>
@@ -6195,7 +6204,7 @@
       <c r="X98" s="2"/>
       <c r="Y98" s="2"/>
     </row>
-    <row r="99" spans="1:25" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:25" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A99" s="18">
         <v>3</v>
       </c>
@@ -6238,7 +6247,7 @@
       <c r="X99" s="2"/>
       <c r="Y99" s="2"/>
     </row>
-    <row r="100" spans="1:25" ht="33.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:25" ht="33.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A100" s="32">
         <v>9</v>
       </c>
@@ -6288,7 +6297,7 @@
       <c r="X100" s="2"/>
       <c r="Y100" s="2"/>
     </row>
-    <row r="101" spans="1:25" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:25" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A101" s="27">
         <v>11</v>
       </c>
@@ -6333,7 +6342,7 @@
       <c r="X101" s="2"/>
       <c r="Y101" s="2"/>
     </row>
-    <row r="102" spans="1:25" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:25" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" s="18">
         <v>3</v>
       </c>
@@ -6378,7 +6387,7 @@
       <c r="X102" s="2"/>
       <c r="Y102" s="2"/>
     </row>
-    <row r="103" spans="1:25" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:25" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A103" s="18">
         <v>8</v>
       </c>
@@ -6423,7 +6432,7 @@
       <c r="X103" s="2"/>
       <c r="Y103" s="2"/>
     </row>
-    <row r="104" spans="1:25" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:25" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A104" s="18">
         <v>2</v>
       </c>
@@ -6468,7 +6477,7 @@
       <c r="X104" s="2"/>
       <c r="Y104" s="2"/>
     </row>
-    <row r="105" spans="1:25" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:25" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A105" s="19">
         <v>12</v>
       </c>
@@ -6513,7 +6522,7 @@
       <c r="X105" s="2"/>
       <c r="Y105" s="2"/>
     </row>
-    <row r="106" spans="1:25" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:25" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A106" s="19">
         <v>1</v>
       </c>
@@ -6558,7 +6567,7 @@
       <c r="X106" s="2"/>
       <c r="Y106" s="2"/>
     </row>
-    <row r="107" spans="1:25" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:25" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A107" s="18">
         <v>5</v>
       </c>
@@ -6608,7 +6617,7 @@
       <c r="X107" s="2"/>
       <c r="Y107" s="2"/>
     </row>
-    <row r="108" spans="1:25" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:25" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A108" s="19">
         <v>6</v>
       </c>
@@ -6653,7 +6662,7 @@
       <c r="X108" s="2"/>
       <c r="Y108" s="2"/>
     </row>
-    <row r="109" spans="1:25" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:25" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A109" s="19">
         <v>4</v>
       </c>
@@ -6698,7 +6707,7 @@
       <c r="X109" s="2"/>
       <c r="Y109" s="2"/>
     </row>
-    <row r="110" spans="1:25" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:25" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A110" s="19">
         <v>7</v>
       </c>
@@ -6743,7 +6752,7 @@
       <c r="X110" s="2"/>
       <c r="Y110" s="2"/>
     </row>
-    <row r="111" spans="1:25" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:25" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A111" s="19">
         <v>10</v>
       </c>
@@ -6788,7 +6797,7 @@
       <c r="X111" s="2"/>
       <c r="Y111" s="2"/>
     </row>
-    <row r="112" spans="1:25" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:25" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A112" s="37">
         <v>9</v>
       </c>
@@ -6833,7 +6842,7 @@
       <c r="X112" s="2"/>
       <c r="Y112" s="2"/>
     </row>
-    <row r="113" spans="1:25" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:25" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A113" s="28">
         <v>10</v>
       </c>
@@ -6878,7 +6887,7 @@
       <c r="X113" s="2"/>
       <c r="Y113" s="2"/>
     </row>
-    <row r="114" spans="1:25" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:25" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A114" s="15">
         <v>9</v>
       </c>
@@ -6923,7 +6932,7 @@
       <c r="X114" s="2"/>
       <c r="Y114" s="2"/>
     </row>
-    <row r="115" spans="1:25" ht="79.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:25" ht="79.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A115" s="15">
         <v>20</v>
       </c>
@@ -6968,7 +6977,7 @@
       <c r="X115" s="2"/>
       <c r="Y115" s="2"/>
     </row>
-    <row r="116" spans="1:25" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:25" ht="36.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A116" s="15">
         <v>2</v>
       </c>
@@ -7013,7 +7022,7 @@
       <c r="X116" s="2"/>
       <c r="Y116" s="2"/>
     </row>
-    <row r="117" spans="1:25" ht="48.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:25" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A117" s="15">
         <v>12</v>
       </c>
@@ -7058,7 +7067,7 @@
       <c r="X117" s="2"/>
       <c r="Y117" s="2"/>
     </row>
-    <row r="118" spans="1:25" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:25" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A118" s="19">
         <v>4</v>
       </c>
@@ -7103,7 +7112,7 @@
       <c r="X118" s="2"/>
       <c r="Y118" s="2"/>
     </row>
-    <row r="119" spans="1:25" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:25" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A119" s="15">
         <v>5</v>
       </c>
@@ -7148,7 +7157,7 @@
       <c r="X119" s="2"/>
       <c r="Y119" s="2"/>
     </row>
-    <row r="120" spans="1:25" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:25" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A120" s="15">
         <v>13</v>
       </c>
@@ -7193,7 +7202,7 @@
       <c r="X120" s="2"/>
       <c r="Y120" s="2"/>
     </row>
-    <row r="121" spans="1:25" ht="63" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:25" ht="63" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A121" s="15">
         <v>19</v>
       </c>
@@ -7238,7 +7247,7 @@
       <c r="X121" s="2"/>
       <c r="Y121" s="2"/>
     </row>
-    <row r="122" spans="1:25" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:25" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A122" s="19">
         <v>8</v>
       </c>
@@ -7283,7 +7292,7 @@
       <c r="X122" s="2"/>
       <c r="Y122" s="2"/>
     </row>
-    <row r="123" spans="1:25" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:25" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A123" s="15">
         <v>1</v>
       </c>
@@ -7328,7 +7337,7 @@
       <c r="X123" s="2"/>
       <c r="Y123" s="2"/>
     </row>
-    <row r="124" spans="1:25" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:25" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A124" s="19">
         <v>6</v>
       </c>
@@ -7373,7 +7382,7 @@
       <c r="X124" s="2"/>
       <c r="Y124" s="2"/>
     </row>
-    <row r="125" spans="1:25" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:25" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A125" s="19">
         <v>7</v>
       </c>
@@ -7418,7 +7427,7 @@
       <c r="X125" s="2"/>
       <c r="Y125" s="2"/>
     </row>
-    <row r="126" spans="1:25" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:25" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A126" s="15">
         <v>22</v>
       </c>
@@ -7463,7 +7472,7 @@
       <c r="X126" s="2"/>
       <c r="Y126" s="2"/>
     </row>
-    <row r="127" spans="1:25" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:25" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A127" s="19">
         <v>15</v>
       </c>
@@ -7508,7 +7517,7 @@
       <c r="X127" s="2"/>
       <c r="Y127" s="2"/>
     </row>
-    <row r="128" spans="1:25" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:25" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A128" s="15">
         <v>24</v>
       </c>
@@ -7553,7 +7562,7 @@
       <c r="X128" s="2"/>
       <c r="Y128" s="2"/>
     </row>
-    <row r="129" spans="1:25" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:25" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A129" s="19">
         <v>18</v>
       </c>
@@ -7598,7 +7607,7 @@
       <c r="X129" s="2"/>
       <c r="Y129" s="2"/>
     </row>
-    <row r="130" spans="1:25" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:25" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A130" s="19">
         <v>16</v>
       </c>
@@ -7643,7 +7652,7 @@
       <c r="X130" s="2"/>
       <c r="Y130" s="2"/>
     </row>
-    <row r="131" spans="1:25" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:25" ht="45.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A131" s="19">
         <v>21</v>
       </c>
@@ -7688,7 +7697,7 @@
       <c r="X131" s="2"/>
       <c r="Y131" s="2"/>
     </row>
-    <row r="132" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A132" s="15">
         <v>3</v>
       </c>
@@ -7738,7 +7747,7 @@
       <c r="X132" s="2"/>
       <c r="Y132" s="2"/>
     </row>
-    <row r="133" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A133" s="19">
         <v>17</v>
       </c>
@@ -7783,7 +7792,7 @@
       <c r="X133" s="2"/>
       <c r="Y133" s="2"/>
     </row>
-    <row r="134" spans="1:25" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:25" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A134" s="19">
         <v>14</v>
       </c>
@@ -7828,7 +7837,7 @@
       <c r="X134" s="2"/>
       <c r="Y134" s="2"/>
     </row>
-    <row r="135" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A135" s="19">
         <v>11</v>
       </c>
@@ -7873,7 +7882,7 @@
       <c r="X135" s="2"/>
       <c r="Y135" s="2"/>
     </row>
-    <row r="136" spans="1:25" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:25" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A136" s="37">
         <v>23</v>
       </c>
@@ -7918,7 +7927,7 @@
       <c r="X136" s="2"/>
       <c r="Y136" s="2"/>
     </row>
-    <row r="137" spans="1:25" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:25" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A137" s="27">
         <v>5</v>
       </c>
@@ -7963,7 +7972,7 @@
       <c r="X137" s="2"/>
       <c r="Y137" s="2"/>
     </row>
-    <row r="138" spans="1:25" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:25" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A138" s="18">
         <v>3</v>
       </c>
@@ -8008,7 +8017,7 @@
       <c r="X138" s="2"/>
       <c r="Y138" s="2"/>
     </row>
-    <row r="139" spans="1:25" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:25" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A139" s="18">
         <v>1</v>
       </c>
@@ -8053,7 +8062,7 @@
       <c r="X139" s="2"/>
       <c r="Y139" s="2"/>
     </row>
-    <row r="140" spans="1:25" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:25" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A140" s="18">
         <v>6</v>
       </c>
@@ -8098,7 +8107,7 @@
       <c r="X140" s="2"/>
       <c r="Y140" s="2"/>
     </row>
-    <row r="141" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A141" s="18">
         <v>4</v>
       </c>
@@ -8142,7 +8151,7 @@
       <c r="X141" s="2"/>
       <c r="Y141" s="2"/>
     </row>
-    <row r="142" spans="1:25" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:25" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A142" s="18">
         <v>2</v>
       </c>
@@ -8192,7 +8201,7 @@
       <c r="X142" s="2"/>
       <c r="Y142" s="2"/>
     </row>
-    <row r="143" spans="1:25" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:25" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A143" s="19">
         <v>8</v>
       </c>
@@ -8235,7 +8244,7 @@
       <c r="X143" s="2"/>
       <c r="Y143" s="2"/>
     </row>
-    <row r="144" spans="1:25" ht="33.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:25" ht="33.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A144" s="37">
         <v>7</v>
       </c>
@@ -8280,7 +8289,7 @@
       <c r="X144" s="2"/>
       <c r="Y144" s="2"/>
     </row>
-    <row r="145" spans="1:25" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:25" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A145" s="27">
         <v>3</v>
       </c>
@@ -8325,7 +8334,7 @@
       <c r="X145" s="2"/>
       <c r="Y145" s="2"/>
     </row>
-    <row r="146" spans="1:25" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:25" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A146" s="18">
         <v>15</v>
       </c>
@@ -8370,7 +8379,7 @@
       <c r="X146" s="2"/>
       <c r="Y146" s="2"/>
     </row>
-    <row r="147" spans="1:25" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:25" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A147" s="18">
         <v>30</v>
       </c>
@@ -8415,7 +8424,7 @@
       <c r="X147" s="2"/>
       <c r="Y147" s="2"/>
     </row>
-    <row r="148" spans="1:25" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:25" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A148" s="19">
         <v>4</v>
       </c>
@@ -8460,7 +8469,7 @@
       <c r="X148" s="2"/>
       <c r="Y148" s="2"/>
     </row>
-    <row r="149" spans="1:25" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:25" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A149" s="19">
         <v>9</v>
       </c>
@@ -8505,7 +8514,7 @@
       <c r="X149" s="2"/>
       <c r="Y149" s="2"/>
     </row>
-    <row r="150" spans="1:25" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:25" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A150" s="18">
         <v>25</v>
       </c>
@@ -8550,7 +8559,7 @@
       <c r="X150" s="2"/>
       <c r="Y150" s="2"/>
     </row>
-    <row r="151" spans="1:25" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:25" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A151" s="18">
         <v>13</v>
       </c>
@@ -8595,7 +8604,7 @@
       <c r="X151" s="2"/>
       <c r="Y151" s="2"/>
     </row>
-    <row r="152" spans="1:25" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:25" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A152" s="18">
         <v>5</v>
       </c>
@@ -8640,7 +8649,7 @@
       <c r="X152" s="2"/>
       <c r="Y152" s="2"/>
     </row>
-    <row r="153" spans="1:25" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:25" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A153" s="18">
         <v>18</v>
       </c>
@@ -8685,7 +8694,7 @@
       <c r="X153" s="2"/>
       <c r="Y153" s="2"/>
     </row>
-    <row r="154" spans="1:25" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:25" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A154" s="18">
         <v>7</v>
       </c>
@@ -8730,7 +8739,7 @@
       <c r="X154" s="2"/>
       <c r="Y154" s="2"/>
     </row>
-    <row r="155" spans="1:25" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:25" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A155" s="18">
         <v>24</v>
       </c>
@@ -8775,7 +8784,7 @@
       <c r="X155" s="2"/>
       <c r="Y155" s="2"/>
     </row>
-    <row r="156" spans="1:25" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:25" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A156" s="19">
         <v>27</v>
       </c>
@@ -8820,7 +8829,7 @@
       <c r="X156" s="2"/>
       <c r="Y156" s="2"/>
     </row>
-    <row r="157" spans="1:25" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:25" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A157" s="19">
         <v>8</v>
       </c>
@@ -8865,7 +8874,7 @@
       <c r="X157" s="2"/>
       <c r="Y157" s="2"/>
     </row>
-    <row r="158" spans="1:25" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:25" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A158" s="19">
         <v>2</v>
       </c>
@@ -8910,7 +8919,7 @@
       <c r="X158" s="2"/>
       <c r="Y158" s="2"/>
     </row>
-    <row r="159" spans="1:25" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:25" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A159" s="19">
         <v>17</v>
       </c>
@@ -8954,7 +8963,7 @@
       <c r="X159" s="2"/>
       <c r="Y159" s="2"/>
     </row>
-    <row r="160" spans="1:25" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:25" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A160" s="19">
         <v>14</v>
       </c>
@@ -8999,7 +9008,7 @@
       <c r="X160" s="2"/>
       <c r="Y160" s="2"/>
     </row>
-    <row r="161" spans="1:25" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:25" ht="36.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A161" s="18">
         <v>1</v>
       </c>
@@ -9044,7 +9053,7 @@
       <c r="X161" s="2"/>
       <c r="Y161" s="2"/>
     </row>
-    <row r="162" spans="1:25" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:25" ht="36.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A162" s="19">
         <v>20</v>
       </c>
@@ -9089,7 +9098,7 @@
       <c r="X162" s="2"/>
       <c r="Y162" s="2"/>
     </row>
-    <row r="163" spans="1:25" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:25" ht="36.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A163" s="18">
         <v>23</v>
       </c>
@@ -9132,7 +9141,7 @@
       <c r="X163" s="2"/>
       <c r="Y163" s="2"/>
     </row>
-    <row r="164" spans="1:25" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:25" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A164" s="19">
         <v>6</v>
       </c>
@@ -9177,7 +9186,7 @@
       <c r="X164" s="2"/>
       <c r="Y164" s="2"/>
     </row>
-    <row r="165" spans="1:25" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:25" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A165" s="19">
         <v>22</v>
       </c>
@@ -9222,7 +9231,7 @@
       <c r="X165" s="2"/>
       <c r="Y165" s="2"/>
     </row>
-    <row r="166" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A166" s="19">
         <v>11</v>
       </c>
@@ -9267,7 +9276,7 @@
       <c r="X166" s="2"/>
       <c r="Y166" s="2"/>
     </row>
-    <row r="167" spans="1:25" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:25" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A167" s="19">
         <v>26</v>
       </c>
@@ -9312,7 +9321,7 @@
       <c r="X167" s="2"/>
       <c r="Y167" s="2"/>
     </row>
-    <row r="168" spans="1:25" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:25" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A168" s="19">
         <v>16</v>
       </c>
@@ -9357,7 +9366,7 @@
       <c r="X168" s="2"/>
       <c r="Y168" s="2"/>
     </row>
-    <row r="169" spans="1:25" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:25" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A169" s="18">
         <v>21</v>
       </c>
@@ -9407,7 +9416,7 @@
       <c r="X169" s="2"/>
       <c r="Y169" s="2"/>
     </row>
-    <row r="170" spans="1:25" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:25" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A170" s="19">
         <v>12</v>
       </c>
@@ -9452,7 +9461,7 @@
       <c r="X170" s="2"/>
       <c r="Y170" s="2"/>
     </row>
-    <row r="171" spans="1:25" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:25" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A171" s="19">
         <v>19</v>
       </c>
@@ -9497,7 +9506,7 @@
       <c r="X171" s="2"/>
       <c r="Y171" s="2"/>
     </row>
-    <row r="172" spans="1:25" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:25" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A172" s="19">
         <v>28</v>
       </c>
@@ -9542,7 +9551,7 @@
       <c r="X172" s="2"/>
       <c r="Y172" s="2"/>
     </row>
-    <row r="173" spans="1:25" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:25" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A173" s="19">
         <v>10</v>
       </c>
@@ -9587,7 +9596,7 @@
       <c r="X173" s="2"/>
       <c r="Y173" s="2"/>
     </row>
-    <row r="174" spans="1:25" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:25" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A174" s="37">
         <v>29</v>
       </c>
@@ -9632,7 +9641,7 @@
       <c r="X174" s="2"/>
       <c r="Y174" s="2"/>
     </row>
-    <row r="175" spans="1:25" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:25" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A175" s="27">
         <v>2</v>
       </c>
@@ -9677,7 +9686,7 @@
       <c r="X175" s="2"/>
       <c r="Y175" s="2"/>
     </row>
-    <row r="176" spans="1:25" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:25" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A176" s="18">
         <v>1</v>
       </c>
@@ -9722,7 +9731,7 @@
       <c r="X176" s="2"/>
       <c r="Y176" s="2"/>
     </row>
-    <row r="177" spans="1:25" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:25" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A177" s="18">
         <v>13</v>
       </c>
@@ -9767,7 +9776,7 @@
       <c r="X177" s="2"/>
       <c r="Y177" s="2"/>
     </row>
-    <row r="178" spans="1:25" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:25" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A178" s="18">
         <v>3</v>
       </c>
@@ -9812,7 +9821,7 @@
       <c r="X178" s="2"/>
       <c r="Y178" s="2"/>
     </row>
-    <row r="179" spans="1:25" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:25" ht="38.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A179" s="18">
         <v>16</v>
       </c>
@@ -9857,7 +9866,7 @@
       <c r="X179" s="2"/>
       <c r="Y179" s="2"/>
     </row>
-    <row r="180" spans="1:25" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:25" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A180" s="18">
         <v>9</v>
       </c>
@@ -9902,7 +9911,7 @@
       <c r="X180" s="2"/>
       <c r="Y180" s="2"/>
     </row>
-    <row r="181" spans="1:25" ht="65.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:25" ht="65.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A181" s="19">
         <v>5</v>
       </c>
@@ -9947,7 +9956,7 @@
       <c r="X181" s="2"/>
       <c r="Y181" s="2"/>
     </row>
-    <row r="182" spans="1:25" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:25" ht="35.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A182" s="19">
         <v>11</v>
       </c>
@@ -9992,7 +10001,7 @@
       <c r="X182" s="2"/>
       <c r="Y182" s="2"/>
     </row>
-    <row r="183" spans="1:25" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:25" ht="38.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A183" s="19">
         <v>7</v>
       </c>
@@ -10037,7 +10046,7 @@
       <c r="X183" s="2"/>
       <c r="Y183" s="2"/>
     </row>
-    <row r="184" spans="1:25" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:25" ht="38.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A184" s="19">
         <v>15</v>
       </c>
@@ -10082,7 +10091,7 @@
       <c r="X184" s="2"/>
       <c r="Y184" s="2"/>
     </row>
-    <row r="185" spans="1:25" ht="57" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:25" ht="57" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A185" s="18">
         <v>14</v>
       </c>
@@ -10125,7 +10134,7 @@
       <c r="X185" s="2"/>
       <c r="Y185" s="2"/>
     </row>
-    <row r="186" spans="1:25" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:25" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A186" s="19">
         <v>12</v>
       </c>
@@ -10170,7 +10179,7 @@
       <c r="X186" s="2"/>
       <c r="Y186" s="2"/>
     </row>
-    <row r="187" spans="1:25" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:25" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A187" s="19">
         <v>8</v>
       </c>
@@ -10215,7 +10224,7 @@
       <c r="X187" s="2"/>
       <c r="Y187" s="2"/>
     </row>
-    <row r="188" spans="1:25" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:25" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A188" s="19">
         <v>6</v>
       </c>
@@ -10260,7 +10269,7 @@
       <c r="X188" s="2"/>
       <c r="Y188" s="2"/>
     </row>
-    <row r="189" spans="1:25" ht="39" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:25" ht="39" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A189" s="18">
         <v>4</v>
       </c>
@@ -10310,7 +10319,7 @@
       <c r="X189" s="2"/>
       <c r="Y189" s="2"/>
     </row>
-    <row r="190" spans="1:25" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:25" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A190" s="37">
         <v>10</v>
       </c>
@@ -10355,7 +10364,7 @@
       <c r="X190" s="2"/>
       <c r="Y190" s="2"/>
     </row>
-    <row r="191" spans="1:25" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:25" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B191" s="5"/>
       <c r="C191" s="5"/>
       <c r="E191" s="2"/>
@@ -10386,7 +10395,7 @@
       <c r="X191" s="2"/>
       <c r="Y191" s="2"/>
     </row>
-    <row r="192" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B192" s="5"/>
       <c r="C192" s="5"/>
       <c r="D192" s="10"/>
@@ -10412,7 +10421,7 @@
       <c r="X192" s="2"/>
       <c r="Y192" s="2"/>
     </row>
-    <row r="193" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B193" s="5"/>
       <c r="C193" s="5"/>
       <c r="D193" s="4"/>
@@ -10438,7 +10447,7 @@
       <c r="X193" s="2"/>
       <c r="Y193" s="2"/>
     </row>
-    <row r="194" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B194" s="5"/>
       <c r="C194" s="5"/>
       <c r="D194" s="4"/>
@@ -10464,7 +10473,7 @@
       <c r="X194" s="2"/>
       <c r="Y194" s="2"/>
     </row>
-    <row r="195" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B195" s="5"/>
       <c r="C195" s="5"/>
       <c r="D195" s="4"/>
@@ -10490,7 +10499,7 @@
       <c r="X195" s="2"/>
       <c r="Y195" s="2"/>
     </row>
-    <row r="196" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B196" s="5"/>
       <c r="C196" s="5"/>
       <c r="D196" s="4"/>
@@ -10516,7 +10525,7 @@
       <c r="X196" s="2"/>
       <c r="Y196" s="2"/>
     </row>
-    <row r="197" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="197" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B197" s="5"/>
       <c r="C197" s="5"/>
       <c r="D197" s="4"/>
@@ -10542,7 +10551,7 @@
       <c r="X197" s="2"/>
       <c r="Y197" s="2"/>
     </row>
-    <row r="198" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="198" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B198" s="5"/>
       <c r="C198" s="5"/>
       <c r="D198" s="4"/>
@@ -10568,7 +10577,7 @@
       <c r="X198" s="2"/>
       <c r="Y198" s="2"/>
     </row>
-    <row r="199" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="199" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B199" s="5"/>
       <c r="C199" s="5"/>
       <c r="D199" s="4"/>
@@ -10594,7 +10603,7 @@
       <c r="X199" s="2"/>
       <c r="Y199" s="2"/>
     </row>
-    <row r="200" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="200" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B200" s="5"/>
       <c r="C200" s="5"/>
       <c r="D200" s="4"/>
@@ -10620,7 +10629,7 @@
       <c r="X200" s="2"/>
       <c r="Y200" s="2"/>
     </row>
-    <row r="201" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="201" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B201" s="5"/>
       <c r="C201" s="5"/>
       <c r="D201" s="4"/>
@@ -10646,7 +10655,7 @@
       <c r="X201" s="2"/>
       <c r="Y201" s="2"/>
     </row>
-    <row r="202" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="202" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B202" s="5"/>
       <c r="C202" s="5"/>
       <c r="D202" s="4"/>
@@ -10672,7 +10681,7 @@
       <c r="X202" s="2"/>
       <c r="Y202" s="2"/>
     </row>
-    <row r="203" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="203" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B203" s="5"/>
       <c r="C203" s="5"/>
       <c r="D203" s="4"/>
@@ -10698,7 +10707,7 @@
       <c r="X203" s="2"/>
       <c r="Y203" s="2"/>
     </row>
-    <row r="204" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="204" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B204" s="5"/>
       <c r="C204" s="5"/>
       <c r="D204" s="4"/>
@@ -10724,7 +10733,7 @@
       <c r="X204" s="2"/>
       <c r="Y204" s="2"/>
     </row>
-    <row r="205" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B205" s="5"/>
       <c r="C205" s="5"/>
       <c r="D205" s="4"/>
@@ -10750,7 +10759,7 @@
       <c r="X205" s="2"/>
       <c r="Y205" s="2"/>
     </row>
-    <row r="206" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="206" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B206" s="5"/>
       <c r="C206" s="5"/>
       <c r="D206" s="4"/>
@@ -10776,7 +10785,7 @@
       <c r="X206" s="2"/>
       <c r="Y206" s="2"/>
     </row>
-    <row r="207" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B207" s="5"/>
       <c r="C207" s="5"/>
       <c r="D207" s="4"/>
@@ -10802,7 +10811,7 @@
       <c r="X207" s="2"/>
       <c r="Y207" s="2"/>
     </row>
-    <row r="208" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="208" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B208" s="5"/>
       <c r="C208" s="5"/>
       <c r="D208" s="4"/>
@@ -10828,7 +10837,7 @@
       <c r="X208" s="2"/>
       <c r="Y208" s="2"/>
     </row>
-    <row r="209" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="209" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B209" s="5"/>
       <c r="C209" s="5"/>
       <c r="D209" s="4"/>
@@ -10854,7 +10863,7 @@
       <c r="X209" s="2"/>
       <c r="Y209" s="2"/>
     </row>
-    <row r="210" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="210" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B210" s="5"/>
       <c r="C210" s="5"/>
       <c r="D210" s="4"/>
@@ -10880,7 +10889,7 @@
       <c r="X210" s="2"/>
       <c r="Y210" s="2"/>
     </row>
-    <row r="211" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="211" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B211" s="5"/>
       <c r="C211" s="5"/>
       <c r="D211" s="4"/>
@@ -10906,7 +10915,7 @@
       <c r="X211" s="2"/>
       <c r="Y211" s="2"/>
     </row>
-    <row r="212" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="212" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B212" s="5"/>
       <c r="C212" s="5"/>
       <c r="D212" s="4"/>
@@ -10932,7 +10941,7 @@
       <c r="X212" s="2"/>
       <c r="Y212" s="2"/>
     </row>
-    <row r="213" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="213" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B213" s="5"/>
       <c r="C213" s="5"/>
       <c r="D213" s="4"/>
@@ -10958,7 +10967,7 @@
       <c r="X213" s="2"/>
       <c r="Y213" s="2"/>
     </row>
-    <row r="214" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="214" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B214" s="5"/>
       <c r="C214" s="5"/>
       <c r="D214" s="4"/>
@@ -10984,7 +10993,7 @@
       <c r="X214" s="2"/>
       <c r="Y214" s="2"/>
     </row>
-    <row r="215" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B215" s="5"/>
       <c r="C215" s="5"/>
       <c r="D215" s="4"/>
@@ -11010,7 +11019,7 @@
       <c r="X215" s="2"/>
       <c r="Y215" s="2"/>
     </row>
-    <row r="216" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="216" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B216" s="5"/>
       <c r="C216" s="5"/>
       <c r="D216" s="4"/>
@@ -11036,7 +11045,7 @@
       <c r="X216" s="2"/>
       <c r="Y216" s="2"/>
     </row>
-    <row r="217" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="217" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B217" s="5"/>
       <c r="C217" s="5"/>
       <c r="D217" s="4"/>
@@ -11062,7 +11071,7 @@
       <c r="X217" s="2"/>
       <c r="Y217" s="2"/>
     </row>
-    <row r="218" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="218" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B218" s="5"/>
       <c r="C218" s="5"/>
       <c r="D218" s="4"/>
@@ -11088,7 +11097,7 @@
       <c r="X218" s="2"/>
       <c r="Y218" s="2"/>
     </row>
-    <row r="219" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="219" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B219" s="5"/>
       <c r="C219" s="5"/>
       <c r="D219" s="4"/>
@@ -11114,7 +11123,7 @@
       <c r="X219" s="2"/>
       <c r="Y219" s="2"/>
     </row>
-    <row r="220" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="220" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B220" s="5"/>
       <c r="C220" s="5"/>
       <c r="D220" s="4"/>
@@ -11140,7 +11149,7 @@
       <c r="X220" s="2"/>
       <c r="Y220" s="2"/>
     </row>
-    <row r="221" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="221" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B221" s="5"/>
       <c r="C221" s="5"/>
       <c r="D221" s="4"/>
@@ -11166,7 +11175,7 @@
       <c r="X221" s="2"/>
       <c r="Y221" s="2"/>
     </row>
-    <row r="222" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="222" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B222" s="5"/>
       <c r="C222" s="5"/>
       <c r="D222" s="4"/>
@@ -11192,7 +11201,7 @@
       <c r="X222" s="2"/>
       <c r="Y222" s="2"/>
     </row>
-    <row r="223" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="223" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B223" s="5"/>
       <c r="C223" s="5"/>
       <c r="D223" s="4"/>
@@ -11218,7 +11227,7 @@
       <c r="X223" s="2"/>
       <c r="Y223" s="2"/>
     </row>
-    <row r="224" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="224" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B224" s="5"/>
       <c r="C224" s="5"/>
       <c r="D224" s="4"/>
@@ -11244,7 +11253,7 @@
       <c r="X224" s="2"/>
       <c r="Y224" s="2"/>
     </row>
-    <row r="225" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="225" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B225" s="5"/>
       <c r="C225" s="5"/>
       <c r="D225" s="4"/>
@@ -11270,7 +11279,7 @@
       <c r="X225" s="2"/>
       <c r="Y225" s="2"/>
     </row>
-    <row r="226" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="226" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B226" s="5"/>
       <c r="C226" s="5"/>
       <c r="D226" s="4"/>
@@ -11296,7 +11305,7 @@
       <c r="X226" s="2"/>
       <c r="Y226" s="2"/>
     </row>
-    <row r="227" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="227" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B227" s="5"/>
       <c r="C227" s="5"/>
       <c r="D227" s="4"/>
@@ -11322,7 +11331,7 @@
       <c r="X227" s="2"/>
       <c r="Y227" s="2"/>
     </row>
-    <row r="228" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="228" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B228" s="5"/>
       <c r="C228" s="5"/>
       <c r="D228" s="4"/>
@@ -11348,7 +11357,7 @@
       <c r="X228" s="2"/>
       <c r="Y228" s="2"/>
     </row>
-    <row r="229" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="229" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B229" s="5"/>
       <c r="C229" s="5"/>
       <c r="D229" s="4"/>
@@ -11374,7 +11383,7 @@
       <c r="X229" s="2"/>
       <c r="Y229" s="2"/>
     </row>
-    <row r="230" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="230" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B230" s="5"/>
       <c r="C230" s="5"/>
       <c r="D230" s="4"/>
@@ -11400,7 +11409,7 @@
       <c r="X230" s="2"/>
       <c r="Y230" s="2"/>
     </row>
-    <row r="231" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="231" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B231" s="5"/>
       <c r="C231" s="5"/>
       <c r="D231" s="4"/>
@@ -11426,7 +11435,7 @@
       <c r="X231" s="2"/>
       <c r="Y231" s="2"/>
     </row>
-    <row r="232" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="232" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B232" s="5"/>
       <c r="C232" s="5"/>
       <c r="D232" s="4"/>
@@ -11452,7 +11461,7 @@
       <c r="X232" s="2"/>
       <c r="Y232" s="2"/>
     </row>
-    <row r="233" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="233" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B233" s="5"/>
       <c r="C233" s="5"/>
       <c r="D233" s="4"/>
@@ -11478,7 +11487,7 @@
       <c r="X233" s="2"/>
       <c r="Y233" s="2"/>
     </row>
-    <row r="234" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="234" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B234" s="5"/>
       <c r="C234" s="5"/>
       <c r="D234" s="4"/>
@@ -11504,7 +11513,7 @@
       <c r="X234" s="2"/>
       <c r="Y234" s="2"/>
     </row>
-    <row r="235" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="235" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B235" s="5"/>
       <c r="C235" s="5"/>
       <c r="D235" s="4"/>
@@ -11530,7 +11539,7 @@
       <c r="X235" s="2"/>
       <c r="Y235" s="2"/>
     </row>
-    <row r="236" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="236" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B236" s="5"/>
       <c r="C236" s="5"/>
       <c r="D236" s="4"/>
@@ -11556,7 +11565,7 @@
       <c r="X236" s="2"/>
       <c r="Y236" s="2"/>
     </row>
-    <row r="237" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="237" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B237" s="5"/>
       <c r="C237" s="5"/>
       <c r="D237" s="4"/>
@@ -11582,7 +11591,7 @@
       <c r="X237" s="2"/>
       <c r="Y237" s="2"/>
     </row>
-    <row r="238" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="238" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B238" s="5"/>
       <c r="C238" s="5"/>
       <c r="D238" s="4"/>
@@ -11608,7 +11617,7 @@
       <c r="X238" s="2"/>
       <c r="Y238" s="2"/>
     </row>
-    <row r="239" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="239" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B239" s="5"/>
       <c r="C239" s="5"/>
       <c r="D239" s="4"/>
@@ -11634,7 +11643,7 @@
       <c r="X239" s="2"/>
       <c r="Y239" s="2"/>
     </row>
-    <row r="240" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="240" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B240" s="5"/>
       <c r="C240" s="5"/>
       <c r="D240" s="4"/>
@@ -11660,7 +11669,7 @@
       <c r="X240" s="2"/>
       <c r="Y240" s="2"/>
     </row>
-    <row r="241" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="241" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B241" s="5"/>
       <c r="C241" s="5"/>
       <c r="D241" s="4"/>
@@ -11686,7 +11695,7 @@
       <c r="X241" s="2"/>
       <c r="Y241" s="2"/>
     </row>
-    <row r="242" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="242" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B242" s="5"/>
       <c r="C242" s="5"/>
       <c r="D242" s="4"/>
@@ -11712,7 +11721,7 @@
       <c r="X242" s="2"/>
       <c r="Y242" s="2"/>
     </row>
-    <row r="243" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="243" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B243" s="5"/>
       <c r="C243" s="5"/>
       <c r="D243" s="4"/>
@@ -11738,7 +11747,7 @@
       <c r="X243" s="2"/>
       <c r="Y243" s="2"/>
     </row>
-    <row r="244" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="244" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B244" s="5"/>
       <c r="C244" s="5"/>
       <c r="D244" s="4"/>
@@ -11764,7 +11773,7 @@
       <c r="X244" s="2"/>
       <c r="Y244" s="2"/>
     </row>
-    <row r="245" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="245" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B245" s="5"/>
       <c r="C245" s="5"/>
       <c r="D245" s="4"/>
@@ -11790,7 +11799,7 @@
       <c r="X245" s="2"/>
       <c r="Y245" s="2"/>
     </row>
-    <row r="246" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="246" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B246" s="5"/>
       <c r="C246" s="5"/>
       <c r="D246" s="4"/>
@@ -11816,7 +11825,7 @@
       <c r="X246" s="2"/>
       <c r="Y246" s="2"/>
     </row>
-    <row r="247" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="247" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B247" s="5"/>
       <c r="C247" s="5"/>
       <c r="D247" s="4"/>
@@ -11842,7 +11851,7 @@
       <c r="X247" s="2"/>
       <c r="Y247" s="2"/>
     </row>
-    <row r="248" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="248" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B248" s="5"/>
       <c r="C248" s="5"/>
       <c r="D248" s="4"/>
@@ -11868,7 +11877,7 @@
       <c r="X248" s="2"/>
       <c r="Y248" s="2"/>
     </row>
-    <row r="249" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="249" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B249" s="5"/>
       <c r="C249" s="5"/>
       <c r="D249" s="4"/>
@@ -11894,7 +11903,7 @@
       <c r="X249" s="2"/>
       <c r="Y249" s="2"/>
     </row>
-    <row r="250" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="250" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B250" s="5"/>
       <c r="C250" s="5"/>
       <c r="D250" s="4"/>
@@ -11920,7 +11929,7 @@
       <c r="X250" s="2"/>
       <c r="Y250" s="2"/>
     </row>
-    <row r="251" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="251" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B251" s="5"/>
       <c r="C251" s="5"/>
       <c r="D251" s="4"/>
@@ -11946,7 +11955,7 @@
       <c r="X251" s="2"/>
       <c r="Y251" s="2"/>
     </row>
-    <row r="252" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="252" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B252" s="5"/>
       <c r="C252" s="5"/>
       <c r="D252" s="4"/>
@@ -11972,7 +11981,7 @@
       <c r="X252" s="2"/>
       <c r="Y252" s="2"/>
     </row>
-    <row r="253" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="253" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B253" s="5"/>
       <c r="C253" s="5"/>
       <c r="D253" s="4"/>
@@ -11998,7 +12007,7 @@
       <c r="X253" s="2"/>
       <c r="Y253" s="2"/>
     </row>
-    <row r="254" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="254" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B254" s="5"/>
       <c r="C254" s="5"/>
       <c r="D254" s="4"/>
@@ -12024,7 +12033,7 @@
       <c r="X254" s="2"/>
       <c r="Y254" s="2"/>
     </row>
-    <row r="255" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="255" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B255" s="5"/>
       <c r="C255" s="5"/>
       <c r="D255" s="4"/>
@@ -12050,7 +12059,7 @@
       <c r="X255" s="2"/>
       <c r="Y255" s="2"/>
     </row>
-    <row r="256" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="256" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B256" s="5"/>
       <c r="C256" s="5"/>
       <c r="D256" s="4"/>
@@ -12076,7 +12085,7 @@
       <c r="X256" s="2"/>
       <c r="Y256" s="2"/>
     </row>
-    <row r="257" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="257" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B257" s="5"/>
       <c r="C257" s="5"/>
       <c r="D257" s="4"/>
@@ -12102,7 +12111,7 @@
       <c r="X257" s="2"/>
       <c r="Y257" s="2"/>
     </row>
-    <row r="258" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="258" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B258" s="5"/>
       <c r="C258" s="5"/>
       <c r="D258" s="4"/>
@@ -12128,7 +12137,7 @@
       <c r="X258" s="2"/>
       <c r="Y258" s="2"/>
     </row>
-    <row r="259" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="259" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B259" s="5"/>
       <c r="C259" s="5"/>
       <c r="D259" s="4"/>
@@ -12154,7 +12163,7 @@
       <c r="X259" s="2"/>
       <c r="Y259" s="2"/>
     </row>
-    <row r="260" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="260" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B260" s="5"/>
       <c r="C260" s="5"/>
       <c r="D260" s="4"/>
@@ -12180,7 +12189,7 @@
       <c r="X260" s="2"/>
       <c r="Y260" s="2"/>
     </row>
-    <row r="261" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="261" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B261" s="5"/>
       <c r="C261" s="5"/>
       <c r="D261" s="4"/>
@@ -12206,7 +12215,7 @@
       <c r="X261" s="2"/>
       <c r="Y261" s="2"/>
     </row>
-    <row r="262" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="262" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B262" s="5"/>
       <c r="C262" s="5"/>
       <c r="D262" s="4"/>
@@ -12232,7 +12241,7 @@
       <c r="X262" s="2"/>
       <c r="Y262" s="2"/>
     </row>
-    <row r="263" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="263" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B263" s="5"/>
       <c r="C263" s="5"/>
       <c r="D263" s="4"/>
@@ -12258,7 +12267,7 @@
       <c r="X263" s="2"/>
       <c r="Y263" s="2"/>
     </row>
-    <row r="264" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="264" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B264" s="5"/>
       <c r="C264" s="5"/>
       <c r="D264" s="4"/>
@@ -12284,7 +12293,7 @@
       <c r="X264" s="2"/>
       <c r="Y264" s="2"/>
     </row>
-    <row r="265" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="265" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B265" s="5"/>
       <c r="C265" s="5"/>
       <c r="D265" s="4"/>
@@ -12310,7 +12319,7 @@
       <c r="X265" s="2"/>
       <c r="Y265" s="2"/>
     </row>
-    <row r="266" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="266" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B266" s="5"/>
       <c r="C266" s="5"/>
       <c r="D266" s="4"/>
@@ -12336,7 +12345,7 @@
       <c r="X266" s="2"/>
       <c r="Y266" s="2"/>
     </row>
-    <row r="267" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="267" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B267" s="5"/>
       <c r="C267" s="5"/>
       <c r="D267" s="4"/>
@@ -12362,7 +12371,7 @@
       <c r="X267" s="2"/>
       <c r="Y267" s="2"/>
     </row>
-    <row r="268" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="268" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B268" s="5"/>
       <c r="C268" s="5"/>
       <c r="D268" s="4"/>
@@ -12388,7 +12397,7 @@
       <c r="X268" s="2"/>
       <c r="Y268" s="2"/>
     </row>
-    <row r="269" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="269" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B269" s="5"/>
       <c r="C269" s="5"/>
       <c r="D269" s="4"/>
@@ -12414,7 +12423,7 @@
       <c r="X269" s="2"/>
       <c r="Y269" s="2"/>
     </row>
-    <row r="270" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="270" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B270" s="5"/>
       <c r="C270" s="5"/>
       <c r="D270" s="4"/>
@@ -12440,7 +12449,7 @@
       <c r="X270" s="2"/>
       <c r="Y270" s="2"/>
     </row>
-    <row r="271" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="271" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B271" s="5"/>
       <c r="C271" s="5"/>
       <c r="D271" s="4"/>
@@ -12466,7 +12475,7 @@
       <c r="X271" s="2"/>
       <c r="Y271" s="2"/>
     </row>
-    <row r="272" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="272" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B272" s="5"/>
       <c r="C272" s="5"/>
       <c r="D272" s="4"/>
@@ -12492,7 +12501,7 @@
       <c r="X272" s="2"/>
       <c r="Y272" s="2"/>
     </row>
-    <row r="273" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="273" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B273" s="5"/>
       <c r="C273" s="5"/>
       <c r="D273" s="4"/>
@@ -12518,7 +12527,7 @@
       <c r="X273" s="2"/>
       <c r="Y273" s="2"/>
     </row>
-    <row r="274" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="274" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B274" s="5"/>
       <c r="C274" s="5"/>
       <c r="D274" s="4"/>
@@ -12544,7 +12553,7 @@
       <c r="X274" s="2"/>
       <c r="Y274" s="2"/>
     </row>
-    <row r="275" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="275" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B275" s="5"/>
       <c r="C275" s="5"/>
       <c r="D275" s="4"/>
@@ -12570,7 +12579,7 @@
       <c r="X275" s="2"/>
       <c r="Y275" s="2"/>
     </row>
-    <row r="276" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="276" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B276" s="5"/>
       <c r="C276" s="5"/>
       <c r="D276" s="4"/>
@@ -12596,7 +12605,7 @@
       <c r="X276" s="2"/>
       <c r="Y276" s="2"/>
     </row>
-    <row r="277" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="277" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B277" s="5"/>
       <c r="C277" s="5"/>
       <c r="D277" s="4"/>
@@ -12622,7 +12631,7 @@
       <c r="X277" s="2"/>
       <c r="Y277" s="2"/>
     </row>
-    <row r="278" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="278" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B278" s="5"/>
       <c r="C278" s="5"/>
       <c r="D278" s="4"/>
@@ -12648,7 +12657,7 @@
       <c r="X278" s="2"/>
       <c r="Y278" s="2"/>
     </row>
-    <row r="279" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="279" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B279" s="5"/>
       <c r="C279" s="5"/>
       <c r="D279" s="4"/>
@@ -12674,7 +12683,7 @@
       <c r="X279" s="2"/>
       <c r="Y279" s="2"/>
     </row>
-    <row r="280" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="280" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B280" s="5"/>
       <c r="C280" s="5"/>
       <c r="D280" s="4"/>
@@ -12700,7 +12709,7 @@
       <c r="X280" s="2"/>
       <c r="Y280" s="2"/>
     </row>
-    <row r="281" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="281" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B281" s="5"/>
       <c r="C281" s="5"/>
       <c r="D281" s="4"/>
@@ -12726,7 +12735,7 @@
       <c r="X281" s="2"/>
       <c r="Y281" s="2"/>
     </row>
-    <row r="282" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="282" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B282" s="5"/>
       <c r="C282" s="5"/>
       <c r="D282" s="4"/>
@@ -12752,7 +12761,7 @@
       <c r="X282" s="2"/>
       <c r="Y282" s="2"/>
     </row>
-    <row r="283" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="283" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B283" s="5"/>
       <c r="C283" s="5"/>
       <c r="D283" s="4"/>
@@ -12778,7 +12787,7 @@
       <c r="X283" s="2"/>
       <c r="Y283" s="2"/>
     </row>
-    <row r="284" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="284" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B284" s="5"/>
       <c r="C284" s="5"/>
       <c r="D284" s="4"/>
@@ -12804,7 +12813,7 @@
       <c r="X284" s="2"/>
       <c r="Y284" s="2"/>
     </row>
-    <row r="285" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="285" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B285" s="5"/>
       <c r="C285" s="5"/>
       <c r="D285" s="4"/>
@@ -12830,7 +12839,7 @@
       <c r="X285" s="2"/>
       <c r="Y285" s="2"/>
     </row>
-    <row r="286" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="286" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B286" s="5"/>
       <c r="C286" s="5"/>
       <c r="D286" s="4"/>
@@ -12856,7 +12865,7 @@
       <c r="X286" s="2"/>
       <c r="Y286" s="2"/>
     </row>
-    <row r="287" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="287" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B287" s="5"/>
       <c r="C287" s="5"/>
       <c r="D287" s="4"/>
@@ -12882,7 +12891,7 @@
       <c r="X287" s="2"/>
       <c r="Y287" s="2"/>
     </row>
-    <row r="288" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="288" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B288" s="5"/>
       <c r="C288" s="5"/>
       <c r="D288" s="4"/>
@@ -12908,7 +12917,7 @@
       <c r="X288" s="2"/>
       <c r="Y288" s="2"/>
     </row>
-    <row r="289" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="289" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B289" s="5"/>
       <c r="C289" s="5"/>
       <c r="D289" s="4"/>
@@ -12934,7 +12943,7 @@
       <c r="X289" s="2"/>
       <c r="Y289" s="2"/>
     </row>
-    <row r="290" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="290" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B290" s="5"/>
       <c r="C290" s="5"/>
       <c r="D290" s="4"/>
@@ -12960,7 +12969,7 @@
       <c r="X290" s="2"/>
       <c r="Y290" s="2"/>
     </row>
-    <row r="291" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="291" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B291" s="5"/>
       <c r="C291" s="5"/>
       <c r="D291" s="4"/>
@@ -12986,7 +12995,7 @@
       <c r="X291" s="2"/>
       <c r="Y291" s="2"/>
     </row>
-    <row r="292" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="292" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B292" s="5"/>
       <c r="C292" s="5"/>
       <c r="D292" s="4"/>
@@ -13012,7 +13021,7 @@
       <c r="X292" s="2"/>
       <c r="Y292" s="2"/>
     </row>
-    <row r="293" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="293" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B293" s="5"/>
       <c r="C293" s="5"/>
       <c r="D293" s="4"/>
@@ -13038,7 +13047,7 @@
       <c r="X293" s="2"/>
       <c r="Y293" s="2"/>
     </row>
-    <row r="294" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="294" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B294" s="5"/>
       <c r="C294" s="5"/>
       <c r="D294" s="4"/>
@@ -13064,7 +13073,7 @@
       <c r="X294" s="2"/>
       <c r="Y294" s="2"/>
     </row>
-    <row r="295" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="295" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B295" s="5"/>
       <c r="C295" s="5"/>
       <c r="D295" s="4"/>
@@ -13090,7 +13099,7 @@
       <c r="X295" s="2"/>
       <c r="Y295" s="2"/>
     </row>
-    <row r="296" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="296" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B296" s="5"/>
       <c r="C296" s="5"/>
       <c r="D296" s="4"/>
@@ -13116,7 +13125,7 @@
       <c r="X296" s="2"/>
       <c r="Y296" s="2"/>
     </row>
-    <row r="297" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="297" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B297" s="5"/>
       <c r="C297" s="5"/>
       <c r="D297" s="4"/>
@@ -13142,7 +13151,7 @@
       <c r="X297" s="2"/>
       <c r="Y297" s="2"/>
     </row>
-    <row r="298" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="298" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B298" s="5"/>
       <c r="C298" s="5"/>
       <c r="D298" s="4"/>
@@ -13168,7 +13177,7 @@
       <c r="X298" s="2"/>
       <c r="Y298" s="2"/>
     </row>
-    <row r="299" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="299" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B299" s="5"/>
       <c r="C299" s="5"/>
       <c r="D299" s="4"/>
@@ -13194,7 +13203,7 @@
       <c r="X299" s="2"/>
       <c r="Y299" s="2"/>
     </row>
-    <row r="300" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="300" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B300" s="5"/>
       <c r="C300" s="5"/>
       <c r="D300" s="4"/>
@@ -13220,7 +13229,7 @@
       <c r="X300" s="2"/>
       <c r="Y300" s="2"/>
     </row>
-    <row r="301" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="301" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B301" s="5"/>
       <c r="C301" s="5"/>
       <c r="D301" s="4"/>
@@ -13246,7 +13255,7 @@
       <c r="X301" s="2"/>
       <c r="Y301" s="2"/>
     </row>
-    <row r="302" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="302" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B302" s="5"/>
       <c r="C302" s="5"/>
       <c r="D302" s="4"/>
@@ -13272,7 +13281,7 @@
       <c r="X302" s="2"/>
       <c r="Y302" s="2"/>
     </row>
-    <row r="303" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="303" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B303" s="5"/>
       <c r="C303" s="5"/>
       <c r="D303" s="4"/>
@@ -13298,7 +13307,7 @@
       <c r="X303" s="2"/>
       <c r="Y303" s="2"/>
     </row>
-    <row r="304" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="304" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B304" s="5"/>
       <c r="C304" s="5"/>
       <c r="D304" s="4"/>
@@ -13324,7 +13333,7 @@
       <c r="X304" s="2"/>
       <c r="Y304" s="2"/>
     </row>
-    <row r="305" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="305" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B305" s="5"/>
       <c r="C305" s="5"/>
       <c r="D305" s="4"/>
@@ -13350,7 +13359,7 @@
       <c r="X305" s="2"/>
       <c r="Y305" s="2"/>
     </row>
-    <row r="306" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="306" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B306" s="5"/>
       <c r="C306" s="5"/>
       <c r="D306" s="4"/>
@@ -13376,7 +13385,7 @@
       <c r="X306" s="2"/>
       <c r="Y306" s="2"/>
     </row>
-    <row r="307" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="307" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B307" s="5"/>
       <c r="C307" s="5"/>
       <c r="D307" s="4"/>
@@ -13402,7 +13411,7 @@
       <c r="X307" s="2"/>
       <c r="Y307" s="2"/>
     </row>
-    <row r="308" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="308" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B308" s="5"/>
       <c r="C308" s="5"/>
       <c r="D308" s="4"/>
@@ -13428,7 +13437,7 @@
       <c r="X308" s="2"/>
       <c r="Y308" s="2"/>
     </row>
-    <row r="309" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="309" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B309" s="5"/>
       <c r="C309" s="5"/>
       <c r="D309" s="4"/>
@@ -13454,7 +13463,7 @@
       <c r="X309" s="2"/>
       <c r="Y309" s="2"/>
     </row>
-    <row r="310" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="310" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B310" s="5"/>
       <c r="C310" s="5"/>
       <c r="D310" s="4"/>
@@ -13480,7 +13489,7 @@
       <c r="X310" s="2"/>
       <c r="Y310" s="2"/>
     </row>
-    <row r="311" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="311" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B311" s="5"/>
       <c r="C311" s="5"/>
       <c r="D311" s="4"/>
@@ -13506,7 +13515,7 @@
       <c r="X311" s="2"/>
       <c r="Y311" s="2"/>
     </row>
-    <row r="312" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="312" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B312" s="5"/>
       <c r="C312" s="5"/>
       <c r="D312" s="4"/>
@@ -13532,7 +13541,7 @@
       <c r="X312" s="2"/>
       <c r="Y312" s="2"/>
     </row>
-    <row r="313" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="313" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B313" s="5"/>
       <c r="C313" s="5"/>
       <c r="D313" s="4"/>
@@ -13558,7 +13567,7 @@
       <c r="X313" s="2"/>
       <c r="Y313" s="2"/>
     </row>
-    <row r="314" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="314" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B314" s="5"/>
       <c r="C314" s="5"/>
       <c r="D314" s="4"/>
@@ -13584,7 +13593,7 @@
       <c r="X314" s="2"/>
       <c r="Y314" s="2"/>
     </row>
-    <row r="315" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="315" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B315" s="5"/>
       <c r="C315" s="5"/>
       <c r="D315" s="4"/>
@@ -13610,7 +13619,7 @@
       <c r="X315" s="2"/>
       <c r="Y315" s="2"/>
     </row>
-    <row r="316" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="316" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B316" s="5"/>
       <c r="C316" s="5"/>
       <c r="D316" s="4"/>
@@ -13636,7 +13645,7 @@
       <c r="X316" s="2"/>
       <c r="Y316" s="2"/>
     </row>
-    <row r="317" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="317" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B317" s="5"/>
       <c r="C317" s="5"/>
       <c r="D317" s="4"/>
@@ -13662,7 +13671,7 @@
       <c r="X317" s="2"/>
       <c r="Y317" s="2"/>
     </row>
-    <row r="318" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="318" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B318" s="5"/>
       <c r="C318" s="5"/>
       <c r="D318" s="4"/>
@@ -13688,7 +13697,7 @@
       <c r="X318" s="2"/>
       <c r="Y318" s="2"/>
     </row>
-    <row r="319" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="319" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B319" s="5"/>
       <c r="C319" s="5"/>
       <c r="D319" s="4"/>
@@ -13714,7 +13723,7 @@
       <c r="X319" s="2"/>
       <c r="Y319" s="2"/>
     </row>
-    <row r="320" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="320" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B320" s="5"/>
       <c r="C320" s="5"/>
       <c r="D320" s="4"/>
@@ -13740,7 +13749,7 @@
       <c r="X320" s="2"/>
       <c r="Y320" s="2"/>
     </row>
-    <row r="321" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="321" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B321" s="5"/>
       <c r="C321" s="5"/>
       <c r="D321" s="4"/>
@@ -13766,7 +13775,7 @@
       <c r="X321" s="2"/>
       <c r="Y321" s="2"/>
     </row>
-    <row r="322" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="322" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B322" s="5"/>
       <c r="C322" s="5"/>
       <c r="D322" s="4"/>
@@ -13792,7 +13801,7 @@
       <c r="X322" s="2"/>
       <c r="Y322" s="2"/>
     </row>
-    <row r="323" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="323" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B323" s="5"/>
       <c r="C323" s="5"/>
       <c r="D323" s="4"/>
@@ -13818,7 +13827,7 @@
       <c r="X323" s="2"/>
       <c r="Y323" s="2"/>
     </row>
-    <row r="324" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="324" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B324" s="5"/>
       <c r="C324" s="5"/>
       <c r="D324" s="4"/>
@@ -13844,7 +13853,7 @@
       <c r="X324" s="2"/>
       <c r="Y324" s="2"/>
     </row>
-    <row r="325" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="325" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B325" s="5"/>
       <c r="C325" s="5"/>
       <c r="D325" s="4"/>
@@ -13870,7 +13879,7 @@
       <c r="X325" s="2"/>
       <c r="Y325" s="2"/>
     </row>
-    <row r="326" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="326" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B326" s="5"/>
       <c r="C326" s="5"/>
       <c r="D326" s="4"/>
@@ -13896,7 +13905,7 @@
       <c r="X326" s="2"/>
       <c r="Y326" s="2"/>
     </row>
-    <row r="327" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="327" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B327" s="5"/>
       <c r="C327" s="5"/>
       <c r="D327" s="4"/>
@@ -13922,7 +13931,7 @@
       <c r="X327" s="2"/>
       <c r="Y327" s="2"/>
     </row>
-    <row r="328" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="328" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B328" s="5"/>
       <c r="C328" s="5"/>
       <c r="D328" s="4"/>
@@ -13948,7 +13957,7 @@
       <c r="X328" s="2"/>
       <c r="Y328" s="2"/>
     </row>
-    <row r="329" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="329" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B329" s="5"/>
       <c r="C329" s="5"/>
       <c r="D329" s="4"/>
@@ -13974,7 +13983,7 @@
       <c r="X329" s="2"/>
       <c r="Y329" s="2"/>
     </row>
-    <row r="330" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="330" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B330" s="5"/>
       <c r="C330" s="5"/>
       <c r="D330" s="4"/>
@@ -14000,7 +14009,7 @@
       <c r="X330" s="2"/>
       <c r="Y330" s="2"/>
     </row>
-    <row r="331" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="331" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B331" s="5"/>
       <c r="C331" s="5"/>
       <c r="D331" s="4"/>
@@ -14026,7 +14035,7 @@
       <c r="X331" s="2"/>
       <c r="Y331" s="2"/>
     </row>
-    <row r="332" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="332" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B332" s="5"/>
       <c r="C332" s="5"/>
       <c r="D332" s="4"/>
@@ -14052,7 +14061,7 @@
       <c r="X332" s="2"/>
       <c r="Y332" s="2"/>
     </row>
-    <row r="333" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="333" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B333" s="5"/>
       <c r="C333" s="5"/>
       <c r="D333" s="4"/>
@@ -14078,7 +14087,7 @@
       <c r="X333" s="2"/>
       <c r="Y333" s="2"/>
     </row>
-    <row r="334" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="334" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B334" s="5"/>
       <c r="C334" s="5"/>
       <c r="D334" s="4"/>
@@ -14104,7 +14113,7 @@
       <c r="X334" s="2"/>
       <c r="Y334" s="2"/>
     </row>
-    <row r="335" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="335" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B335" s="5"/>
       <c r="C335" s="5"/>
       <c r="D335" s="4"/>
@@ -14130,7 +14139,7 @@
       <c r="X335" s="2"/>
       <c r="Y335" s="2"/>
     </row>
-    <row r="336" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="336" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B336" s="5"/>
       <c r="C336" s="5"/>
       <c r="D336" s="4"/>
@@ -14156,7 +14165,7 @@
       <c r="X336" s="2"/>
       <c r="Y336" s="2"/>
     </row>
-    <row r="337" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="337" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B337" s="5"/>
       <c r="C337" s="5"/>
       <c r="D337" s="4"/>
@@ -14182,7 +14191,7 @@
       <c r="X337" s="2"/>
       <c r="Y337" s="2"/>
     </row>
-    <row r="338" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="338" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B338" s="5"/>
       <c r="C338" s="5"/>
       <c r="D338" s="4"/>
@@ -14208,7 +14217,7 @@
       <c r="X338" s="2"/>
       <c r="Y338" s="2"/>
     </row>
-    <row r="339" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="339" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B339" s="5"/>
       <c r="C339" s="5"/>
       <c r="D339" s="4"/>
@@ -14234,7 +14243,7 @@
       <c r="X339" s="2"/>
       <c r="Y339" s="2"/>
     </row>
-    <row r="340" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="340" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B340" s="5"/>
       <c r="C340" s="5"/>
       <c r="D340" s="4"/>
@@ -14260,7 +14269,7 @@
       <c r="X340" s="2"/>
       <c r="Y340" s="2"/>
     </row>
-    <row r="341" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="341" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B341" s="5"/>
       <c r="C341" s="5"/>
       <c r="D341" s="4"/>
@@ -14286,7 +14295,7 @@
       <c r="X341" s="2"/>
       <c r="Y341" s="2"/>
     </row>
-    <row r="342" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="342" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B342" s="5"/>
       <c r="C342" s="5"/>
       <c r="D342" s="4"/>
@@ -14312,7 +14321,7 @@
       <c r="X342" s="2"/>
       <c r="Y342" s="2"/>
     </row>
-    <row r="343" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="343" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B343" s="5"/>
       <c r="C343" s="5"/>
       <c r="D343" s="4"/>
@@ -14338,7 +14347,7 @@
       <c r="X343" s="2"/>
       <c r="Y343" s="2"/>
     </row>
-    <row r="344" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="344" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B344" s="5"/>
       <c r="C344" s="5"/>
       <c r="D344" s="4"/>
@@ -14364,7 +14373,7 @@
       <c r="X344" s="2"/>
       <c r="Y344" s="2"/>
     </row>
-    <row r="345" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="345" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B345" s="5"/>
       <c r="C345" s="5"/>
       <c r="D345" s="4"/>
@@ -14390,7 +14399,7 @@
       <c r="X345" s="2"/>
       <c r="Y345" s="2"/>
     </row>
-    <row r="346" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="346" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B346" s="5"/>
       <c r="C346" s="5"/>
       <c r="D346" s="4"/>
@@ -14416,7 +14425,7 @@
       <c r="X346" s="2"/>
       <c r="Y346" s="2"/>
     </row>
-    <row r="347" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="347" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B347" s="5"/>
       <c r="C347" s="5"/>
       <c r="D347" s="4"/>
@@ -14442,7 +14451,7 @@
       <c r="X347" s="2"/>
       <c r="Y347" s="2"/>
     </row>
-    <row r="348" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="348" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B348" s="5"/>
       <c r="C348" s="5"/>
       <c r="D348" s="4"/>
@@ -14468,7 +14477,7 @@
       <c r="X348" s="2"/>
       <c r="Y348" s="2"/>
     </row>
-    <row r="349" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="349" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B349" s="5"/>
       <c r="C349" s="5"/>
       <c r="D349" s="4"/>
@@ -14494,7 +14503,7 @@
       <c r="X349" s="2"/>
       <c r="Y349" s="2"/>
     </row>
-    <row r="350" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="350" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B350" s="5"/>
       <c r="C350" s="5"/>
       <c r="D350" s="4"/>
@@ -14520,7 +14529,7 @@
       <c r="X350" s="2"/>
       <c r="Y350" s="2"/>
     </row>
-    <row r="351" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="351" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B351" s="5"/>
       <c r="C351" s="5"/>
       <c r="D351" s="4"/>
@@ -14546,7 +14555,7 @@
       <c r="X351" s="2"/>
       <c r="Y351" s="2"/>
     </row>
-    <row r="352" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="352" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B352" s="5"/>
       <c r="C352" s="5"/>
       <c r="D352" s="4"/>
@@ -14572,7 +14581,7 @@
       <c r="X352" s="2"/>
       <c r="Y352" s="2"/>
     </row>
-    <row r="353" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="353" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B353" s="5"/>
       <c r="C353" s="5"/>
       <c r="D353" s="4"/>
@@ -14598,7 +14607,7 @@
       <c r="X353" s="2"/>
       <c r="Y353" s="2"/>
     </row>
-    <row r="354" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="354" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B354" s="5"/>
       <c r="C354" s="5"/>
       <c r="D354" s="4"/>
@@ -14624,7 +14633,7 @@
       <c r="X354" s="2"/>
       <c r="Y354" s="2"/>
     </row>
-    <row r="355" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="355" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B355" s="5"/>
       <c r="C355" s="5"/>
       <c r="D355" s="4"/>
@@ -14650,7 +14659,7 @@
       <c r="X355" s="2"/>
       <c r="Y355" s="2"/>
     </row>
-    <row r="356" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="356" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B356" s="5"/>
       <c r="C356" s="5"/>
       <c r="D356" s="4"/>
@@ -14676,7 +14685,7 @@
       <c r="X356" s="2"/>
       <c r="Y356" s="2"/>
     </row>
-    <row r="357" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="357" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B357" s="5"/>
       <c r="C357" s="5"/>
       <c r="D357" s="4"/>
@@ -14702,7 +14711,7 @@
       <c r="X357" s="2"/>
       <c r="Y357" s="2"/>
     </row>
-    <row r="358" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="358" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B358" s="5"/>
       <c r="C358" s="5"/>
       <c r="D358" s="4"/>
@@ -14728,7 +14737,7 @@
       <c r="X358" s="2"/>
       <c r="Y358" s="2"/>
     </row>
-    <row r="359" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="359" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B359" s="5"/>
       <c r="C359" s="5"/>
       <c r="D359" s="4"/>
@@ -14754,7 +14763,7 @@
       <c r="X359" s="2"/>
       <c r="Y359" s="2"/>
     </row>
-    <row r="360" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="360" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B360" s="5"/>
       <c r="C360" s="5"/>
       <c r="D360" s="4"/>
@@ -14780,7 +14789,7 @@
       <c r="X360" s="2"/>
       <c r="Y360" s="2"/>
     </row>
-    <row r="361" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="361" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B361" s="5"/>
       <c r="C361" s="5"/>
       <c r="D361" s="4"/>
@@ -14806,7 +14815,7 @@
       <c r="X361" s="2"/>
       <c r="Y361" s="2"/>
     </row>
-    <row r="362" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="362" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B362" s="5"/>
       <c r="C362" s="5"/>
       <c r="D362" s="4"/>
@@ -14832,7 +14841,7 @@
       <c r="X362" s="2"/>
       <c r="Y362" s="2"/>
     </row>
-    <row r="363" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="363" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B363" s="5"/>
       <c r="C363" s="5"/>
       <c r="D363" s="4"/>
@@ -14858,7 +14867,7 @@
       <c r="X363" s="2"/>
       <c r="Y363" s="2"/>
     </row>
-    <row r="364" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="364" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B364" s="5"/>
       <c r="C364" s="5"/>
       <c r="D364" s="4"/>
@@ -14884,7 +14893,7 @@
       <c r="X364" s="2"/>
       <c r="Y364" s="2"/>
     </row>
-    <row r="365" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="365" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B365" s="5"/>
       <c r="C365" s="5"/>
       <c r="D365" s="4"/>
@@ -14910,7 +14919,7 @@
       <c r="X365" s="2"/>
       <c r="Y365" s="2"/>
     </row>
-    <row r="366" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="366" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B366" s="5"/>
       <c r="C366" s="5"/>
       <c r="D366" s="4"/>
@@ -14936,7 +14945,7 @@
       <c r="X366" s="2"/>
       <c r="Y366" s="2"/>
     </row>
-    <row r="367" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="367" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B367" s="5"/>
       <c r="C367" s="5"/>
       <c r="D367" s="4"/>
@@ -14962,7 +14971,7 @@
       <c r="X367" s="2"/>
       <c r="Y367" s="2"/>
     </row>
-    <row r="368" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="368" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B368" s="5"/>
       <c r="C368" s="5"/>
       <c r="D368" s="4"/>
@@ -14988,7 +14997,7 @@
       <c r="X368" s="2"/>
       <c r="Y368" s="2"/>
     </row>
-    <row r="369" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="369" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B369" s="5"/>
       <c r="C369" s="5"/>
       <c r="D369" s="4"/>
@@ -15014,7 +15023,7 @@
       <c r="X369" s="2"/>
       <c r="Y369" s="2"/>
     </row>
-    <row r="370" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="370" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B370" s="5"/>
       <c r="C370" s="5"/>
       <c r="D370" s="4"/>
@@ -15040,7 +15049,7 @@
       <c r="X370" s="2"/>
       <c r="Y370" s="2"/>
     </row>
-    <row r="371" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="371" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B371" s="5"/>
       <c r="C371" s="5"/>
       <c r="D371" s="4"/>
@@ -15066,7 +15075,7 @@
       <c r="X371" s="2"/>
       <c r="Y371" s="2"/>
     </row>
-    <row r="372" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="372" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B372" s="5"/>
       <c r="C372" s="5"/>
       <c r="D372" s="4"/>
@@ -15092,7 +15101,7 @@
       <c r="X372" s="2"/>
       <c r="Y372" s="2"/>
     </row>
-    <row r="373" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="373" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B373" s="5"/>
       <c r="C373" s="5"/>
       <c r="D373" s="4"/>
@@ -15118,7 +15127,7 @@
       <c r="X373" s="2"/>
       <c r="Y373" s="2"/>
     </row>
-    <row r="374" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="374" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B374" s="5"/>
       <c r="C374" s="5"/>
       <c r="D374" s="4"/>
@@ -15144,7 +15153,7 @@
       <c r="X374" s="2"/>
       <c r="Y374" s="2"/>
     </row>
-    <row r="375" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="375" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B375" s="5"/>
       <c r="C375" s="5"/>
       <c r="D375" s="4"/>
@@ -15170,7 +15179,7 @@
       <c r="X375" s="2"/>
       <c r="Y375" s="2"/>
     </row>
-    <row r="376" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="376" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B376" s="5"/>
       <c r="C376" s="5"/>
       <c r="D376" s="4"/>
@@ -15196,7 +15205,7 @@
       <c r="X376" s="2"/>
       <c r="Y376" s="2"/>
     </row>
-    <row r="377" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="377" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B377" s="5"/>
       <c r="C377" s="5"/>
       <c r="D377" s="4"/>
@@ -15222,7 +15231,7 @@
       <c r="X377" s="2"/>
       <c r="Y377" s="2"/>
     </row>
-    <row r="378" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="378" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B378" s="5"/>
       <c r="C378" s="5"/>
       <c r="D378" s="4"/>
@@ -15248,7 +15257,7 @@
       <c r="X378" s="2"/>
       <c r="Y378" s="2"/>
     </row>
-    <row r="379" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="379" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B379" s="5"/>
       <c r="C379" s="5"/>
       <c r="D379" s="4"/>
@@ -15274,7 +15283,7 @@
       <c r="X379" s="2"/>
       <c r="Y379" s="2"/>
     </row>
-    <row r="380" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="380" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B380" s="5"/>
       <c r="C380" s="5"/>
       <c r="D380" s="4"/>
@@ -15300,7 +15309,7 @@
       <c r="X380" s="2"/>
       <c r="Y380" s="2"/>
     </row>
-    <row r="381" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="381" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B381" s="5"/>
       <c r="C381" s="5"/>
       <c r="D381" s="4"/>
@@ -15326,7 +15335,7 @@
       <c r="X381" s="2"/>
       <c r="Y381" s="2"/>
     </row>
-    <row r="382" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="382" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B382" s="5"/>
       <c r="C382" s="5"/>
       <c r="D382" s="4"/>
@@ -15352,7 +15361,7 @@
       <c r="X382" s="2"/>
       <c r="Y382" s="2"/>
     </row>
-    <row r="383" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="383" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B383" s="5"/>
       <c r="C383" s="5"/>
       <c r="D383" s="4"/>
@@ -15378,7 +15387,7 @@
       <c r="X383" s="2"/>
       <c r="Y383" s="2"/>
     </row>
-    <row r="384" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="384" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B384" s="5"/>
       <c r="C384" s="5"/>
       <c r="D384" s="4"/>
@@ -15404,7 +15413,7 @@
       <c r="X384" s="2"/>
       <c r="Y384" s="2"/>
     </row>
-    <row r="385" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="385" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B385" s="5"/>
       <c r="C385" s="5"/>
       <c r="D385" s="4"/>
@@ -15430,7 +15439,7 @@
       <c r="X385" s="2"/>
       <c r="Y385" s="2"/>
     </row>
-    <row r="386" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="386" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B386" s="5"/>
       <c r="C386" s="5"/>
       <c r="D386" s="4"/>
@@ -15456,7 +15465,7 @@
       <c r="X386" s="2"/>
       <c r="Y386" s="2"/>
     </row>
-    <row r="387" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="387" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B387" s="5"/>
       <c r="C387" s="5"/>
       <c r="D387" s="4"/>
@@ -15482,7 +15491,7 @@
       <c r="X387" s="2"/>
       <c r="Y387" s="2"/>
     </row>
-    <row r="388" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="388" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B388" s="5"/>
       <c r="C388" s="5"/>
       <c r="D388" s="4"/>
@@ -15508,7 +15517,7 @@
       <c r="X388" s="2"/>
       <c r="Y388" s="2"/>
     </row>
-    <row r="389" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="389" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B389" s="5"/>
       <c r="C389" s="5"/>
       <c r="D389" s="4"/>
@@ -15534,7 +15543,7 @@
       <c r="X389" s="2"/>
       <c r="Y389" s="2"/>
     </row>
-    <row r="390" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="390" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B390" s="5"/>
       <c r="C390" s="5"/>
       <c r="D390" s="4"/>
@@ -15560,7 +15569,7 @@
       <c r="X390" s="2"/>
       <c r="Y390" s="2"/>
     </row>
-    <row r="391" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="391" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B391" s="5"/>
       <c r="C391" s="5"/>
       <c r="D391" s="4"/>
@@ -15586,7 +15595,7 @@
       <c r="X391" s="2"/>
       <c r="Y391" s="2"/>
     </row>
-    <row r="392" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="392" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B392" s="5"/>
       <c r="C392" s="5"/>
       <c r="D392" s="4"/>
@@ -15612,7 +15621,7 @@
       <c r="X392" s="2"/>
       <c r="Y392" s="2"/>
     </row>
-    <row r="393" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="393" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B393" s="5"/>
       <c r="C393" s="5"/>
       <c r="D393" s="4"/>
@@ -15638,7 +15647,7 @@
       <c r="X393" s="2"/>
       <c r="Y393" s="2"/>
     </row>
-    <row r="394" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="394" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B394" s="5"/>
       <c r="C394" s="5"/>
       <c r="D394" s="4"/>
@@ -15664,7 +15673,7 @@
       <c r="X394" s="2"/>
       <c r="Y394" s="2"/>
     </row>
-    <row r="395" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="395" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B395" s="5"/>
       <c r="C395" s="5"/>
       <c r="D395" s="4"/>
@@ -15690,7 +15699,7 @@
       <c r="X395" s="2"/>
       <c r="Y395" s="2"/>
     </row>
-    <row r="396" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="396" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B396" s="5"/>
       <c r="C396" s="5"/>
       <c r="D396" s="4"/>
@@ -15716,7 +15725,7 @@
       <c r="X396" s="2"/>
       <c r="Y396" s="2"/>
     </row>
-    <row r="397" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="397" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B397" s="5"/>
       <c r="C397" s="5"/>
       <c r="D397" s="4"/>
@@ -15742,7 +15751,7 @@
       <c r="X397" s="2"/>
       <c r="Y397" s="2"/>
     </row>
-    <row r="398" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="398" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B398" s="5"/>
       <c r="C398" s="5"/>
       <c r="D398" s="4"/>
@@ -15768,7 +15777,7 @@
       <c r="X398" s="2"/>
       <c r="Y398" s="2"/>
     </row>
-    <row r="399" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="399" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B399" s="5"/>
       <c r="C399" s="5"/>
       <c r="D399" s="4"/>
@@ -15794,7 +15803,7 @@
       <c r="X399" s="2"/>
       <c r="Y399" s="2"/>
     </row>
-    <row r="400" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="400" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B400" s="5"/>
       <c r="C400" s="5"/>
       <c r="D400" s="4"/>
@@ -15820,7 +15829,7 @@
       <c r="X400" s="2"/>
       <c r="Y400" s="2"/>
     </row>
-    <row r="401" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="401" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B401" s="5"/>
       <c r="C401" s="5"/>
       <c r="D401" s="4"/>
@@ -15846,7 +15855,7 @@
       <c r="X401" s="2"/>
       <c r="Y401" s="2"/>
     </row>
-    <row r="402" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="402" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B402" s="5"/>
       <c r="C402" s="5"/>
       <c r="D402" s="4"/>
@@ -15872,7 +15881,7 @@
       <c r="X402" s="2"/>
       <c r="Y402" s="2"/>
     </row>
-    <row r="403" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="403" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B403" s="5"/>
       <c r="C403" s="5"/>
       <c r="D403" s="4"/>
@@ -15898,7 +15907,7 @@
       <c r="X403" s="2"/>
       <c r="Y403" s="2"/>
     </row>
-    <row r="404" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="404" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B404" s="5"/>
       <c r="C404" s="5"/>
       <c r="D404" s="4"/>
@@ -15924,7 +15933,7 @@
       <c r="X404" s="2"/>
       <c r="Y404" s="2"/>
     </row>
-    <row r="405" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="405" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B405" s="5"/>
       <c r="C405" s="5"/>
       <c r="D405" s="4"/>
@@ -15950,7 +15959,7 @@
       <c r="X405" s="2"/>
       <c r="Y405" s="2"/>
     </row>
-    <row r="406" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="406" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B406" s="5"/>
       <c r="C406" s="5"/>
       <c r="D406" s="4"/>
@@ -15976,7 +15985,7 @@
       <c r="X406" s="2"/>
       <c r="Y406" s="2"/>
     </row>
-    <row r="407" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="407" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B407" s="5"/>
       <c r="C407" s="5"/>
       <c r="D407" s="4"/>
@@ -16002,7 +16011,7 @@
       <c r="X407" s="2"/>
       <c r="Y407" s="2"/>
     </row>
-    <row r="408" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="408" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B408" s="5"/>
       <c r="C408" s="5"/>
       <c r="D408" s="4"/>
@@ -16028,7 +16037,7 @@
       <c r="X408" s="2"/>
       <c r="Y408" s="2"/>
     </row>
-    <row r="409" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="409" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B409" s="5"/>
       <c r="C409" s="5"/>
       <c r="D409" s="4"/>
@@ -16054,7 +16063,7 @@
       <c r="X409" s="2"/>
       <c r="Y409" s="2"/>
     </row>
-    <row r="410" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="410" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B410" s="5"/>
       <c r="C410" s="5"/>
       <c r="D410" s="4"/>
@@ -16080,7 +16089,7 @@
       <c r="X410" s="2"/>
       <c r="Y410" s="2"/>
     </row>
-    <row r="411" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="411" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B411" s="5"/>
       <c r="C411" s="5"/>
       <c r="D411" s="4"/>
@@ -16106,7 +16115,7 @@
       <c r="X411" s="2"/>
       <c r="Y411" s="2"/>
     </row>
-    <row r="412" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="412" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B412" s="5"/>
       <c r="C412" s="5"/>
       <c r="D412" s="4"/>
@@ -16132,7 +16141,7 @@
       <c r="X412" s="2"/>
       <c r="Y412" s="2"/>
     </row>
-    <row r="413" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="413" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B413" s="5"/>
       <c r="C413" s="5"/>
       <c r="D413" s="4"/>
@@ -16158,7 +16167,7 @@
       <c r="X413" s="2"/>
       <c r="Y413" s="2"/>
     </row>
-    <row r="414" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="414" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B414" s="5"/>
       <c r="C414" s="5"/>
       <c r="D414" s="4"/>
@@ -16184,7 +16193,7 @@
       <c r="X414" s="2"/>
       <c r="Y414" s="2"/>
     </row>
-    <row r="415" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="415" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B415" s="5"/>
       <c r="C415" s="5"/>
       <c r="D415" s="4"/>
@@ -16210,7 +16219,7 @@
       <c r="X415" s="2"/>
       <c r="Y415" s="2"/>
     </row>
-    <row r="416" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="416" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B416" s="5"/>
       <c r="C416" s="5"/>
       <c r="D416" s="4"/>
@@ -16236,7 +16245,7 @@
       <c r="X416" s="2"/>
       <c r="Y416" s="2"/>
     </row>
-    <row r="417" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="417" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B417" s="5"/>
       <c r="C417" s="5"/>
       <c r="D417" s="4"/>
@@ -16262,7 +16271,7 @@
       <c r="X417" s="2"/>
       <c r="Y417" s="2"/>
     </row>
-    <row r="418" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="418" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B418" s="5"/>
       <c r="C418" s="5"/>
       <c r="D418" s="4"/>
@@ -16288,7 +16297,7 @@
       <c r="X418" s="2"/>
       <c r="Y418" s="2"/>
     </row>
-    <row r="419" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="419" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B419" s="5"/>
       <c r="C419" s="5"/>
       <c r="D419" s="4"/>
@@ -16314,7 +16323,7 @@
       <c r="X419" s="2"/>
       <c r="Y419" s="2"/>
     </row>
-    <row r="420" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="420" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B420" s="5"/>
       <c r="C420" s="5"/>
       <c r="D420" s="4"/>
@@ -16340,7 +16349,7 @@
       <c r="X420" s="2"/>
       <c r="Y420" s="2"/>
     </row>
-    <row r="421" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="421" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B421" s="5"/>
       <c r="C421" s="5"/>
       <c r="D421" s="4"/>
@@ -16366,7 +16375,7 @@
       <c r="X421" s="2"/>
       <c r="Y421" s="2"/>
     </row>
-    <row r="422" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="422" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B422" s="5"/>
       <c r="C422" s="5"/>
       <c r="D422" s="4"/>
@@ -16392,7 +16401,7 @@
       <c r="X422" s="2"/>
       <c r="Y422" s="2"/>
     </row>
-    <row r="423" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="423" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B423" s="5"/>
       <c r="C423" s="5"/>
       <c r="D423" s="4"/>
@@ -16418,7 +16427,7 @@
       <c r="X423" s="2"/>
       <c r="Y423" s="2"/>
     </row>
-    <row r="424" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="424" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B424" s="5"/>
       <c r="C424" s="5"/>
       <c r="D424" s="4"/>
@@ -16444,7 +16453,7 @@
       <c r="X424" s="2"/>
       <c r="Y424" s="2"/>
     </row>
-    <row r="425" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="425" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B425" s="5"/>
       <c r="C425" s="5"/>
       <c r="D425" s="4"/>
@@ -16470,7 +16479,7 @@
       <c r="X425" s="2"/>
       <c r="Y425" s="2"/>
     </row>
-    <row r="426" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="426" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B426" s="5"/>
       <c r="C426" s="5"/>
       <c r="D426" s="4"/>
@@ -16496,7 +16505,7 @@
       <c r="X426" s="2"/>
       <c r="Y426" s="2"/>
     </row>
-    <row r="427" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="427" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B427" s="5"/>
       <c r="C427" s="5"/>
       <c r="D427" s="4"/>
@@ -16522,7 +16531,7 @@
       <c r="X427" s="2"/>
       <c r="Y427" s="2"/>
     </row>
-    <row r="428" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="428" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B428" s="5"/>
       <c r="C428" s="5"/>
       <c r="D428" s="4"/>
@@ -16548,7 +16557,7 @@
       <c r="X428" s="2"/>
       <c r="Y428" s="2"/>
     </row>
-    <row r="429" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="429" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B429" s="5"/>
       <c r="C429" s="5"/>
       <c r="D429" s="4"/>
@@ -16574,7 +16583,7 @@
       <c r="X429" s="2"/>
       <c r="Y429" s="2"/>
     </row>
-    <row r="430" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="430" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B430" s="5"/>
       <c r="C430" s="5"/>
       <c r="D430" s="4"/>
@@ -16600,7 +16609,7 @@
       <c r="X430" s="2"/>
       <c r="Y430" s="2"/>
     </row>
-    <row r="431" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="431" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B431" s="5"/>
       <c r="C431" s="5"/>
       <c r="D431" s="4"/>
@@ -16626,7 +16635,7 @@
       <c r="X431" s="2"/>
       <c r="Y431" s="2"/>
     </row>
-    <row r="432" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="432" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B432" s="5"/>
       <c r="C432" s="5"/>
       <c r="D432" s="4"/>
@@ -16652,7 +16661,7 @@
       <c r="X432" s="2"/>
       <c r="Y432" s="2"/>
     </row>
-    <row r="433" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="433" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B433" s="5"/>
       <c r="C433" s="5"/>
       <c r="D433" s="4"/>
@@ -16678,7 +16687,7 @@
       <c r="X433" s="2"/>
       <c r="Y433" s="2"/>
     </row>
-    <row r="434" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="434" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B434" s="5"/>
       <c r="C434" s="5"/>
       <c r="D434" s="4"/>
@@ -16704,7 +16713,7 @@
       <c r="X434" s="2"/>
       <c r="Y434" s="2"/>
     </row>
-    <row r="435" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="435" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B435" s="5"/>
       <c r="C435" s="5"/>
       <c r="D435" s="4"/>
@@ -16730,7 +16739,7 @@
       <c r="X435" s="2"/>
       <c r="Y435" s="2"/>
     </row>
-    <row r="436" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="436" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B436" s="5"/>
       <c r="C436" s="5"/>
       <c r="D436" s="4"/>
@@ -16756,7 +16765,7 @@
       <c r="X436" s="2"/>
       <c r="Y436" s="2"/>
     </row>
-    <row r="437" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="437" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B437" s="5"/>
       <c r="C437" s="5"/>
       <c r="D437" s="4"/>
@@ -16782,7 +16791,7 @@
       <c r="X437" s="2"/>
       <c r="Y437" s="2"/>
     </row>
-    <row r="438" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="438" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B438" s="5"/>
       <c r="C438" s="5"/>
       <c r="D438" s="4"/>
@@ -16808,7 +16817,7 @@
       <c r="X438" s="2"/>
       <c r="Y438" s="2"/>
     </row>
-    <row r="439" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="439" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B439" s="5"/>
       <c r="C439" s="5"/>
       <c r="D439" s="4"/>
@@ -16834,7 +16843,7 @@
       <c r="X439" s="2"/>
       <c r="Y439" s="2"/>
     </row>
-    <row r="440" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="440" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B440" s="5"/>
       <c r="C440" s="5"/>
       <c r="D440" s="4"/>
@@ -16860,7 +16869,7 @@
       <c r="X440" s="2"/>
       <c r="Y440" s="2"/>
     </row>
-    <row r="441" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="441" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B441" s="5"/>
       <c r="C441" s="5"/>
       <c r="D441" s="4"/>
@@ -16886,7 +16895,7 @@
       <c r="X441" s="2"/>
       <c r="Y441" s="2"/>
     </row>
-    <row r="442" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="442" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B442" s="5"/>
       <c r="C442" s="5"/>
       <c r="D442" s="4"/>
@@ -16912,7 +16921,7 @@
       <c r="X442" s="2"/>
       <c r="Y442" s="2"/>
     </row>
-    <row r="443" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="443" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B443" s="5"/>
       <c r="C443" s="5"/>
       <c r="D443" s="4"/>
@@ -16938,7 +16947,7 @@
       <c r="X443" s="2"/>
       <c r="Y443" s="2"/>
     </row>
-    <row r="444" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="444" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B444" s="5"/>
       <c r="C444" s="5"/>
       <c r="D444" s="4"/>
@@ -16964,7 +16973,7 @@
       <c r="X444" s="2"/>
       <c r="Y444" s="2"/>
     </row>
-    <row r="445" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="445" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B445" s="5"/>
       <c r="C445" s="5"/>
       <c r="D445" s="4"/>
@@ -16990,7 +16999,7 @@
       <c r="X445" s="2"/>
       <c r="Y445" s="2"/>
     </row>
-    <row r="446" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="446" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B446" s="5"/>
       <c r="C446" s="5"/>
       <c r="D446" s="4"/>
@@ -17016,7 +17025,7 @@
       <c r="X446" s="2"/>
       <c r="Y446" s="2"/>
     </row>
-    <row r="447" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="447" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B447" s="5"/>
       <c r="C447" s="5"/>
       <c r="D447" s="4"/>
@@ -17042,7 +17051,7 @@
       <c r="X447" s="2"/>
       <c r="Y447" s="2"/>
     </row>
-    <row r="448" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="448" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B448" s="5"/>
       <c r="C448" s="5"/>
       <c r="D448" s="4"/>
@@ -17068,7 +17077,7 @@
       <c r="X448" s="2"/>
       <c r="Y448" s="2"/>
     </row>
-    <row r="449" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="449" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B449" s="5"/>
       <c r="C449" s="5"/>
       <c r="D449" s="4"/>
@@ -17094,7 +17103,7 @@
       <c r="X449" s="2"/>
       <c r="Y449" s="2"/>
     </row>
-    <row r="450" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="450" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B450" s="5"/>
       <c r="C450" s="5"/>
       <c r="D450" s="4"/>
@@ -17120,7 +17129,7 @@
       <c r="X450" s="2"/>
       <c r="Y450" s="2"/>
     </row>
-    <row r="451" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="451" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B451" s="5"/>
       <c r="C451" s="5"/>
       <c r="D451" s="4"/>
@@ -17146,7 +17155,7 @@
       <c r="X451" s="2"/>
       <c r="Y451" s="2"/>
     </row>
-    <row r="452" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="452" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B452" s="5"/>
       <c r="C452" s="5"/>
       <c r="D452" s="4"/>
@@ -17172,7 +17181,7 @@
       <c r="X452" s="2"/>
       <c r="Y452" s="2"/>
     </row>
-    <row r="453" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="453" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B453" s="5"/>
       <c r="C453" s="5"/>
       <c r="D453" s="4"/>
@@ -17198,7 +17207,7 @@
       <c r="X453" s="2"/>
       <c r="Y453" s="2"/>
     </row>
-    <row r="454" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="454" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B454" s="5"/>
       <c r="C454" s="5"/>
       <c r="D454" s="4"/>
@@ -17224,7 +17233,7 @@
       <c r="X454" s="2"/>
       <c r="Y454" s="2"/>
     </row>
-    <row r="455" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="455" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B455" s="5"/>
       <c r="C455" s="5"/>
       <c r="D455" s="4"/>
@@ -17250,7 +17259,7 @@
       <c r="X455" s="2"/>
       <c r="Y455" s="2"/>
     </row>
-    <row r="456" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="456" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B456" s="5"/>
       <c r="C456" s="5"/>
       <c r="D456" s="4"/>
@@ -17276,7 +17285,7 @@
       <c r="X456" s="2"/>
       <c r="Y456" s="2"/>
     </row>
-    <row r="457" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="457" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B457" s="5"/>
       <c r="C457" s="5"/>
       <c r="D457" s="4"/>
@@ -17302,7 +17311,7 @@
       <c r="X457" s="2"/>
       <c r="Y457" s="2"/>
     </row>
-    <row r="458" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="458" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B458" s="5"/>
       <c r="C458" s="5"/>
       <c r="D458" s="4"/>
@@ -17328,7 +17337,7 @@
       <c r="X458" s="2"/>
       <c r="Y458" s="2"/>
     </row>
-    <row r="459" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="459" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B459" s="5"/>
       <c r="C459" s="5"/>
       <c r="D459" s="4"/>
@@ -17354,7 +17363,7 @@
       <c r="X459" s="2"/>
       <c r="Y459" s="2"/>
     </row>
-    <row r="460" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="460" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B460" s="5"/>
       <c r="C460" s="5"/>
       <c r="D460" s="4"/>
@@ -17380,7 +17389,7 @@
       <c r="X460" s="2"/>
       <c r="Y460" s="2"/>
     </row>
-    <row r="461" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="461" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B461" s="5"/>
       <c r="C461" s="5"/>
       <c r="D461" s="4"/>
@@ -17406,7 +17415,7 @@
       <c r="X461" s="2"/>
       <c r="Y461" s="2"/>
     </row>
-    <row r="462" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="462" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B462" s="5"/>
       <c r="C462" s="5"/>
       <c r="D462" s="4"/>
@@ -17432,7 +17441,7 @@
       <c r="X462" s="2"/>
       <c r="Y462" s="2"/>
     </row>
-    <row r="463" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="463" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B463" s="5"/>
       <c r="C463" s="5"/>
       <c r="D463" s="4"/>
@@ -17458,7 +17467,7 @@
       <c r="X463" s="2"/>
       <c r="Y463" s="2"/>
     </row>
-    <row r="464" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="464" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B464" s="5"/>
       <c r="C464" s="5"/>
       <c r="D464" s="4"/>
@@ -17484,7 +17493,7 @@
       <c r="X464" s="2"/>
       <c r="Y464" s="2"/>
     </row>
-    <row r="465" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="465" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B465" s="5"/>
       <c r="C465" s="5"/>
       <c r="D465" s="4"/>
@@ -17510,7 +17519,7 @@
       <c r="X465" s="2"/>
       <c r="Y465" s="2"/>
     </row>
-    <row r="466" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="466" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B466" s="5"/>
       <c r="C466" s="5"/>
       <c r="D466" s="4"/>
@@ -17536,7 +17545,7 @@
       <c r="X466" s="2"/>
       <c r="Y466" s="2"/>
     </row>
-    <row r="467" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="467" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B467" s="5"/>
       <c r="C467" s="5"/>
       <c r="D467" s="4"/>
@@ -17562,7 +17571,7 @@
       <c r="X467" s="2"/>
       <c r="Y467" s="2"/>
     </row>
-    <row r="468" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="468" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B468" s="5"/>
       <c r="C468" s="5"/>
       <c r="D468" s="4"/>
@@ -17588,7 +17597,7 @@
       <c r="X468" s="2"/>
       <c r="Y468" s="2"/>
     </row>
-    <row r="469" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="469" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B469" s="5"/>
       <c r="C469" s="5"/>
       <c r="D469" s="4"/>
@@ -17614,7 +17623,7 @@
       <c r="X469" s="2"/>
       <c r="Y469" s="2"/>
     </row>
-    <row r="470" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="470" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B470" s="5"/>
       <c r="C470" s="5"/>
       <c r="D470" s="4"/>
@@ -17640,7 +17649,7 @@
       <c r="X470" s="2"/>
       <c r="Y470" s="2"/>
     </row>
-    <row r="471" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="471" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B471" s="5"/>
       <c r="C471" s="5"/>
       <c r="D471" s="4"/>
@@ -17666,7 +17675,7 @@
       <c r="X471" s="2"/>
       <c r="Y471" s="2"/>
     </row>
-    <row r="472" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="472" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B472" s="5"/>
       <c r="C472" s="5"/>
       <c r="D472" s="4"/>
@@ -17692,7 +17701,7 @@
       <c r="X472" s="2"/>
       <c r="Y472" s="2"/>
     </row>
-    <row r="473" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="473" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B473" s="5"/>
       <c r="C473" s="5"/>
       <c r="D473" s="4"/>
@@ -17718,7 +17727,7 @@
       <c r="X473" s="2"/>
       <c r="Y473" s="2"/>
     </row>
-    <row r="474" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="474" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B474" s="5"/>
       <c r="C474" s="5"/>
       <c r="D474" s="4"/>
@@ -17744,7 +17753,7 @@
       <c r="X474" s="2"/>
       <c r="Y474" s="2"/>
     </row>
-    <row r="475" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="475" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B475" s="5"/>
       <c r="C475" s="5"/>
       <c r="D475" s="4"/>
@@ -17770,7 +17779,7 @@
       <c r="X475" s="2"/>
       <c r="Y475" s="2"/>
     </row>
-    <row r="476" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="476" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B476" s="5"/>
       <c r="C476" s="5"/>
       <c r="D476" s="4"/>
@@ -17796,7 +17805,7 @@
       <c r="X476" s="2"/>
       <c r="Y476" s="2"/>
     </row>
-    <row r="477" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="477" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B477" s="5"/>
       <c r="C477" s="5"/>
       <c r="D477" s="4"/>
@@ -17822,7 +17831,7 @@
       <c r="X477" s="2"/>
       <c r="Y477" s="2"/>
     </row>
-    <row r="478" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="478" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B478" s="5"/>
       <c r="C478" s="5"/>
       <c r="D478" s="4"/>
@@ -17848,7 +17857,7 @@
       <c r="X478" s="2"/>
       <c r="Y478" s="2"/>
     </row>
-    <row r="479" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="479" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B479" s="5"/>
       <c r="C479" s="5"/>
       <c r="D479" s="4"/>
@@ -17874,7 +17883,7 @@
       <c r="X479" s="2"/>
       <c r="Y479" s="2"/>
     </row>
-    <row r="480" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="480" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B480" s="5"/>
       <c r="C480" s="5"/>
       <c r="D480" s="4"/>
@@ -17900,7 +17909,7 @@
       <c r="X480" s="2"/>
       <c r="Y480" s="2"/>
     </row>
-    <row r="481" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="481" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B481" s="5"/>
       <c r="C481" s="5"/>
       <c r="D481" s="4"/>
@@ -17926,7 +17935,7 @@
       <c r="X481" s="2"/>
       <c r="Y481" s="2"/>
     </row>
-    <row r="482" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="482" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B482" s="5"/>
       <c r="C482" s="5"/>
       <c r="D482" s="4"/>
@@ -17952,7 +17961,7 @@
       <c r="X482" s="2"/>
       <c r="Y482" s="2"/>
     </row>
-    <row r="483" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="483" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B483" s="5"/>
       <c r="C483" s="5"/>
       <c r="D483" s="4"/>
@@ -17978,7 +17987,7 @@
       <c r="X483" s="2"/>
       <c r="Y483" s="2"/>
     </row>
-    <row r="484" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="484" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B484" s="5"/>
       <c r="C484" s="5"/>
       <c r="D484" s="4"/>
@@ -18004,7 +18013,7 @@
       <c r="X484" s="2"/>
       <c r="Y484" s="2"/>
     </row>
-    <row r="485" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="485" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B485" s="5"/>
       <c r="C485" s="5"/>
       <c r="D485" s="4"/>
@@ -18030,7 +18039,7 @@
       <c r="X485" s="2"/>
       <c r="Y485" s="2"/>
     </row>
-    <row r="486" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="486" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B486" s="5"/>
       <c r="C486" s="5"/>
       <c r="D486" s="4"/>
@@ -18056,7 +18065,7 @@
       <c r="X486" s="2"/>
       <c r="Y486" s="2"/>
     </row>
-    <row r="487" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="487" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B487" s="5"/>
       <c r="C487" s="5"/>
       <c r="D487" s="4"/>
@@ -18082,7 +18091,7 @@
       <c r="X487" s="2"/>
       <c r="Y487" s="2"/>
     </row>
-    <row r="488" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="488" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B488" s="5"/>
       <c r="C488" s="5"/>
       <c r="D488" s="4"/>
@@ -18108,7 +18117,7 @@
       <c r="X488" s="2"/>
       <c r="Y488" s="2"/>
     </row>
-    <row r="489" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="489" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B489" s="5"/>
       <c r="C489" s="5"/>
       <c r="D489" s="4"/>
@@ -18134,7 +18143,7 @@
       <c r="X489" s="2"/>
       <c r="Y489" s="2"/>
     </row>
-    <row r="490" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="490" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B490" s="5"/>
       <c r="C490" s="5"/>
       <c r="D490" s="4"/>
@@ -18160,7 +18169,7 @@
       <c r="X490" s="2"/>
       <c r="Y490" s="2"/>
     </row>
-    <row r="491" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="491" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B491" s="5"/>
       <c r="C491" s="5"/>
       <c r="D491" s="4"/>
@@ -18186,7 +18195,7 @@
       <c r="X491" s="2"/>
       <c r="Y491" s="2"/>
     </row>
-    <row r="492" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="492" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B492" s="5"/>
       <c r="C492" s="5"/>
       <c r="D492" s="4"/>
@@ -18212,7 +18221,7 @@
       <c r="X492" s="2"/>
       <c r="Y492" s="2"/>
     </row>
-    <row r="493" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="493" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B493" s="5"/>
       <c r="C493" s="5"/>
       <c r="D493" s="4"/>
@@ -18238,7 +18247,7 @@
       <c r="X493" s="2"/>
       <c r="Y493" s="2"/>
     </row>
-    <row r="494" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="494" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B494" s="5"/>
       <c r="C494" s="5"/>
       <c r="D494" s="4"/>
@@ -18264,7 +18273,7 @@
       <c r="X494" s="2"/>
       <c r="Y494" s="2"/>
     </row>
-    <row r="495" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="495" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B495" s="5"/>
       <c r="C495" s="5"/>
       <c r="D495" s="4"/>
@@ -18290,7 +18299,7 @@
       <c r="X495" s="2"/>
       <c r="Y495" s="2"/>
     </row>
-    <row r="496" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="496" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B496" s="5"/>
       <c r="C496" s="5"/>
       <c r="D496" s="4"/>
@@ -18316,7 +18325,7 @@
       <c r="X496" s="2"/>
       <c r="Y496" s="2"/>
     </row>
-    <row r="497" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="497" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B497" s="5"/>
       <c r="C497" s="5"/>
       <c r="D497" s="4"/>
@@ -18342,7 +18351,7 @@
       <c r="X497" s="2"/>
       <c r="Y497" s="2"/>
     </row>
-    <row r="498" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="498" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B498" s="5"/>
       <c r="C498" s="5"/>
       <c r="D498" s="4"/>
@@ -18368,7 +18377,7 @@
       <c r="X498" s="2"/>
       <c r="Y498" s="2"/>
     </row>
-    <row r="499" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="499" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B499" s="5"/>
       <c r="C499" s="5"/>
       <c r="D499" s="4"/>
@@ -18394,7 +18403,7 @@
       <c r="X499" s="2"/>
       <c r="Y499" s="2"/>
     </row>
-    <row r="500" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="500" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B500" s="5"/>
       <c r="C500" s="5"/>
       <c r="D500" s="4"/>
@@ -18420,7 +18429,7 @@
       <c r="X500" s="2"/>
       <c r="Y500" s="2"/>
     </row>
-    <row r="501" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="501" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B501" s="5"/>
       <c r="C501" s="5"/>
       <c r="D501" s="4"/>
@@ -18446,7 +18455,7 @@
       <c r="X501" s="2"/>
       <c r="Y501" s="2"/>
     </row>
-    <row r="502" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="502" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B502" s="5"/>
       <c r="C502" s="5"/>
       <c r="D502" s="4"/>
@@ -18472,7 +18481,7 @@
       <c r="X502" s="2"/>
       <c r="Y502" s="2"/>
     </row>
-    <row r="503" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="503" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B503" s="5"/>
       <c r="C503" s="5"/>
       <c r="D503" s="4"/>
@@ -18498,7 +18507,7 @@
       <c r="X503" s="2"/>
       <c r="Y503" s="2"/>
     </row>
-    <row r="504" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="504" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B504" s="5"/>
       <c r="C504" s="5"/>
       <c r="D504" s="4"/>
@@ -18524,7 +18533,7 @@
       <c r="X504" s="2"/>
       <c r="Y504" s="2"/>
     </row>
-    <row r="505" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="505" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B505" s="5"/>
       <c r="C505" s="5"/>
       <c r="D505" s="4"/>
@@ -18550,7 +18559,7 @@
       <c r="X505" s="2"/>
       <c r="Y505" s="2"/>
     </row>
-    <row r="506" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="506" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B506" s="5"/>
       <c r="C506" s="5"/>
       <c r="D506" s="4"/>
@@ -18576,7 +18585,7 @@
       <c r="X506" s="2"/>
       <c r="Y506" s="2"/>
     </row>
-    <row r="507" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="507" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B507" s="5"/>
       <c r="C507" s="5"/>
       <c r="D507" s="4"/>
@@ -18602,7 +18611,7 @@
       <c r="X507" s="2"/>
       <c r="Y507" s="2"/>
     </row>
-    <row r="508" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="508" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B508" s="5"/>
       <c r="C508" s="5"/>
       <c r="D508" s="4"/>
@@ -18628,7 +18637,7 @@
       <c r="X508" s="2"/>
       <c r="Y508" s="2"/>
     </row>
-    <row r="509" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="509" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B509" s="5"/>
       <c r="C509" s="5"/>
       <c r="D509" s="4"/>
@@ -18654,7 +18663,7 @@
       <c r="X509" s="2"/>
       <c r="Y509" s="2"/>
     </row>
-    <row r="510" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="510" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B510" s="5"/>
       <c r="C510" s="5"/>
       <c r="D510" s="4"/>
@@ -18680,7 +18689,7 @@
       <c r="X510" s="2"/>
       <c r="Y510" s="2"/>
     </row>
-    <row r="511" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="511" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B511" s="5"/>
       <c r="C511" s="5"/>
       <c r="D511" s="4"/>
@@ -18706,7 +18715,7 @@
       <c r="X511" s="2"/>
       <c r="Y511" s="2"/>
     </row>
-    <row r="512" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="512" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B512" s="5"/>
       <c r="C512" s="5"/>
       <c r="D512" s="4"/>
@@ -18732,7 +18741,7 @@
       <c r="X512" s="2"/>
       <c r="Y512" s="2"/>
     </row>
-    <row r="513" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="513" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B513" s="5"/>
       <c r="C513" s="5"/>
       <c r="D513" s="4"/>
@@ -18758,7 +18767,7 @@
       <c r="X513" s="2"/>
       <c r="Y513" s="2"/>
     </row>
-    <row r="514" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="514" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B514" s="5"/>
       <c r="C514" s="5"/>
       <c r="D514" s="4"/>
@@ -18784,7 +18793,7 @@
       <c r="X514" s="2"/>
       <c r="Y514" s="2"/>
     </row>
-    <row r="515" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="515" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B515" s="5"/>
       <c r="C515" s="5"/>
       <c r="D515" s="4"/>
@@ -18810,7 +18819,7 @@
       <c r="X515" s="2"/>
       <c r="Y515" s="2"/>
     </row>
-    <row r="516" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="516" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B516" s="5"/>
       <c r="C516" s="5"/>
       <c r="D516" s="4"/>
@@ -18836,7 +18845,7 @@
       <c r="X516" s="2"/>
       <c r="Y516" s="2"/>
     </row>
-    <row r="517" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="517" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B517" s="5"/>
       <c r="C517" s="5"/>
       <c r="D517" s="4"/>
@@ -18862,7 +18871,7 @@
       <c r="X517" s="2"/>
       <c r="Y517" s="2"/>
     </row>
-    <row r="518" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="518" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B518" s="5"/>
       <c r="C518" s="5"/>
       <c r="D518" s="4"/>
@@ -18888,7 +18897,7 @@
       <c r="X518" s="2"/>
       <c r="Y518" s="2"/>
     </row>
-    <row r="519" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="519" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B519" s="5"/>
       <c r="C519" s="5"/>
       <c r="D519" s="4"/>
@@ -18914,7 +18923,7 @@
       <c r="X519" s="2"/>
       <c r="Y519" s="2"/>
     </row>
-    <row r="520" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="520" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B520" s="5"/>
       <c r="C520" s="5"/>
       <c r="D520" s="4"/>
@@ -18940,7 +18949,7 @@
       <c r="X520" s="2"/>
       <c r="Y520" s="2"/>
     </row>
-    <row r="521" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="521" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B521" s="5"/>
       <c r="C521" s="5"/>
       <c r="D521" s="4"/>
@@ -18966,7 +18975,7 @@
       <c r="X521" s="2"/>
       <c r="Y521" s="2"/>
     </row>
-    <row r="522" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="522" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B522" s="5"/>
       <c r="C522" s="5"/>
       <c r="D522" s="4"/>
@@ -18992,7 +19001,7 @@
       <c r="X522" s="2"/>
       <c r="Y522" s="2"/>
     </row>
-    <row r="523" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="523" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B523" s="5"/>
       <c r="C523" s="5"/>
       <c r="D523" s="4"/>
@@ -19018,7 +19027,7 @@
       <c r="X523" s="2"/>
       <c r="Y523" s="2"/>
     </row>
-    <row r="524" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="524" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B524" s="5"/>
       <c r="C524" s="5"/>
       <c r="D524" s="4"/>
@@ -19044,7 +19053,7 @@
       <c r="X524" s="2"/>
       <c r="Y524" s="2"/>
     </row>
-    <row r="525" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="525" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B525" s="5"/>
       <c r="C525" s="5"/>
       <c r="D525" s="4"/>
@@ -19070,7 +19079,7 @@
       <c r="X525" s="2"/>
       <c r="Y525" s="2"/>
     </row>
-    <row r="526" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="526" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B526" s="5"/>
       <c r="C526" s="5"/>
       <c r="D526" s="4"/>
@@ -19096,7 +19105,7 @@
       <c r="X526" s="2"/>
       <c r="Y526" s="2"/>
     </row>
-    <row r="527" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="527" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B527" s="5"/>
       <c r="C527" s="5"/>
       <c r="D527" s="4"/>
@@ -19122,7 +19131,7 @@
       <c r="X527" s="2"/>
       <c r="Y527" s="2"/>
     </row>
-    <row r="528" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="528" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B528" s="5"/>
       <c r="C528" s="5"/>
       <c r="D528" s="4"/>
@@ -19148,7 +19157,7 @@
       <c r="X528" s="2"/>
       <c r="Y528" s="2"/>
     </row>
-    <row r="529" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="529" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B529" s="5"/>
       <c r="C529" s="5"/>
       <c r="D529" s="4"/>
@@ -19174,7 +19183,7 @@
       <c r="X529" s="2"/>
       <c r="Y529" s="2"/>
     </row>
-    <row r="530" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="530" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B530" s="5"/>
       <c r="C530" s="5"/>
       <c r="D530" s="4"/>
@@ -19200,7 +19209,7 @@
       <c r="X530" s="2"/>
       <c r="Y530" s="2"/>
     </row>
-    <row r="531" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="531" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B531" s="5"/>
       <c r="C531" s="5"/>
       <c r="D531" s="4"/>
@@ -19226,7 +19235,7 @@
       <c r="X531" s="2"/>
       <c r="Y531" s="2"/>
     </row>
-    <row r="532" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="532" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B532" s="5"/>
       <c r="C532" s="5"/>
       <c r="D532" s="4"/>
@@ -19252,7 +19261,7 @@
       <c r="X532" s="2"/>
       <c r="Y532" s="2"/>
     </row>
-    <row r="533" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="533" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B533" s="5"/>
       <c r="C533" s="5"/>
       <c r="D533" s="4"/>
@@ -19278,7 +19287,7 @@
       <c r="X533" s="2"/>
       <c r="Y533" s="2"/>
     </row>
-    <row r="534" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="534" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B534" s="5"/>
       <c r="C534" s="5"/>
       <c r="D534" s="4"/>
@@ -19304,7 +19313,7 @@
       <c r="X534" s="2"/>
       <c r="Y534" s="2"/>
     </row>
-    <row r="535" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="535" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B535" s="5"/>
       <c r="C535" s="5"/>
       <c r="D535" s="4"/>
@@ -19330,7 +19339,7 @@
       <c r="X535" s="2"/>
       <c r="Y535" s="2"/>
     </row>
-    <row r="536" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="536" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B536" s="5"/>
       <c r="C536" s="5"/>
       <c r="D536" s="4"/>
@@ -19356,7 +19365,7 @@
       <c r="X536" s="2"/>
       <c r="Y536" s="2"/>
     </row>
-    <row r="537" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="537" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B537" s="5"/>
       <c r="C537" s="5"/>
       <c r="D537" s="4"/>
@@ -19382,7 +19391,7 @@
       <c r="X537" s="2"/>
       <c r="Y537" s="2"/>
     </row>
-    <row r="538" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="538" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B538" s="5"/>
       <c r="C538" s="5"/>
       <c r="D538" s="4"/>
@@ -19408,7 +19417,7 @@
       <c r="X538" s="2"/>
       <c r="Y538" s="2"/>
     </row>
-    <row r="539" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="539" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B539" s="5"/>
       <c r="C539" s="5"/>
       <c r="D539" s="4"/>
@@ -19434,7 +19443,7 @@
       <c r="X539" s="2"/>
       <c r="Y539" s="2"/>
     </row>
-    <row r="540" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="540" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B540" s="5"/>
       <c r="C540" s="5"/>
       <c r="D540" s="4"/>
@@ -19460,7 +19469,7 @@
       <c r="X540" s="2"/>
       <c r="Y540" s="2"/>
     </row>
-    <row r="541" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="541" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B541" s="5"/>
       <c r="C541" s="5"/>
       <c r="D541" s="4"/>
@@ -19486,7 +19495,7 @@
       <c r="X541" s="2"/>
       <c r="Y541" s="2"/>
     </row>
-    <row r="542" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="542" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B542" s="5"/>
       <c r="C542" s="5"/>
       <c r="D542" s="4"/>
@@ -19512,7 +19521,7 @@
       <c r="X542" s="2"/>
       <c r="Y542" s="2"/>
     </row>
-    <row r="543" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="543" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B543" s="5"/>
       <c r="C543" s="5"/>
       <c r="D543" s="4"/>
@@ -19538,7 +19547,7 @@
       <c r="X543" s="2"/>
       <c r="Y543" s="2"/>
     </row>
-    <row r="544" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="544" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B544" s="5"/>
       <c r="C544" s="5"/>
       <c r="D544" s="4"/>
@@ -19564,7 +19573,7 @@
       <c r="X544" s="2"/>
       <c r="Y544" s="2"/>
     </row>
-    <row r="545" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="545" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B545" s="5"/>
       <c r="C545" s="5"/>
       <c r="D545" s="4"/>
@@ -19590,7 +19599,7 @@
       <c r="X545" s="2"/>
       <c r="Y545" s="2"/>
     </row>
-    <row r="546" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="546" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B546" s="5"/>
       <c r="C546" s="5"/>
       <c r="D546" s="4"/>
@@ -19616,7 +19625,7 @@
       <c r="X546" s="2"/>
       <c r="Y546" s="2"/>
     </row>
-    <row r="547" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="547" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B547" s="5"/>
       <c r="C547" s="5"/>
       <c r="D547" s="4"/>
@@ -19642,7 +19651,7 @@
       <c r="X547" s="2"/>
       <c r="Y547" s="2"/>
     </row>
-    <row r="548" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="548" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B548" s="5"/>
       <c r="C548" s="5"/>
       <c r="D548" s="4"/>
@@ -19668,7 +19677,7 @@
       <c r="X548" s="2"/>
       <c r="Y548" s="2"/>
     </row>
-    <row r="549" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="549" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B549" s="5"/>
       <c r="C549" s="5"/>
       <c r="D549" s="4"/>
@@ -19694,7 +19703,7 @@
       <c r="X549" s="2"/>
       <c r="Y549" s="2"/>
     </row>
-    <row r="550" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="550" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B550" s="5"/>
       <c r="C550" s="5"/>
       <c r="D550" s="4"/>
@@ -19720,7 +19729,7 @@
       <c r="X550" s="2"/>
       <c r="Y550" s="2"/>
     </row>
-    <row r="551" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="551" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B551" s="5"/>
       <c r="C551" s="5"/>
       <c r="D551" s="4"/>
@@ -19746,7 +19755,7 @@
       <c r="X551" s="2"/>
       <c r="Y551" s="2"/>
     </row>
-    <row r="552" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="552" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B552" s="5"/>
       <c r="C552" s="5"/>
       <c r="D552" s="4"/>
@@ -19772,7 +19781,7 @@
       <c r="X552" s="2"/>
       <c r="Y552" s="2"/>
     </row>
-    <row r="553" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="553" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B553" s="5"/>
       <c r="C553" s="5"/>
       <c r="D553" s="4"/>
@@ -19798,7 +19807,7 @@
       <c r="X553" s="2"/>
       <c r="Y553" s="2"/>
     </row>
-    <row r="554" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="554" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B554" s="5"/>
       <c r="C554" s="5"/>
       <c r="D554" s="4"/>
@@ -19824,7 +19833,7 @@
       <c r="X554" s="2"/>
       <c r="Y554" s="2"/>
     </row>
-    <row r="555" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="555" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B555" s="5"/>
       <c r="C555" s="5"/>
       <c r="D555" s="4"/>
@@ -19850,7 +19859,7 @@
       <c r="X555" s="2"/>
       <c r="Y555" s="2"/>
     </row>
-    <row r="556" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="556" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B556" s="5"/>
       <c r="C556" s="5"/>
       <c r="D556" s="4"/>
@@ -19876,7 +19885,7 @@
       <c r="X556" s="2"/>
       <c r="Y556" s="2"/>
     </row>
-    <row r="557" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="557" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B557" s="5"/>
       <c r="C557" s="5"/>
       <c r="D557" s="4"/>
@@ -19902,7 +19911,7 @@
       <c r="X557" s="2"/>
       <c r="Y557" s="2"/>
     </row>
-    <row r="558" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="558" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B558" s="5"/>
       <c r="C558" s="5"/>
       <c r="D558" s="4"/>
@@ -19928,7 +19937,7 @@
       <c r="X558" s="2"/>
       <c r="Y558" s="2"/>
     </row>
-    <row r="559" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="559" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B559" s="5"/>
       <c r="C559" s="5"/>
       <c r="D559" s="4"/>
@@ -19954,7 +19963,7 @@
       <c r="X559" s="2"/>
       <c r="Y559" s="2"/>
     </row>
-    <row r="560" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="560" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B560" s="5"/>
       <c r="C560" s="5"/>
       <c r="D560" s="4"/>
@@ -19980,7 +19989,7 @@
       <c r="X560" s="2"/>
       <c r="Y560" s="2"/>
     </row>
-    <row r="561" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="561" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B561" s="5"/>
       <c r="C561" s="5"/>
       <c r="D561" s="4"/>
@@ -20006,7 +20015,7 @@
       <c r="X561" s="2"/>
       <c r="Y561" s="2"/>
     </row>
-    <row r="562" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="562" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B562" s="5"/>
       <c r="C562" s="5"/>
       <c r="D562" s="4"/>
@@ -20032,7 +20041,7 @@
       <c r="X562" s="2"/>
       <c r="Y562" s="2"/>
     </row>
-    <row r="563" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="563" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B563" s="5"/>
       <c r="C563" s="5"/>
       <c r="D563" s="4"/>
@@ -20058,7 +20067,7 @@
       <c r="X563" s="2"/>
       <c r="Y563" s="2"/>
     </row>
-    <row r="564" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="564" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B564" s="5"/>
       <c r="C564" s="5"/>
       <c r="D564" s="4"/>
@@ -20084,7 +20093,7 @@
       <c r="X564" s="2"/>
       <c r="Y564" s="2"/>
     </row>
-    <row r="565" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="565" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B565" s="5"/>
       <c r="C565" s="5"/>
       <c r="D565" s="4"/>
@@ -20110,7 +20119,7 @@
       <c r="X565" s="2"/>
       <c r="Y565" s="2"/>
     </row>
-    <row r="566" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="566" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B566" s="5"/>
       <c r="C566" s="5"/>
       <c r="D566" s="4"/>
@@ -20136,7 +20145,7 @@
       <c r="X566" s="2"/>
       <c r="Y566" s="2"/>
     </row>
-    <row r="567" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="567" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B567" s="5"/>
       <c r="C567" s="5"/>
       <c r="D567" s="4"/>
@@ -20162,7 +20171,7 @@
       <c r="X567" s="2"/>
       <c r="Y567" s="2"/>
     </row>
-    <row r="568" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="568" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B568" s="5"/>
       <c r="C568" s="5"/>
       <c r="D568" s="4"/>
@@ -20188,7 +20197,7 @@
       <c r="X568" s="2"/>
       <c r="Y568" s="2"/>
     </row>
-    <row r="569" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="569" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B569" s="5"/>
       <c r="C569" s="5"/>
       <c r="D569" s="4"/>
@@ -20214,7 +20223,7 @@
       <c r="X569" s="2"/>
       <c r="Y569" s="2"/>
     </row>
-    <row r="570" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="570" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B570" s="5"/>
       <c r="C570" s="5"/>
       <c r="D570" s="4"/>
@@ -20240,7 +20249,7 @@
       <c r="X570" s="2"/>
       <c r="Y570" s="2"/>
     </row>
-    <row r="571" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="571" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B571" s="5"/>
       <c r="C571" s="5"/>
       <c r="D571" s="4"/>
@@ -20266,7 +20275,7 @@
       <c r="X571" s="2"/>
       <c r="Y571" s="2"/>
     </row>
-    <row r="572" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="572" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B572" s="5"/>
       <c r="C572" s="5"/>
       <c r="D572" s="4"/>
@@ -20292,7 +20301,7 @@
       <c r="X572" s="2"/>
       <c r="Y572" s="2"/>
     </row>
-    <row r="573" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="573" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B573" s="5"/>
       <c r="C573" s="5"/>
       <c r="D573" s="4"/>
@@ -20318,7 +20327,7 @@
       <c r="X573" s="2"/>
       <c r="Y573" s="2"/>
     </row>
-    <row r="574" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="574" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B574" s="5"/>
       <c r="C574" s="5"/>
       <c r="D574" s="4"/>
@@ -20344,7 +20353,7 @@
       <c r="X574" s="2"/>
       <c r="Y574" s="2"/>
     </row>
-    <row r="575" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="575" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B575" s="5"/>
       <c r="C575" s="5"/>
       <c r="D575" s="4"/>
@@ -20370,7 +20379,7 @@
       <c r="X575" s="2"/>
       <c r="Y575" s="2"/>
     </row>
-    <row r="576" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="576" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B576" s="5"/>
       <c r="C576" s="5"/>
       <c r="D576" s="4"/>
@@ -20396,7 +20405,7 @@
       <c r="X576" s="2"/>
       <c r="Y576" s="2"/>
     </row>
-    <row r="577" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="577" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B577" s="5"/>
       <c r="C577" s="5"/>
       <c r="D577" s="4"/>
@@ -20422,7 +20431,7 @@
       <c r="X577" s="2"/>
       <c r="Y577" s="2"/>
     </row>
-    <row r="578" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="578" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B578" s="5"/>
       <c r="C578" s="5"/>
       <c r="D578" s="4"/>
@@ -20448,7 +20457,7 @@
       <c r="X578" s="2"/>
       <c r="Y578" s="2"/>
     </row>
-    <row r="579" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="579" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B579" s="5"/>
       <c r="C579" s="5"/>
       <c r="D579" s="4"/>
@@ -20474,7 +20483,7 @@
       <c r="X579" s="2"/>
       <c r="Y579" s="2"/>
     </row>
-    <row r="580" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="580" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B580" s="5"/>
       <c r="C580" s="5"/>
       <c r="D580" s="4"/>
@@ -20500,7 +20509,7 @@
       <c r="X580" s="2"/>
       <c r="Y580" s="2"/>
     </row>
-    <row r="581" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="581" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B581" s="5"/>
       <c r="C581" s="5"/>
       <c r="D581" s="4"/>
@@ -20526,7 +20535,7 @@
       <c r="X581" s="2"/>
       <c r="Y581" s="2"/>
     </row>
-    <row r="582" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="582" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B582" s="5"/>
       <c r="C582" s="5"/>
       <c r="D582" s="4"/>
@@ -20552,7 +20561,7 @@
       <c r="X582" s="2"/>
       <c r="Y582" s="2"/>
     </row>
-    <row r="583" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="583" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B583" s="5"/>
       <c r="C583" s="5"/>
       <c r="D583" s="4"/>
@@ -20578,7 +20587,7 @@
       <c r="X583" s="2"/>
       <c r="Y583" s="2"/>
     </row>
-    <row r="584" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="584" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B584" s="5"/>
       <c r="C584" s="5"/>
       <c r="D584" s="4"/>
@@ -20604,7 +20613,7 @@
       <c r="X584" s="2"/>
       <c r="Y584" s="2"/>
     </row>
-    <row r="585" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="585" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B585" s="5"/>
       <c r="C585" s="5"/>
       <c r="D585" s="4"/>
@@ -20630,7 +20639,7 @@
       <c r="X585" s="2"/>
       <c r="Y585" s="2"/>
     </row>
-    <row r="586" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="586" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B586" s="5"/>
       <c r="C586" s="5"/>
       <c r="D586" s="4"/>
@@ -20656,7 +20665,7 @@
       <c r="X586" s="2"/>
       <c r="Y586" s="2"/>
     </row>
-    <row r="587" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="587" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B587" s="5"/>
       <c r="C587" s="5"/>
       <c r="D587" s="4"/>
@@ -20682,7 +20691,7 @@
       <c r="X587" s="2"/>
       <c r="Y587" s="2"/>
     </row>
-    <row r="588" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="588" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B588" s="5"/>
       <c r="C588" s="5"/>
       <c r="D588" s="4"/>
@@ -20708,7 +20717,7 @@
       <c r="X588" s="2"/>
       <c r="Y588" s="2"/>
     </row>
-    <row r="589" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="589" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B589" s="5"/>
       <c r="C589" s="5"/>
       <c r="D589" s="4"/>
@@ -20734,7 +20743,7 @@
       <c r="X589" s="2"/>
       <c r="Y589" s="2"/>
     </row>
-    <row r="590" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="590" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B590" s="5"/>
       <c r="C590" s="5"/>
       <c r="D590" s="4"/>
@@ -20760,7 +20769,7 @@
       <c r="X590" s="2"/>
       <c r="Y590" s="2"/>
     </row>
-    <row r="591" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="591" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B591" s="5"/>
       <c r="C591" s="5"/>
       <c r="D591" s="4"/>
@@ -20786,7 +20795,7 @@
       <c r="X591" s="2"/>
       <c r="Y591" s="2"/>
     </row>
-    <row r="592" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="592" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B592" s="5"/>
       <c r="C592" s="5"/>
       <c r="D592" s="4"/>
@@ -20812,7 +20821,7 @@
       <c r="X592" s="2"/>
       <c r="Y592" s="2"/>
     </row>
-    <row r="593" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="593" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B593" s="5"/>
       <c r="C593" s="5"/>
       <c r="D593" s="4"/>
@@ -20838,7 +20847,7 @@
       <c r="X593" s="2"/>
       <c r="Y593" s="2"/>
     </row>
-    <row r="594" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="594" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B594" s="5"/>
       <c r="C594" s="5"/>
       <c r="D594" s="4"/>
@@ -20864,7 +20873,7 @@
       <c r="X594" s="2"/>
       <c r="Y594" s="2"/>
     </row>
-    <row r="595" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="595" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B595" s="5"/>
       <c r="C595" s="5"/>
       <c r="D595" s="4"/>
@@ -20890,7 +20899,7 @@
       <c r="X595" s="2"/>
       <c r="Y595" s="2"/>
     </row>
-    <row r="596" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="596" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B596" s="5"/>
       <c r="C596" s="5"/>
       <c r="D596" s="4"/>
@@ -20916,7 +20925,7 @@
       <c r="X596" s="2"/>
       <c r="Y596" s="2"/>
     </row>
-    <row r="597" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="597" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B597" s="5"/>
       <c r="C597" s="5"/>
       <c r="D597" s="4"/>
@@ -20942,7 +20951,7 @@
       <c r="X597" s="2"/>
       <c r="Y597" s="2"/>
     </row>
-    <row r="598" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="598" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B598" s="5"/>
       <c r="C598" s="5"/>
       <c r="D598" s="4"/>
@@ -20968,7 +20977,7 @@
       <c r="X598" s="2"/>
       <c r="Y598" s="2"/>
     </row>
-    <row r="599" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="599" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B599" s="5"/>
       <c r="C599" s="5"/>
       <c r="D599" s="4"/>
@@ -20994,7 +21003,7 @@
       <c r="X599" s="2"/>
       <c r="Y599" s="2"/>
     </row>
-    <row r="600" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="600" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B600" s="5"/>
       <c r="C600" s="5"/>
       <c r="D600" s="4"/>
@@ -21020,7 +21029,7 @@
       <c r="X600" s="2"/>
       <c r="Y600" s="2"/>
     </row>
-    <row r="601" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="601" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B601" s="5"/>
       <c r="C601" s="5"/>
       <c r="D601" s="4"/>
@@ -21046,7 +21055,7 @@
       <c r="X601" s="2"/>
       <c r="Y601" s="2"/>
     </row>
-    <row r="602" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="602" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B602" s="5"/>
       <c r="C602" s="5"/>
       <c r="D602" s="4"/>
@@ -21072,7 +21081,7 @@
       <c r="X602" s="2"/>
       <c r="Y602" s="2"/>
     </row>
-    <row r="603" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="603" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B603" s="5"/>
       <c r="C603" s="5"/>
       <c r="D603" s="4"/>
@@ -21098,7 +21107,7 @@
       <c r="X603" s="2"/>
       <c r="Y603" s="2"/>
     </row>
-    <row r="604" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="604" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B604" s="5"/>
       <c r="C604" s="5"/>
       <c r="D604" s="4"/>
@@ -21124,7 +21133,7 @@
       <c r="X604" s="2"/>
       <c r="Y604" s="2"/>
     </row>
-    <row r="605" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="605" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B605" s="5"/>
       <c r="C605" s="5"/>
       <c r="D605" s="4"/>
@@ -21150,7 +21159,7 @@
       <c r="X605" s="2"/>
       <c r="Y605" s="2"/>
     </row>
-    <row r="606" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="606" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B606" s="5"/>
       <c r="C606" s="5"/>
       <c r="D606" s="4"/>
@@ -21176,7 +21185,7 @@
       <c r="X606" s="2"/>
       <c r="Y606" s="2"/>
     </row>
-    <row r="607" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="607" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B607" s="5"/>
       <c r="C607" s="5"/>
       <c r="D607" s="4"/>
@@ -21202,7 +21211,7 @@
       <c r="X607" s="2"/>
       <c r="Y607" s="2"/>
     </row>
-    <row r="608" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="608" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B608" s="5"/>
       <c r="C608" s="5"/>
       <c r="D608" s="4"/>
@@ -21228,7 +21237,7 @@
       <c r="X608" s="2"/>
       <c r="Y608" s="2"/>
     </row>
-    <row r="609" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="609" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B609" s="5"/>
       <c r="C609" s="5"/>
       <c r="D609" s="4"/>
@@ -21254,7 +21263,7 @@
       <c r="X609" s="2"/>
       <c r="Y609" s="2"/>
     </row>
-    <row r="610" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="610" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B610" s="5"/>
       <c r="C610" s="5"/>
       <c r="D610" s="4"/>
@@ -21280,7 +21289,7 @@
       <c r="X610" s="2"/>
       <c r="Y610" s="2"/>
     </row>
-    <row r="611" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="611" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B611" s="5"/>
       <c r="C611" s="5"/>
       <c r="D611" s="4"/>
@@ -21306,7 +21315,7 @@
       <c r="X611" s="2"/>
       <c r="Y611" s="2"/>
     </row>
-    <row r="612" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="612" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B612" s="5"/>
       <c r="C612" s="5"/>
       <c r="D612" s="4"/>
@@ -21332,7 +21341,7 @@
       <c r="X612" s="2"/>
       <c r="Y612" s="2"/>
     </row>
-    <row r="613" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="613" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B613" s="5"/>
       <c r="C613" s="5"/>
       <c r="D613" s="4"/>
@@ -21358,7 +21367,7 @@
       <c r="X613" s="2"/>
       <c r="Y613" s="2"/>
     </row>
-    <row r="614" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="614" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B614" s="5"/>
       <c r="C614" s="5"/>
       <c r="D614" s="4"/>
@@ -21384,7 +21393,7 @@
       <c r="X614" s="2"/>
       <c r="Y614" s="2"/>
     </row>
-    <row r="615" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="615" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B615" s="5"/>
       <c r="C615" s="5"/>
       <c r="D615" s="4"/>
@@ -21410,7 +21419,7 @@
       <c r="X615" s="2"/>
       <c r="Y615" s="2"/>
     </row>
-    <row r="616" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="616" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B616" s="5"/>
       <c r="C616" s="5"/>
       <c r="D616" s="4"/>
@@ -21436,7 +21445,7 @@
       <c r="X616" s="2"/>
       <c r="Y616" s="2"/>
     </row>
-    <row r="617" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="617" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B617" s="5"/>
       <c r="C617" s="5"/>
       <c r="D617" s="4"/>
@@ -21462,7 +21471,7 @@
       <c r="X617" s="2"/>
       <c r="Y617" s="2"/>
     </row>
-    <row r="618" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="618" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B618" s="5"/>
       <c r="C618" s="5"/>
       <c r="D618" s="4"/>
@@ -21488,7 +21497,7 @@
       <c r="X618" s="2"/>
       <c r="Y618" s="2"/>
     </row>
-    <row r="619" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="619" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B619" s="5"/>
       <c r="C619" s="5"/>
       <c r="D619" s="4"/>
@@ -21514,7 +21523,7 @@
       <c r="X619" s="2"/>
       <c r="Y619" s="2"/>
     </row>
-    <row r="620" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="620" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B620" s="5"/>
       <c r="C620" s="5"/>
       <c r="D620" s="4"/>
@@ -21540,7 +21549,7 @@
       <c r="X620" s="2"/>
       <c r="Y620" s="2"/>
     </row>
-    <row r="621" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="621" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B621" s="5"/>
       <c r="C621" s="5"/>
       <c r="D621" s="4"/>
@@ -21566,7 +21575,7 @@
       <c r="X621" s="2"/>
       <c r="Y621" s="2"/>
     </row>
-    <row r="622" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="622" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B622" s="5"/>
       <c r="C622" s="5"/>
       <c r="D622" s="4"/>
@@ -21592,7 +21601,7 @@
       <c r="X622" s="2"/>
       <c r="Y622" s="2"/>
     </row>
-    <row r="623" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="623" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B623" s="5"/>
       <c r="C623" s="5"/>
       <c r="D623" s="4"/>
@@ -21618,7 +21627,7 @@
       <c r="X623" s="2"/>
       <c r="Y623" s="2"/>
     </row>
-    <row r="624" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="624" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B624" s="5"/>
       <c r="C624" s="5"/>
       <c r="D624" s="4"/>
@@ -21644,7 +21653,7 @@
       <c r="X624" s="2"/>
       <c r="Y624" s="2"/>
     </row>
-    <row r="625" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="625" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B625" s="5"/>
       <c r="C625" s="5"/>
       <c r="D625" s="4"/>
@@ -21670,7 +21679,7 @@
       <c r="X625" s="2"/>
       <c r="Y625" s="2"/>
     </row>
-    <row r="626" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="626" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B626" s="5"/>
       <c r="C626" s="5"/>
       <c r="D626" s="4"/>
@@ -21696,7 +21705,7 @@
       <c r="X626" s="2"/>
       <c r="Y626" s="2"/>
     </row>
-    <row r="627" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="627" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B627" s="5"/>
       <c r="C627" s="5"/>
       <c r="D627" s="4"/>
@@ -21722,7 +21731,7 @@
       <c r="X627" s="2"/>
       <c r="Y627" s="2"/>
     </row>
-    <row r="628" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="628" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B628" s="5"/>
       <c r="C628" s="5"/>
       <c r="D628" s="4"/>
@@ -21748,7 +21757,7 @@
       <c r="X628" s="2"/>
       <c r="Y628" s="2"/>
     </row>
-    <row r="629" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="629" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B629" s="5"/>
       <c r="C629" s="5"/>
       <c r="D629" s="4"/>
@@ -21774,7 +21783,7 @@
       <c r="X629" s="2"/>
       <c r="Y629" s="2"/>
     </row>
-    <row r="630" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="630" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B630" s="5"/>
       <c r="C630" s="5"/>
       <c r="D630" s="4"/>
@@ -21800,7 +21809,7 @@
       <c r="X630" s="2"/>
       <c r="Y630" s="2"/>
     </row>
-    <row r="631" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="631" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B631" s="5"/>
       <c r="C631" s="5"/>
       <c r="D631" s="4"/>
@@ -21826,7 +21835,7 @@
       <c r="X631" s="2"/>
       <c r="Y631" s="2"/>
     </row>
-    <row r="632" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="632" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B632" s="5"/>
       <c r="C632" s="5"/>
       <c r="D632" s="4"/>
@@ -21852,7 +21861,7 @@
       <c r="X632" s="2"/>
       <c r="Y632" s="2"/>
     </row>
-    <row r="633" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="633" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B633" s="5"/>
       <c r="C633" s="5"/>
       <c r="D633" s="4"/>
@@ -21878,7 +21887,7 @@
       <c r="X633" s="2"/>
       <c r="Y633" s="2"/>
     </row>
-    <row r="634" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="634" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B634" s="5"/>
       <c r="C634" s="5"/>
       <c r="D634" s="4"/>
@@ -21904,7 +21913,7 @@
       <c r="X634" s="2"/>
       <c r="Y634" s="2"/>
     </row>
-    <row r="635" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="635" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B635" s="5"/>
       <c r="C635" s="5"/>
       <c r="D635" s="4"/>
@@ -21930,7 +21939,7 @@
       <c r="X635" s="2"/>
       <c r="Y635" s="2"/>
     </row>
-    <row r="636" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="636" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B636" s="5"/>
       <c r="C636" s="5"/>
       <c r="D636" s="4"/>
@@ -21956,7 +21965,7 @@
       <c r="X636" s="2"/>
       <c r="Y636" s="2"/>
     </row>
-    <row r="637" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="637" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B637" s="5"/>
       <c r="C637" s="5"/>
       <c r="D637" s="4"/>
@@ -21982,7 +21991,7 @@
       <c r="X637" s="2"/>
       <c r="Y637" s="2"/>
     </row>
-    <row r="638" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="638" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B638" s="5"/>
       <c r="C638" s="5"/>
       <c r="D638" s="4"/>
@@ -22008,7 +22017,7 @@
       <c r="X638" s="2"/>
       <c r="Y638" s="2"/>
     </row>
-    <row r="639" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="639" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B639" s="5"/>
       <c r="C639" s="5"/>
       <c r="D639" s="4"/>
@@ -22034,7 +22043,7 @@
       <c r="X639" s="2"/>
       <c r="Y639" s="2"/>
     </row>
-    <row r="640" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="640" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B640" s="5"/>
       <c r="C640" s="5"/>
       <c r="D640" s="4"/>
@@ -22060,7 +22069,7 @@
       <c r="X640" s="2"/>
       <c r="Y640" s="2"/>
     </row>
-    <row r="641" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="641" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B641" s="5"/>
       <c r="C641" s="5"/>
       <c r="D641" s="4"/>
@@ -22086,7 +22095,7 @@
       <c r="X641" s="2"/>
       <c r="Y641" s="2"/>
     </row>
-    <row r="642" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="642" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B642" s="5"/>
       <c r="C642" s="5"/>
       <c r="D642" s="4"/>
@@ -22112,7 +22121,7 @@
       <c r="X642" s="2"/>
       <c r="Y642" s="2"/>
     </row>
-    <row r="643" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="643" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B643" s="5"/>
       <c r="C643" s="5"/>
       <c r="D643" s="4"/>
@@ -22138,7 +22147,7 @@
       <c r="X643" s="2"/>
       <c r="Y643" s="2"/>
     </row>
-    <row r="644" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="644" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B644" s="5"/>
       <c r="C644" s="5"/>
       <c r="D644" s="4"/>
@@ -22164,7 +22173,7 @@
       <c r="X644" s="2"/>
       <c r="Y644" s="2"/>
     </row>
-    <row r="645" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="645" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B645" s="5"/>
       <c r="C645" s="5"/>
       <c r="D645" s="4"/>
@@ -22190,7 +22199,7 @@
       <c r="X645" s="2"/>
       <c r="Y645" s="2"/>
     </row>
-    <row r="646" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="646" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B646" s="5"/>
       <c r="C646" s="5"/>
       <c r="D646" s="4"/>
@@ -22216,7 +22225,7 @@
       <c r="X646" s="2"/>
       <c r="Y646" s="2"/>
     </row>
-    <row r="647" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="647" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B647" s="5"/>
       <c r="C647" s="5"/>
       <c r="D647" s="4"/>
@@ -22242,7 +22251,7 @@
       <c r="X647" s="2"/>
       <c r="Y647" s="2"/>
     </row>
-    <row r="648" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="648" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B648" s="5"/>
       <c r="C648" s="5"/>
       <c r="D648" s="4"/>
@@ -22268,7 +22277,7 @@
       <c r="X648" s="2"/>
       <c r="Y648" s="2"/>
     </row>
-    <row r="649" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="649" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B649" s="5"/>
       <c r="C649" s="5"/>
       <c r="D649" s="4"/>
@@ -22294,7 +22303,7 @@
       <c r="X649" s="2"/>
       <c r="Y649" s="2"/>
     </row>
-    <row r="650" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="650" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B650" s="5"/>
       <c r="C650" s="5"/>
       <c r="D650" s="4"/>
@@ -22320,7 +22329,7 @@
       <c r="X650" s="2"/>
       <c r="Y650" s="2"/>
     </row>
-    <row r="651" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="651" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B651" s="5"/>
       <c r="C651" s="5"/>
       <c r="D651" s="4"/>
@@ -22346,7 +22355,7 @@
       <c r="X651" s="2"/>
       <c r="Y651" s="2"/>
     </row>
-    <row r="652" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="652" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B652" s="5"/>
       <c r="C652" s="5"/>
       <c r="D652" s="4"/>
@@ -22372,7 +22381,7 @@
       <c r="X652" s="2"/>
       <c r="Y652" s="2"/>
     </row>
-    <row r="653" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="653" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B653" s="5"/>
       <c r="C653" s="5"/>
       <c r="D653" s="4"/>
@@ -22398,7 +22407,7 @@
       <c r="X653" s="2"/>
       <c r="Y653" s="2"/>
     </row>
-    <row r="654" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="654" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B654" s="5"/>
       <c r="C654" s="5"/>
       <c r="D654" s="4"/>
@@ -22424,7 +22433,7 @@
       <c r="X654" s="2"/>
       <c r="Y654" s="2"/>
     </row>
-    <row r="655" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="655" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B655" s="5"/>
       <c r="C655" s="5"/>
       <c r="D655" s="4"/>
@@ -22450,7 +22459,7 @@
       <c r="X655" s="2"/>
       <c r="Y655" s="2"/>
     </row>
-    <row r="656" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="656" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B656" s="5"/>
       <c r="C656" s="5"/>
       <c r="D656" s="4"/>
@@ -22476,7 +22485,7 @@
       <c r="X656" s="2"/>
       <c r="Y656" s="2"/>
     </row>
-    <row r="657" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="657" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B657" s="5"/>
       <c r="C657" s="5"/>
       <c r="D657" s="4"/>
@@ -22502,7 +22511,7 @@
       <c r="X657" s="2"/>
       <c r="Y657" s="2"/>
     </row>
-    <row r="658" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="658" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B658" s="5"/>
       <c r="C658" s="5"/>
       <c r="D658" s="4"/>
@@ -22528,7 +22537,7 @@
       <c r="X658" s="2"/>
       <c r="Y658" s="2"/>
     </row>
-    <row r="659" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="659" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B659" s="5"/>
       <c r="C659" s="5"/>
       <c r="D659" s="4"/>
@@ -22554,7 +22563,7 @@
       <c r="X659" s="2"/>
       <c r="Y659" s="2"/>
     </row>
-    <row r="660" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="660" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B660" s="5"/>
       <c r="C660" s="5"/>
       <c r="D660" s="4"/>
@@ -22580,7 +22589,7 @@
       <c r="X660" s="2"/>
       <c r="Y660" s="2"/>
     </row>
-    <row r="661" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="661" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B661" s="5"/>
       <c r="C661" s="5"/>
       <c r="D661" s="4"/>
@@ -22606,7 +22615,7 @@
       <c r="X661" s="2"/>
       <c r="Y661" s="2"/>
     </row>
-    <row r="662" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="662" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B662" s="5"/>
       <c r="C662" s="5"/>
       <c r="D662" s="4"/>
@@ -22632,7 +22641,7 @@
       <c r="X662" s="2"/>
       <c r="Y662" s="2"/>
     </row>
-    <row r="663" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="663" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B663" s="5"/>
       <c r="C663" s="5"/>
       <c r="D663" s="4"/>
@@ -22658,7 +22667,7 @@
       <c r="X663" s="2"/>
       <c r="Y663" s="2"/>
     </row>
-    <row r="664" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="664" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B664" s="5"/>
       <c r="C664" s="5"/>
       <c r="D664" s="4"/>
@@ -22684,7 +22693,7 @@
       <c r="X664" s="2"/>
       <c r="Y664" s="2"/>
     </row>
-    <row r="665" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="665" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B665" s="5"/>
       <c r="C665" s="5"/>
       <c r="D665" s="4"/>
@@ -22710,7 +22719,7 @@
       <c r="X665" s="2"/>
       <c r="Y665" s="2"/>
     </row>
-    <row r="666" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="666" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B666" s="5"/>
       <c r="C666" s="5"/>
       <c r="D666" s="4"/>
@@ -22736,7 +22745,7 @@
       <c r="X666" s="2"/>
       <c r="Y666" s="2"/>
     </row>
-    <row r="667" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="667" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B667" s="5"/>
       <c r="C667" s="5"/>
       <c r="D667" s="4"/>
@@ -22762,7 +22771,7 @@
       <c r="X667" s="2"/>
       <c r="Y667" s="2"/>
     </row>
-    <row r="668" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="668" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B668" s="5"/>
       <c r="C668" s="5"/>
       <c r="D668" s="4"/>
@@ -22788,7 +22797,7 @@
       <c r="X668" s="2"/>
       <c r="Y668" s="2"/>
     </row>
-    <row r="669" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="669" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B669" s="5"/>
       <c r="C669" s="5"/>
       <c r="D669" s="4"/>
@@ -22814,7 +22823,7 @@
       <c r="X669" s="2"/>
       <c r="Y669" s="2"/>
     </row>
-    <row r="670" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="670" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B670" s="5"/>
       <c r="C670" s="5"/>
       <c r="D670" s="4"/>
@@ -22840,7 +22849,7 @@
       <c r="X670" s="2"/>
       <c r="Y670" s="2"/>
     </row>
-    <row r="671" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="671" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B671" s="5"/>
       <c r="C671" s="5"/>
       <c r="D671" s="4"/>
@@ -22866,7 +22875,7 @@
       <c r="X671" s="2"/>
       <c r="Y671" s="2"/>
     </row>
-    <row r="672" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="672" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B672" s="5"/>
       <c r="C672" s="5"/>
       <c r="D672" s="4"/>
@@ -22892,7 +22901,7 @@
       <c r="X672" s="2"/>
       <c r="Y672" s="2"/>
     </row>
-    <row r="673" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="673" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B673" s="5"/>
       <c r="C673" s="5"/>
       <c r="D673" s="4"/>
@@ -22918,7 +22927,7 @@
       <c r="X673" s="2"/>
       <c r="Y673" s="2"/>
     </row>
-    <row r="674" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="674" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B674" s="5"/>
       <c r="C674" s="5"/>
       <c r="D674" s="4"/>
@@ -22944,7 +22953,7 @@
       <c r="X674" s="2"/>
       <c r="Y674" s="2"/>
     </row>
-    <row r="675" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="675" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B675" s="5"/>
       <c r="C675" s="5"/>
       <c r="D675" s="4"/>
@@ -22970,7 +22979,7 @@
       <c r="X675" s="2"/>
       <c r="Y675" s="2"/>
     </row>
-    <row r="676" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="676" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B676" s="5"/>
       <c r="C676" s="5"/>
       <c r="D676" s="4"/>
@@ -22996,7 +23005,7 @@
       <c r="X676" s="2"/>
       <c r="Y676" s="2"/>
     </row>
-    <row r="677" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="677" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B677" s="5"/>
       <c r="C677" s="5"/>
       <c r="D677" s="4"/>
@@ -23022,7 +23031,7 @@
       <c r="X677" s="2"/>
       <c r="Y677" s="2"/>
     </row>
-    <row r="678" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="678" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B678" s="5"/>
       <c r="C678" s="5"/>
       <c r="D678" s="4"/>
@@ -23048,7 +23057,7 @@
       <c r="X678" s="2"/>
       <c r="Y678" s="2"/>
     </row>
-    <row r="679" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="679" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B679" s="5"/>
       <c r="C679" s="5"/>
       <c r="D679" s="4"/>
@@ -23074,7 +23083,7 @@
       <c r="X679" s="2"/>
       <c r="Y679" s="2"/>
     </row>
-    <row r="680" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="680" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B680" s="5"/>
       <c r="C680" s="5"/>
       <c r="D680" s="4"/>
@@ -23100,7 +23109,7 @@
       <c r="X680" s="2"/>
       <c r="Y680" s="2"/>
     </row>
-    <row r="681" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="681" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B681" s="5"/>
       <c r="C681" s="5"/>
       <c r="D681" s="4"/>
@@ -23126,7 +23135,7 @@
       <c r="X681" s="2"/>
       <c r="Y681" s="2"/>
     </row>
-    <row r="682" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="682" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B682" s="5"/>
       <c r="C682" s="5"/>
       <c r="D682" s="4"/>
@@ -23152,7 +23161,7 @@
       <c r="X682" s="2"/>
       <c r="Y682" s="2"/>
     </row>
-    <row r="683" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="683" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B683" s="5"/>
       <c r="C683" s="5"/>
       <c r="D683" s="4"/>
@@ -23178,7 +23187,7 @@
       <c r="X683" s="2"/>
       <c r="Y683" s="2"/>
     </row>
-    <row r="684" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="684" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B684" s="5"/>
       <c r="C684" s="5"/>
       <c r="D684" s="4"/>
@@ -23204,7 +23213,7 @@
       <c r="X684" s="2"/>
       <c r="Y684" s="2"/>
     </row>
-    <row r="685" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="685" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B685" s="5"/>
       <c r="C685" s="5"/>
       <c r="D685" s="4"/>
@@ -23230,7 +23239,7 @@
       <c r="X685" s="2"/>
       <c r="Y685" s="2"/>
     </row>
-    <row r="686" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="686" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B686" s="5"/>
       <c r="C686" s="5"/>
       <c r="D686" s="4"/>
@@ -23256,7 +23265,7 @@
       <c r="X686" s="2"/>
       <c r="Y686" s="2"/>
     </row>
-    <row r="687" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="687" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B687" s="5"/>
       <c r="C687" s="5"/>
       <c r="D687" s="4"/>
@@ -23282,7 +23291,7 @@
       <c r="X687" s="2"/>
       <c r="Y687" s="2"/>
     </row>
-    <row r="688" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="688" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B688" s="5"/>
       <c r="C688" s="5"/>
       <c r="D688" s="4"/>
@@ -23308,7 +23317,7 @@
       <c r="X688" s="2"/>
       <c r="Y688" s="2"/>
     </row>
-    <row r="689" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="689" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B689" s="5"/>
       <c r="C689" s="5"/>
       <c r="D689" s="4"/>
@@ -23334,7 +23343,7 @@
       <c r="X689" s="2"/>
       <c r="Y689" s="2"/>
     </row>
-    <row r="690" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="690" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B690" s="5"/>
       <c r="C690" s="5"/>
       <c r="D690" s="4"/>
@@ -23360,7 +23369,7 @@
       <c r="X690" s="2"/>
       <c r="Y690" s="2"/>
     </row>
-    <row r="691" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="691" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B691" s="5"/>
       <c r="C691" s="5"/>
       <c r="D691" s="4"/>
@@ -23386,7 +23395,7 @@
       <c r="X691" s="2"/>
       <c r="Y691" s="2"/>
     </row>
-    <row r="692" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="692" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B692" s="5"/>
       <c r="C692" s="5"/>
       <c r="D692" s="4"/>
@@ -23412,7 +23421,7 @@
       <c r="X692" s="2"/>
       <c r="Y692" s="2"/>
     </row>
-    <row r="693" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="693" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B693" s="5"/>
       <c r="C693" s="5"/>
       <c r="D693" s="4"/>
@@ -23438,7 +23447,7 @@
       <c r="X693" s="2"/>
       <c r="Y693" s="2"/>
     </row>
-    <row r="694" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="694" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B694" s="5"/>
       <c r="C694" s="5"/>
       <c r="D694" s="4"/>
@@ -23464,7 +23473,7 @@
       <c r="X694" s="2"/>
       <c r="Y694" s="2"/>
     </row>
-    <row r="695" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="695" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B695" s="5"/>
       <c r="C695" s="5"/>
       <c r="D695" s="4"/>
@@ -23490,7 +23499,7 @@
       <c r="X695" s="2"/>
       <c r="Y695" s="2"/>
     </row>
-    <row r="696" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="696" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B696" s="5"/>
       <c r="C696" s="5"/>
       <c r="D696" s="4"/>
@@ -23516,7 +23525,7 @@
       <c r="X696" s="2"/>
       <c r="Y696" s="2"/>
     </row>
-    <row r="697" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="697" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B697" s="5"/>
       <c r="C697" s="5"/>
       <c r="D697" s="4"/>
@@ -23542,7 +23551,7 @@
       <c r="X697" s="2"/>
       <c r="Y697" s="2"/>
     </row>
-    <row r="698" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="698" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B698" s="5"/>
       <c r="C698" s="5"/>
       <c r="D698" s="4"/>
@@ -23568,7 +23577,7 @@
       <c r="X698" s="2"/>
       <c r="Y698" s="2"/>
     </row>
-    <row r="699" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="699" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B699" s="5"/>
       <c r="C699" s="5"/>
       <c r="D699" s="4"/>
@@ -23594,7 +23603,7 @@
       <c r="X699" s="2"/>
       <c r="Y699" s="2"/>
     </row>
-    <row r="700" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="700" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B700" s="5"/>
       <c r="C700" s="5"/>
       <c r="D700" s="4"/>
@@ -23620,7 +23629,7 @@
       <c r="X700" s="2"/>
       <c r="Y700" s="2"/>
     </row>
-    <row r="701" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="701" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B701" s="5"/>
       <c r="C701" s="5"/>
       <c r="D701" s="4"/>
@@ -23646,7 +23655,7 @@
       <c r="X701" s="2"/>
       <c r="Y701" s="2"/>
     </row>
-    <row r="702" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="702" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B702" s="5"/>
       <c r="C702" s="5"/>
       <c r="D702" s="4"/>
@@ -23672,7 +23681,7 @@
       <c r="X702" s="2"/>
       <c r="Y702" s="2"/>
     </row>
-    <row r="703" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="703" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B703" s="5"/>
       <c r="C703" s="5"/>
       <c r="D703" s="4"/>
@@ -23698,7 +23707,7 @@
       <c r="X703" s="2"/>
       <c r="Y703" s="2"/>
     </row>
-    <row r="704" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="704" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B704" s="5"/>
       <c r="C704" s="5"/>
       <c r="D704" s="4"/>
@@ -23724,7 +23733,7 @@
       <c r="X704" s="2"/>
       <c r="Y704" s="2"/>
     </row>
-    <row r="705" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="705" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B705" s="5"/>
       <c r="C705" s="5"/>
       <c r="D705" s="4"/>
@@ -23750,7 +23759,7 @@
       <c r="X705" s="2"/>
       <c r="Y705" s="2"/>
     </row>
-    <row r="706" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="706" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B706" s="5"/>
       <c r="C706" s="5"/>
       <c r="D706" s="4"/>
@@ -23776,7 +23785,7 @@
       <c r="X706" s="2"/>
       <c r="Y706" s="2"/>
     </row>
-    <row r="707" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="707" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B707" s="5"/>
       <c r="C707" s="5"/>
       <c r="D707" s="4"/>
@@ -23802,7 +23811,7 @@
       <c r="X707" s="2"/>
       <c r="Y707" s="2"/>
     </row>
-    <row r="708" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="708" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B708" s="5"/>
       <c r="C708" s="5"/>
       <c r="D708" s="4"/>
@@ -23828,7 +23837,7 @@
       <c r="X708" s="2"/>
       <c r="Y708" s="2"/>
     </row>
-    <row r="709" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="709" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B709" s="5"/>
       <c r="C709" s="5"/>
       <c r="D709" s="4"/>
@@ -23854,7 +23863,7 @@
       <c r="X709" s="2"/>
       <c r="Y709" s="2"/>
     </row>
-    <row r="710" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="710" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B710" s="5"/>
       <c r="C710" s="5"/>
       <c r="D710" s="4"/>
@@ -23880,7 +23889,7 @@
       <c r="X710" s="2"/>
       <c r="Y710" s="2"/>
     </row>
-    <row r="711" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="711" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B711" s="5"/>
       <c r="C711" s="5"/>
       <c r="D711" s="4"/>
@@ -23906,7 +23915,7 @@
       <c r="X711" s="2"/>
       <c r="Y711" s="2"/>
     </row>
-    <row r="712" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="712" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B712" s="5"/>
       <c r="C712" s="5"/>
       <c r="D712" s="4"/>
@@ -23932,7 +23941,7 @@
       <c r="X712" s="2"/>
       <c r="Y712" s="2"/>
     </row>
-    <row r="713" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="713" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B713" s="5"/>
       <c r="C713" s="5"/>
       <c r="D713" s="4"/>
@@ -23958,7 +23967,7 @@
       <c r="X713" s="2"/>
       <c r="Y713" s="2"/>
     </row>
-    <row r="714" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="714" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B714" s="5"/>
       <c r="C714" s="5"/>
       <c r="D714" s="4"/>
@@ -23984,7 +23993,7 @@
       <c r="X714" s="2"/>
       <c r="Y714" s="2"/>
     </row>
-    <row r="715" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="715" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B715" s="5"/>
       <c r="C715" s="5"/>
       <c r="D715" s="4"/>
@@ -24010,7 +24019,7 @@
       <c r="X715" s="2"/>
       <c r="Y715" s="2"/>
     </row>
-    <row r="716" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="716" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B716" s="5"/>
       <c r="C716" s="5"/>
       <c r="D716" s="4"/>
@@ -24036,7 +24045,7 @@
       <c r="X716" s="2"/>
       <c r="Y716" s="2"/>
     </row>
-    <row r="717" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="717" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B717" s="5"/>
       <c r="C717" s="5"/>
       <c r="D717" s="4"/>
@@ -24062,7 +24071,7 @@
       <c r="X717" s="2"/>
       <c r="Y717" s="2"/>
     </row>
-    <row r="718" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="718" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B718" s="5"/>
       <c r="C718" s="5"/>
       <c r="D718" s="4"/>
@@ -24088,7 +24097,7 @@
       <c r="X718" s="2"/>
       <c r="Y718" s="2"/>
     </row>
-    <row r="719" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="719" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B719" s="5"/>
       <c r="C719" s="5"/>
       <c r="D719" s="4"/>
@@ -24114,7 +24123,7 @@
       <c r="X719" s="2"/>
       <c r="Y719" s="2"/>
     </row>
-    <row r="720" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="720" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B720" s="5"/>
       <c r="C720" s="5"/>
       <c r="D720" s="4"/>
@@ -24140,7 +24149,7 @@
       <c r="X720" s="2"/>
       <c r="Y720" s="2"/>
     </row>
-    <row r="721" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="721" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B721" s="5"/>
       <c r="C721" s="5"/>
       <c r="D721" s="4"/>
@@ -24166,7 +24175,7 @@
       <c r="X721" s="2"/>
       <c r="Y721" s="2"/>
     </row>
-    <row r="722" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="722" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B722" s="5"/>
       <c r="C722" s="5"/>
       <c r="D722" s="4"/>
@@ -24192,7 +24201,7 @@
       <c r="X722" s="2"/>
       <c r="Y722" s="2"/>
     </row>
-    <row r="723" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="723" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B723" s="5"/>
       <c r="C723" s="5"/>
       <c r="D723" s="4"/>
@@ -24218,7 +24227,7 @@
       <c r="X723" s="2"/>
       <c r="Y723" s="2"/>
     </row>
-    <row r="724" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="724" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B724" s="5"/>
       <c r="C724" s="5"/>
       <c r="D724" s="4"/>
@@ -24244,7 +24253,7 @@
       <c r="X724" s="2"/>
       <c r="Y724" s="2"/>
     </row>
-    <row r="725" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="725" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B725" s="5"/>
       <c r="C725" s="5"/>
       <c r="D725" s="4"/>
@@ -24270,7 +24279,7 @@
       <c r="X725" s="2"/>
       <c r="Y725" s="2"/>
     </row>
-    <row r="726" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="726" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B726" s="5"/>
       <c r="C726" s="5"/>
       <c r="D726" s="4"/>
@@ -24296,7 +24305,7 @@
       <c r="X726" s="2"/>
       <c r="Y726" s="2"/>
     </row>
-    <row r="727" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="727" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B727" s="5"/>
       <c r="C727" s="5"/>
       <c r="D727" s="4"/>
@@ -24322,7 +24331,7 @@
       <c r="X727" s="2"/>
       <c r="Y727" s="2"/>
     </row>
-    <row r="728" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="728" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B728" s="5"/>
       <c r="C728" s="5"/>
       <c r="D728" s="4"/>
@@ -24348,7 +24357,7 @@
       <c r="X728" s="2"/>
       <c r="Y728" s="2"/>
     </row>
-    <row r="729" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="729" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B729" s="5"/>
       <c r="C729" s="5"/>
       <c r="D729" s="4"/>
@@ -24374,7 +24383,7 @@
       <c r="X729" s="2"/>
       <c r="Y729" s="2"/>
     </row>
-    <row r="730" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="730" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B730" s="5"/>
       <c r="C730" s="5"/>
       <c r="D730" s="4"/>
@@ -24400,7 +24409,7 @@
       <c r="X730" s="2"/>
       <c r="Y730" s="2"/>
     </row>
-    <row r="731" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="731" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B731" s="5"/>
       <c r="C731" s="5"/>
       <c r="D731" s="4"/>
@@ -24426,7 +24435,7 @@
       <c r="X731" s="2"/>
       <c r="Y731" s="2"/>
     </row>
-    <row r="732" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="732" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B732" s="5"/>
       <c r="C732" s="5"/>
       <c r="D732" s="4"/>
@@ -24452,7 +24461,7 @@
       <c r="X732" s="2"/>
       <c r="Y732" s="2"/>
     </row>
-    <row r="733" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="733" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B733" s="5"/>
       <c r="C733" s="5"/>
       <c r="D733" s="4"/>
@@ -24478,7 +24487,7 @@
       <c r="X733" s="2"/>
       <c r="Y733" s="2"/>
     </row>
-    <row r="734" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="734" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B734" s="5"/>
       <c r="C734" s="5"/>
       <c r="D734" s="4"/>
@@ -24504,7 +24513,7 @@
       <c r="X734" s="2"/>
       <c r="Y734" s="2"/>
     </row>
-    <row r="735" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="735" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B735" s="5"/>
       <c r="C735" s="5"/>
       <c r="D735" s="4"/>
@@ -24530,7 +24539,7 @@
       <c r="X735" s="2"/>
       <c r="Y735" s="2"/>
     </row>
-    <row r="736" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="736" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B736" s="5"/>
       <c r="C736" s="5"/>
       <c r="D736" s="4"/>
@@ -24556,7 +24565,7 @@
       <c r="X736" s="2"/>
       <c r="Y736" s="2"/>
     </row>
-    <row r="737" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="737" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B737" s="5"/>
       <c r="C737" s="5"/>
       <c r="D737" s="4"/>
@@ -24582,7 +24591,7 @@
       <c r="X737" s="2"/>
       <c r="Y737" s="2"/>
     </row>
-    <row r="738" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="738" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B738" s="5"/>
       <c r="C738" s="5"/>
       <c r="D738" s="4"/>
@@ -24608,7 +24617,7 @@
       <c r="X738" s="2"/>
       <c r="Y738" s="2"/>
     </row>
-    <row r="739" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="739" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B739" s="5"/>
       <c r="C739" s="5"/>
       <c r="D739" s="4"/>
@@ -24634,7 +24643,7 @@
       <c r="X739" s="2"/>
       <c r="Y739" s="2"/>
     </row>
-    <row r="740" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="740" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B740" s="5"/>
       <c r="C740" s="5"/>
       <c r="D740" s="4"/>
@@ -24660,7 +24669,7 @@
       <c r="X740" s="2"/>
       <c r="Y740" s="2"/>
     </row>
-    <row r="741" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="741" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B741" s="5"/>
       <c r="C741" s="5"/>
       <c r="D741" s="4"/>
@@ -24686,7 +24695,7 @@
       <c r="X741" s="2"/>
       <c r="Y741" s="2"/>
     </row>
-    <row r="742" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="742" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B742" s="5"/>
       <c r="C742" s="5"/>
       <c r="D742" s="4"/>
@@ -24712,7 +24721,7 @@
       <c r="X742" s="2"/>
       <c r="Y742" s="2"/>
     </row>
-    <row r="743" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="743" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B743" s="5"/>
       <c r="C743" s="5"/>
       <c r="D743" s="4"/>
@@ -24738,7 +24747,7 @@
       <c r="X743" s="2"/>
       <c r="Y743" s="2"/>
     </row>
-    <row r="744" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="744" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B744" s="5"/>
       <c r="C744" s="5"/>
       <c r="D744" s="4"/>
@@ -24764,7 +24773,7 @@
       <c r="X744" s="2"/>
       <c r="Y744" s="2"/>
     </row>
-    <row r="745" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="745" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B745" s="5"/>
       <c r="C745" s="5"/>
       <c r="D745" s="4"/>
@@ -24790,7 +24799,7 @@
       <c r="X745" s="2"/>
       <c r="Y745" s="2"/>
     </row>
-    <row r="746" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="746" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B746" s="5"/>
       <c r="C746" s="5"/>
       <c r="D746" s="4"/>
@@ -24816,7 +24825,7 @@
       <c r="X746" s="2"/>
       <c r="Y746" s="2"/>
     </row>
-    <row r="747" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="747" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B747" s="5"/>
       <c r="C747" s="5"/>
       <c r="D747" s="4"/>
@@ -24842,7 +24851,7 @@
       <c r="X747" s="2"/>
       <c r="Y747" s="2"/>
     </row>
-    <row r="748" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="748" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B748" s="5"/>
       <c r="C748" s="5"/>
       <c r="D748" s="4"/>
@@ -24868,7 +24877,7 @@
       <c r="X748" s="2"/>
       <c r="Y748" s="2"/>
     </row>
-    <row r="749" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="749" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B749" s="5"/>
       <c r="C749" s="5"/>
       <c r="D749" s="4"/>
@@ -24894,7 +24903,7 @@
       <c r="X749" s="2"/>
       <c r="Y749" s="2"/>
     </row>
-    <row r="750" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="750" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B750" s="5"/>
       <c r="C750" s="5"/>
       <c r="D750" s="4"/>
@@ -24920,7 +24929,7 @@
       <c r="X750" s="2"/>
       <c r="Y750" s="2"/>
     </row>
-    <row r="751" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="751" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B751" s="5"/>
       <c r="C751" s="5"/>
       <c r="D751" s="4"/>
@@ -24946,7 +24955,7 @@
       <c r="X751" s="2"/>
       <c r="Y751" s="2"/>
     </row>
-    <row r="752" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="752" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B752" s="5"/>
       <c r="C752" s="5"/>
       <c r="D752" s="4"/>
@@ -24972,7 +24981,7 @@
       <c r="X752" s="2"/>
       <c r="Y752" s="2"/>
     </row>
-    <row r="753" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="753" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B753" s="5"/>
       <c r="C753" s="5"/>
       <c r="D753" s="4"/>
@@ -24998,7 +25007,7 @@
       <c r="X753" s="2"/>
       <c r="Y753" s="2"/>
     </row>
-    <row r="754" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="754" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B754" s="5"/>
       <c r="C754" s="5"/>
       <c r="D754" s="4"/>
@@ -25024,7 +25033,7 @@
       <c r="X754" s="2"/>
       <c r="Y754" s="2"/>
     </row>
-    <row r="755" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="755" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B755" s="5"/>
       <c r="C755" s="5"/>
       <c r="D755" s="4"/>
@@ -25050,7 +25059,7 @@
       <c r="X755" s="2"/>
       <c r="Y755" s="2"/>
     </row>
-    <row r="756" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="756" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B756" s="5"/>
       <c r="C756" s="5"/>
       <c r="D756" s="4"/>
@@ -25076,7 +25085,7 @@
       <c r="X756" s="2"/>
       <c r="Y756" s="2"/>
     </row>
-    <row r="757" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="757" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B757" s="5"/>
       <c r="C757" s="5"/>
       <c r="D757" s="4"/>
@@ -25102,7 +25111,7 @@
       <c r="X757" s="2"/>
       <c r="Y757" s="2"/>
     </row>
-    <row r="758" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="758" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B758" s="5"/>
       <c r="C758" s="5"/>
       <c r="D758" s="4"/>
@@ -25128,7 +25137,7 @@
       <c r="X758" s="2"/>
       <c r="Y758" s="2"/>
     </row>
-    <row r="759" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="759" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B759" s="5"/>
       <c r="C759" s="5"/>
       <c r="D759" s="4"/>
@@ -25154,7 +25163,7 @@
       <c r="X759" s="2"/>
       <c r="Y759" s="2"/>
     </row>
-    <row r="760" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="760" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B760" s="5"/>
       <c r="C760" s="5"/>
       <c r="D760" s="4"/>
@@ -25180,7 +25189,7 @@
       <c r="X760" s="2"/>
       <c r="Y760" s="2"/>
     </row>
-    <row r="761" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="761" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B761" s="5"/>
       <c r="C761" s="5"/>
       <c r="D761" s="4"/>
@@ -25206,7 +25215,7 @@
       <c r="X761" s="2"/>
       <c r="Y761" s="2"/>
     </row>
-    <row r="762" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="762" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B762" s="5"/>
       <c r="C762" s="5"/>
       <c r="D762" s="4"/>
@@ -25232,7 +25241,7 @@
       <c r="X762" s="2"/>
       <c r="Y762" s="2"/>
     </row>
-    <row r="763" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="763" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B763" s="5"/>
       <c r="C763" s="5"/>
       <c r="D763" s="4"/>
@@ -25258,7 +25267,7 @@
       <c r="X763" s="2"/>
       <c r="Y763" s="2"/>
     </row>
-    <row r="764" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="764" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B764" s="5"/>
       <c r="C764" s="5"/>
       <c r="D764" s="4"/>
@@ -25284,7 +25293,7 @@
       <c r="X764" s="2"/>
       <c r="Y764" s="2"/>
     </row>
-    <row r="765" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="765" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B765" s="5"/>
       <c r="C765" s="5"/>
       <c r="D765" s="4"/>
@@ -25310,7 +25319,7 @@
       <c r="X765" s="2"/>
       <c r="Y765" s="2"/>
     </row>
-    <row r="766" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="766" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B766" s="5"/>
       <c r="C766" s="5"/>
       <c r="D766" s="4"/>
@@ -25336,7 +25345,7 @@
       <c r="X766" s="2"/>
       <c r="Y766" s="2"/>
     </row>
-    <row r="767" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="767" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B767" s="5"/>
       <c r="C767" s="5"/>
       <c r="D767" s="4"/>
@@ -25362,7 +25371,7 @@
       <c r="X767" s="2"/>
       <c r="Y767" s="2"/>
     </row>
-    <row r="768" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="768" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B768" s="5"/>
       <c r="C768" s="5"/>
       <c r="D768" s="4"/>
@@ -25388,7 +25397,7 @@
       <c r="X768" s="2"/>
       <c r="Y768" s="2"/>
     </row>
-    <row r="769" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="769" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B769" s="5"/>
       <c r="C769" s="5"/>
       <c r="D769" s="4"/>
@@ -25414,7 +25423,7 @@
       <c r="X769" s="2"/>
       <c r="Y769" s="2"/>
     </row>
-    <row r="770" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="770" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B770" s="5"/>
       <c r="C770" s="5"/>
       <c r="D770" s="4"/>
@@ -25440,7 +25449,7 @@
       <c r="X770" s="2"/>
       <c r="Y770" s="2"/>
     </row>
-    <row r="771" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="771" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B771" s="5"/>
       <c r="C771" s="5"/>
       <c r="D771" s="4"/>
@@ -25466,7 +25475,7 @@
       <c r="X771" s="2"/>
       <c r="Y771" s="2"/>
     </row>
-    <row r="772" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="772" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B772" s="5"/>
       <c r="C772" s="5"/>
       <c r="D772" s="4"/>
@@ -25492,7 +25501,7 @@
       <c r="X772" s="2"/>
       <c r="Y772" s="2"/>
     </row>
-    <row r="773" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="773" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B773" s="5"/>
       <c r="C773" s="5"/>
       <c r="D773" s="4"/>
@@ -25518,7 +25527,7 @@
       <c r="X773" s="2"/>
       <c r="Y773" s="2"/>
     </row>
-    <row r="774" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="774" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B774" s="5"/>
       <c r="C774" s="5"/>
       <c r="D774" s="4"/>
@@ -25544,7 +25553,7 @@
       <c r="X774" s="2"/>
       <c r="Y774" s="2"/>
     </row>
-    <row r="775" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="775" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B775" s="5"/>
       <c r="C775" s="5"/>
       <c r="D775" s="4"/>
@@ -25570,7 +25579,7 @@
       <c r="X775" s="2"/>
       <c r="Y775" s="2"/>
     </row>
-    <row r="776" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="776" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B776" s="5"/>
       <c r="C776" s="5"/>
       <c r="D776" s="4"/>
@@ -25596,7 +25605,7 @@
       <c r="X776" s="2"/>
       <c r="Y776" s="2"/>
     </row>
-    <row r="777" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="777" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B777" s="5"/>
       <c r="C777" s="5"/>
       <c r="D777" s="4"/>
@@ -25622,7 +25631,7 @@
       <c r="X777" s="2"/>
       <c r="Y777" s="2"/>
     </row>
-    <row r="778" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="778" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B778" s="5"/>
       <c r="C778" s="5"/>
       <c r="D778" s="4"/>
@@ -25648,7 +25657,7 @@
       <c r="X778" s="2"/>
       <c r="Y778" s="2"/>
     </row>
-    <row r="779" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="779" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B779" s="5"/>
       <c r="C779" s="5"/>
       <c r="D779" s="4"/>
@@ -25674,7 +25683,7 @@
       <c r="X779" s="2"/>
       <c r="Y779" s="2"/>
     </row>
-    <row r="780" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="780" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B780" s="5"/>
       <c r="C780" s="5"/>
       <c r="D780" s="4"/>
@@ -25700,7 +25709,7 @@
       <c r="X780" s="2"/>
       <c r="Y780" s="2"/>
     </row>
-    <row r="781" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="781" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B781" s="5"/>
       <c r="C781" s="5"/>
       <c r="D781" s="4"/>
@@ -25726,7 +25735,7 @@
       <c r="X781" s="2"/>
       <c r="Y781" s="2"/>
     </row>
-    <row r="782" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="782" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B782" s="5"/>
       <c r="C782" s="5"/>
       <c r="D782" s="4"/>
@@ -25752,7 +25761,7 @@
       <c r="X782" s="2"/>
       <c r="Y782" s="2"/>
     </row>
-    <row r="783" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="783" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B783" s="5"/>
       <c r="C783" s="5"/>
       <c r="D783" s="4"/>
@@ -25778,7 +25787,7 @@
       <c r="X783" s="2"/>
       <c r="Y783" s="2"/>
     </row>
-    <row r="784" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="784" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B784" s="5"/>
       <c r="C784" s="5"/>
       <c r="D784" s="4"/>
@@ -25804,7 +25813,7 @@
       <c r="X784" s="2"/>
       <c r="Y784" s="2"/>
     </row>
-    <row r="785" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="785" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B785" s="5"/>
       <c r="C785" s="5"/>
       <c r="D785" s="4"/>
@@ -25830,7 +25839,7 @@
       <c r="X785" s="2"/>
       <c r="Y785" s="2"/>
     </row>
-    <row r="786" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="786" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B786" s="5"/>
       <c r="C786" s="5"/>
       <c r="D786" s="4"/>
@@ -25856,7 +25865,7 @@
       <c r="X786" s="2"/>
       <c r="Y786" s="2"/>
     </row>
-    <row r="787" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="787" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B787" s="5"/>
       <c r="C787" s="5"/>
       <c r="D787" s="4"/>
@@ -25882,7 +25891,7 @@
       <c r="X787" s="2"/>
       <c r="Y787" s="2"/>
     </row>
-    <row r="788" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="788" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B788" s="5"/>
       <c r="C788" s="5"/>
       <c r="D788" s="4"/>
@@ -25908,7 +25917,7 @@
       <c r="X788" s="2"/>
       <c r="Y788" s="2"/>
     </row>
-    <row r="789" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="789" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B789" s="5"/>
       <c r="C789" s="5"/>
       <c r="D789" s="4"/>
@@ -25934,7 +25943,7 @@
       <c r="X789" s="2"/>
       <c r="Y789" s="2"/>
     </row>
-    <row r="790" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="790" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B790" s="5"/>
       <c r="C790" s="5"/>
       <c r="D790" s="4"/>
@@ -25960,7 +25969,7 @@
       <c r="X790" s="2"/>
       <c r="Y790" s="2"/>
     </row>
-    <row r="791" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="791" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B791" s="5"/>
       <c r="C791" s="5"/>
       <c r="D791" s="4"/>
@@ -25986,7 +25995,7 @@
       <c r="X791" s="2"/>
       <c r="Y791" s="2"/>
     </row>
-    <row r="792" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="792" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B792" s="5"/>
       <c r="C792" s="5"/>
       <c r="D792" s="4"/>
@@ -26012,7 +26021,7 @@
       <c r="X792" s="2"/>
       <c r="Y792" s="2"/>
     </row>
-    <row r="793" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="793" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B793" s="5"/>
       <c r="C793" s="5"/>
       <c r="D793" s="4"/>
@@ -26038,7 +26047,7 @@
       <c r="X793" s="2"/>
       <c r="Y793" s="2"/>
     </row>
-    <row r="794" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="794" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B794" s="5"/>
       <c r="C794" s="5"/>
       <c r="D794" s="4"/>
@@ -26064,7 +26073,7 @@
       <c r="X794" s="2"/>
       <c r="Y794" s="2"/>
     </row>
-    <row r="795" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="795" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B795" s="5"/>
       <c r="C795" s="5"/>
       <c r="D795" s="4"/>
@@ -26090,7 +26099,7 @@
       <c r="X795" s="2"/>
       <c r="Y795" s="2"/>
     </row>
-    <row r="796" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="796" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B796" s="5"/>
       <c r="C796" s="5"/>
       <c r="D796" s="4"/>
@@ -26116,7 +26125,7 @@
       <c r="X796" s="2"/>
       <c r="Y796" s="2"/>
     </row>
-    <row r="797" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="797" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B797" s="5"/>
       <c r="C797" s="5"/>
       <c r="D797" s="4"/>
@@ -26142,7 +26151,7 @@
       <c r="X797" s="2"/>
       <c r="Y797" s="2"/>
     </row>
-    <row r="798" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="798" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B798" s="5"/>
       <c r="C798" s="5"/>
       <c r="D798" s="4"/>
@@ -26168,7 +26177,7 @@
       <c r="X798" s="2"/>
       <c r="Y798" s="2"/>
     </row>
-    <row r="799" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="799" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B799" s="5"/>
       <c r="C799" s="5"/>
       <c r="D799" s="4"/>
@@ -26194,7 +26203,7 @@
       <c r="X799" s="2"/>
       <c r="Y799" s="2"/>
     </row>
-    <row r="800" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="800" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B800" s="5"/>
       <c r="C800" s="5"/>
       <c r="D800" s="4"/>
@@ -26220,7 +26229,7 @@
       <c r="X800" s="2"/>
       <c r="Y800" s="2"/>
     </row>
-    <row r="801" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="801" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B801" s="5"/>
       <c r="C801" s="5"/>
       <c r="D801" s="4"/>
@@ -26246,7 +26255,7 @@
       <c r="X801" s="2"/>
       <c r="Y801" s="2"/>
     </row>
-    <row r="802" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="802" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B802" s="5"/>
       <c r="C802" s="5"/>
       <c r="D802" s="4"/>
@@ -26272,7 +26281,7 @@
       <c r="X802" s="2"/>
       <c r="Y802" s="2"/>
     </row>
-    <row r="803" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="803" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B803" s="5"/>
       <c r="C803" s="5"/>
       <c r="D803" s="4"/>
@@ -26298,7 +26307,7 @@
       <c r="X803" s="2"/>
       <c r="Y803" s="2"/>
     </row>
-    <row r="804" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="804" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B804" s="5"/>
       <c r="C804" s="5"/>
       <c r="D804" s="4"/>
@@ -26324,7 +26333,7 @@
       <c r="X804" s="2"/>
       <c r="Y804" s="2"/>
     </row>
-    <row r="805" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="805" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B805" s="5"/>
       <c r="C805" s="5"/>
       <c r="D805" s="4"/>
@@ -26350,7 +26359,7 @@
       <c r="X805" s="2"/>
       <c r="Y805" s="2"/>
     </row>
-    <row r="806" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="806" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B806" s="5"/>
       <c r="C806" s="5"/>
       <c r="D806" s="4"/>
@@ -26376,7 +26385,7 @@
       <c r="X806" s="2"/>
       <c r="Y806" s="2"/>
     </row>
-    <row r="807" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="807" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B807" s="5"/>
       <c r="C807" s="5"/>
       <c r="D807" s="4"/>
@@ -26402,7 +26411,7 @@
       <c r="X807" s="2"/>
       <c r="Y807" s="2"/>
     </row>
-    <row r="808" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="808" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B808" s="5"/>
       <c r="C808" s="5"/>
       <c r="D808" s="4"/>
@@ -26428,7 +26437,7 @@
       <c r="X808" s="2"/>
       <c r="Y808" s="2"/>
     </row>
-    <row r="809" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="809" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B809" s="5"/>
       <c r="C809" s="5"/>
       <c r="D809" s="4"/>
@@ -26454,7 +26463,7 @@
       <c r="X809" s="2"/>
       <c r="Y809" s="2"/>
     </row>
-    <row r="810" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="810" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B810" s="5"/>
       <c r="C810" s="5"/>
       <c r="D810" s="4"/>
@@ -26480,7 +26489,7 @@
       <c r="X810" s="2"/>
       <c r="Y810" s="2"/>
     </row>
-    <row r="811" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="811" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B811" s="5"/>
       <c r="C811" s="5"/>
       <c r="D811" s="4"/>
@@ -26506,7 +26515,7 @@
       <c r="X811" s="2"/>
       <c r="Y811" s="2"/>
     </row>
-    <row r="812" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="812" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B812" s="5"/>
       <c r="C812" s="5"/>
       <c r="D812" s="4"/>
@@ -26532,7 +26541,7 @@
       <c r="X812" s="2"/>
       <c r="Y812" s="2"/>
     </row>
-    <row r="813" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="813" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B813" s="5"/>
       <c r="C813" s="5"/>
       <c r="D813" s="4"/>
@@ -26558,7 +26567,7 @@
       <c r="X813" s="2"/>
       <c r="Y813" s="2"/>
     </row>
-    <row r="814" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="814" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B814" s="5"/>
       <c r="C814" s="5"/>
       <c r="D814" s="4"/>
@@ -26584,7 +26593,7 @@
       <c r="X814" s="2"/>
       <c r="Y814" s="2"/>
     </row>
-    <row r="815" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="815" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B815" s="5"/>
       <c r="C815" s="5"/>
       <c r="D815" s="4"/>
@@ -26610,7 +26619,7 @@
       <c r="X815" s="2"/>
       <c r="Y815" s="2"/>
     </row>
-    <row r="816" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="816" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B816" s="5"/>
       <c r="C816" s="5"/>
       <c r="D816" s="4"/>
@@ -26636,7 +26645,7 @@
       <c r="X816" s="2"/>
       <c r="Y816" s="2"/>
     </row>
-    <row r="817" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="817" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B817" s="5"/>
       <c r="C817" s="5"/>
       <c r="D817" s="4"/>
@@ -26662,7 +26671,7 @@
       <c r="X817" s="2"/>
       <c r="Y817" s="2"/>
     </row>
-    <row r="818" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="818" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B818" s="5"/>
       <c r="C818" s="5"/>
       <c r="D818" s="4"/>
@@ -26688,7 +26697,7 @@
       <c r="X818" s="2"/>
       <c r="Y818" s="2"/>
     </row>
-    <row r="819" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="819" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B819" s="5"/>
       <c r="C819" s="5"/>
       <c r="D819" s="4"/>
@@ -26714,7 +26723,7 @@
       <c r="X819" s="2"/>
       <c r="Y819" s="2"/>
     </row>
-    <row r="820" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="820" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B820" s="5"/>
       <c r="C820" s="5"/>
       <c r="D820" s="4"/>
@@ -26740,7 +26749,7 @@
       <c r="X820" s="2"/>
       <c r="Y820" s="2"/>
     </row>
-    <row r="821" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="821" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B821" s="5"/>
       <c r="C821" s="5"/>
       <c r="D821" s="4"/>
@@ -26766,7 +26775,7 @@
       <c r="X821" s="2"/>
       <c r="Y821" s="2"/>
     </row>
-    <row r="822" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="822" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B822" s="5"/>
       <c r="C822" s="5"/>
       <c r="D822" s="4"/>
@@ -26792,7 +26801,7 @@
       <c r="X822" s="2"/>
       <c r="Y822" s="2"/>
     </row>
-    <row r="823" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="823" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B823" s="5"/>
       <c r="C823" s="5"/>
       <c r="D823" s="4"/>
@@ -26818,7 +26827,7 @@
       <c r="X823" s="2"/>
       <c r="Y823" s="2"/>
     </row>
-    <row r="824" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="824" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B824" s="5"/>
       <c r="C824" s="5"/>
       <c r="D824" s="4"/>
@@ -26844,7 +26853,7 @@
       <c r="X824" s="2"/>
       <c r="Y824" s="2"/>
     </row>
-    <row r="825" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="825" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B825" s="5"/>
       <c r="C825" s="5"/>
       <c r="D825" s="4"/>
@@ -26870,7 +26879,7 @@
       <c r="X825" s="2"/>
       <c r="Y825" s="2"/>
     </row>
-    <row r="826" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="826" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B826" s="5"/>
       <c r="C826" s="5"/>
       <c r="D826" s="4"/>
@@ -26896,7 +26905,7 @@
       <c r="X826" s="2"/>
       <c r="Y826" s="2"/>
     </row>
-    <row r="827" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="827" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B827" s="5"/>
       <c r="C827" s="5"/>
       <c r="D827" s="4"/>
@@ -26922,7 +26931,7 @@
       <c r="X827" s="2"/>
       <c r="Y827" s="2"/>
     </row>
-    <row r="828" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="828" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B828" s="5"/>
       <c r="C828" s="5"/>
       <c r="D828" s="4"/>
@@ -26948,7 +26957,7 @@
       <c r="X828" s="2"/>
       <c r="Y828" s="2"/>
     </row>
-    <row r="829" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="829" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B829" s="5"/>
       <c r="C829" s="5"/>
       <c r="D829" s="4"/>
@@ -26974,7 +26983,7 @@
       <c r="X829" s="2"/>
       <c r="Y829" s="2"/>
     </row>
-    <row r="830" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="830" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B830" s="5"/>
       <c r="C830" s="5"/>
       <c r="D830" s="4"/>
@@ -27000,7 +27009,7 @@
       <c r="X830" s="2"/>
       <c r="Y830" s="2"/>
     </row>
-    <row r="831" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="831" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B831" s="5"/>
       <c r="C831" s="5"/>
       <c r="D831" s="4"/>
@@ -27026,7 +27035,7 @@
       <c r="X831" s="2"/>
       <c r="Y831" s="2"/>
     </row>
-    <row r="832" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="832" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B832" s="5"/>
       <c r="C832" s="5"/>
       <c r="D832" s="4"/>
@@ -27052,7 +27061,7 @@
       <c r="X832" s="2"/>
       <c r="Y832" s="2"/>
     </row>
-    <row r="833" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="833" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B833" s="5"/>
       <c r="C833" s="5"/>
       <c r="D833" s="4"/>
@@ -27078,7 +27087,7 @@
       <c r="X833" s="2"/>
       <c r="Y833" s="2"/>
     </row>
-    <row r="834" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="834" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B834" s="5"/>
       <c r="C834" s="5"/>
       <c r="D834" s="4"/>
@@ -27104,7 +27113,7 @@
       <c r="X834" s="2"/>
       <c r="Y834" s="2"/>
     </row>
-    <row r="835" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="835" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B835" s="5"/>
       <c r="C835" s="5"/>
       <c r="D835" s="4"/>
@@ -27130,7 +27139,7 @@
       <c r="X835" s="2"/>
       <c r="Y835" s="2"/>
     </row>
-    <row r="836" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="836" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B836" s="5"/>
       <c r="C836" s="5"/>
       <c r="D836" s="4"/>
@@ -27156,7 +27165,7 @@
       <c r="X836" s="2"/>
       <c r="Y836" s="2"/>
     </row>
-    <row r="837" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="837" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B837" s="5"/>
       <c r="C837" s="5"/>
       <c r="D837" s="4"/>
@@ -27182,7 +27191,7 @@
       <c r="X837" s="2"/>
       <c r="Y837" s="2"/>
     </row>
-    <row r="838" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="838" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B838" s="5"/>
       <c r="C838" s="5"/>
       <c r="D838" s="4"/>
@@ -27208,7 +27217,7 @@
       <c r="X838" s="2"/>
       <c r="Y838" s="2"/>
     </row>
-    <row r="839" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="839" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B839" s="5"/>
       <c r="C839" s="5"/>
       <c r="D839" s="4"/>
@@ -27234,7 +27243,7 @@
       <c r="X839" s="2"/>
       <c r="Y839" s="2"/>
     </row>
-    <row r="840" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="840" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B840" s="5"/>
       <c r="C840" s="5"/>
       <c r="D840" s="4"/>
@@ -27260,7 +27269,7 @@
       <c r="X840" s="2"/>
       <c r="Y840" s="2"/>
     </row>
-    <row r="841" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="841" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B841" s="5"/>
       <c r="C841" s="5"/>
       <c r="D841" s="4"/>
@@ -27286,7 +27295,7 @@
       <c r="X841" s="2"/>
       <c r="Y841" s="2"/>
     </row>
-    <row r="842" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="842" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B842" s="5"/>
       <c r="C842" s="5"/>
       <c r="D842" s="4"/>
@@ -27312,7 +27321,7 @@
       <c r="X842" s="2"/>
       <c r="Y842" s="2"/>
     </row>
-    <row r="843" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="843" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B843" s="5"/>
       <c r="C843" s="5"/>
       <c r="D843" s="4"/>
@@ -27338,7 +27347,7 @@
       <c r="X843" s="2"/>
       <c r="Y843" s="2"/>
     </row>
-    <row r="844" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="844" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B844" s="5"/>
       <c r="C844" s="5"/>
       <c r="D844" s="4"/>
@@ -27364,7 +27373,7 @@
       <c r="X844" s="2"/>
       <c r="Y844" s="2"/>
     </row>
-    <row r="845" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="845" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B845" s="5"/>
       <c r="C845" s="5"/>
       <c r="D845" s="4"/>
@@ -27390,7 +27399,7 @@
       <c r="X845" s="2"/>
       <c r="Y845" s="2"/>
     </row>
-    <row r="846" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="846" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B846" s="5"/>
       <c r="C846" s="5"/>
       <c r="D846" s="4"/>
@@ -27416,7 +27425,7 @@
       <c r="X846" s="2"/>
       <c r="Y846" s="2"/>
     </row>
-    <row r="847" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="847" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B847" s="5"/>
       <c r="C847" s="5"/>
       <c r="D847" s="4"/>
@@ -27442,7 +27451,7 @@
       <c r="X847" s="2"/>
       <c r="Y847" s="2"/>
     </row>
-    <row r="848" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="848" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B848" s="5"/>
       <c r="C848" s="5"/>
       <c r="D848" s="4"/>
@@ -27468,7 +27477,7 @@
       <c r="X848" s="2"/>
       <c r="Y848" s="2"/>
     </row>
-    <row r="849" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="849" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B849" s="5"/>
       <c r="C849" s="5"/>
       <c r="D849" s="4"/>
@@ -27494,7 +27503,7 @@
       <c r="X849" s="2"/>
       <c r="Y849" s="2"/>
     </row>
-    <row r="850" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="850" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B850" s="5"/>
       <c r="C850" s="5"/>
       <c r="D850" s="4"/>
@@ -27520,7 +27529,7 @@
       <c r="X850" s="2"/>
       <c r="Y850" s="2"/>
     </row>
-    <row r="851" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="851" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B851" s="5"/>
       <c r="C851" s="5"/>
       <c r="D851" s="4"/>
@@ -27546,7 +27555,7 @@
       <c r="X851" s="2"/>
       <c r="Y851" s="2"/>
     </row>
-    <row r="852" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="852" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B852" s="5"/>
       <c r="C852" s="5"/>
       <c r="D852" s="4"/>
@@ -27572,7 +27581,7 @@
       <c r="X852" s="2"/>
       <c r="Y852" s="2"/>
     </row>
-    <row r="853" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="853" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B853" s="5"/>
       <c r="C853" s="5"/>
       <c r="D853" s="4"/>
@@ -27598,7 +27607,7 @@
       <c r="X853" s="2"/>
       <c r="Y853" s="2"/>
     </row>
-    <row r="854" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="854" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B854" s="5"/>
       <c r="C854" s="5"/>
       <c r="D854" s="4"/>
@@ -27624,7 +27633,7 @@
       <c r="X854" s="2"/>
       <c r="Y854" s="2"/>
     </row>
-    <row r="855" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="855" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B855" s="5"/>
       <c r="C855" s="5"/>
       <c r="D855" s="4"/>
@@ -27650,7 +27659,7 @@
       <c r="X855" s="2"/>
       <c r="Y855" s="2"/>
     </row>
-    <row r="856" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="856" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B856" s="5"/>
       <c r="C856" s="5"/>
       <c r="D856" s="4"/>
@@ -27676,7 +27685,7 @@
       <c r="X856" s="2"/>
       <c r="Y856" s="2"/>
     </row>
-    <row r="857" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="857" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B857" s="5"/>
       <c r="C857" s="5"/>
       <c r="D857" s="4"/>
@@ -27702,7 +27711,7 @@
       <c r="X857" s="2"/>
       <c r="Y857" s="2"/>
     </row>
-    <row r="858" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="858" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B858" s="5"/>
       <c r="C858" s="5"/>
       <c r="D858" s="4"/>
@@ -27728,7 +27737,7 @@
       <c r="X858" s="2"/>
       <c r="Y858" s="2"/>
     </row>
-    <row r="859" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="859" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B859" s="5"/>
       <c r="C859" s="5"/>
       <c r="D859" s="4"/>
@@ -27754,7 +27763,7 @@
       <c r="X859" s="2"/>
       <c r="Y859" s="2"/>
     </row>
-    <row r="860" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="860" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B860" s="5"/>
       <c r="C860" s="5"/>
       <c r="D860" s="4"/>
@@ -27780,7 +27789,7 @@
       <c r="X860" s="2"/>
       <c r="Y860" s="2"/>
     </row>
-    <row r="861" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="861" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B861" s="5"/>
       <c r="C861" s="5"/>
       <c r="D861" s="4"/>
@@ -27806,7 +27815,7 @@
       <c r="X861" s="2"/>
       <c r="Y861" s="2"/>
     </row>
-    <row r="862" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="862" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B862" s="5"/>
       <c r="C862" s="5"/>
       <c r="D862" s="4"/>
@@ -27832,7 +27841,7 @@
       <c r="X862" s="2"/>
       <c r="Y862" s="2"/>
     </row>
-    <row r="863" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="863" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B863" s="5"/>
       <c r="C863" s="5"/>
       <c r="D863" s="4"/>
@@ -27858,7 +27867,7 @@
       <c r="X863" s="2"/>
       <c r="Y863" s="2"/>
     </row>
-    <row r="864" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="864" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B864" s="5"/>
       <c r="C864" s="5"/>
       <c r="D864" s="4"/>
@@ -27884,7 +27893,7 @@
       <c r="X864" s="2"/>
       <c r="Y864" s="2"/>
     </row>
-    <row r="865" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="865" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B865" s="5"/>
       <c r="C865" s="5"/>
       <c r="D865" s="4"/>
@@ -27910,7 +27919,7 @@
       <c r="X865" s="2"/>
       <c r="Y865" s="2"/>
     </row>
-    <row r="866" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="866" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B866" s="5"/>
       <c r="C866" s="5"/>
       <c r="D866" s="4"/>
@@ -27936,7 +27945,7 @@
       <c r="X866" s="2"/>
       <c r="Y866" s="2"/>
     </row>
-    <row r="867" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="867" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B867" s="5"/>
       <c r="C867" s="5"/>
       <c r="D867" s="4"/>
@@ -27962,7 +27971,7 @@
       <c r="X867" s="2"/>
       <c r="Y867" s="2"/>
     </row>
-    <row r="868" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="868" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B868" s="5"/>
       <c r="C868" s="5"/>
       <c r="D868" s="4"/>
@@ -27988,7 +27997,7 @@
       <c r="X868" s="2"/>
       <c r="Y868" s="2"/>
     </row>
-    <row r="869" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="869" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B869" s="5"/>
       <c r="C869" s="5"/>
       <c r="D869" s="4"/>
@@ -28014,7 +28023,7 @@
       <c r="X869" s="2"/>
       <c r="Y869" s="2"/>
     </row>
-    <row r="870" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="870" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B870" s="5"/>
       <c r="C870" s="5"/>
       <c r="D870" s="4"/>
@@ -28040,7 +28049,7 @@
       <c r="X870" s="2"/>
       <c r="Y870" s="2"/>
     </row>
-    <row r="871" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="871" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B871" s="5"/>
       <c r="C871" s="5"/>
       <c r="D871" s="4"/>
@@ -28066,7 +28075,7 @@
       <c r="X871" s="2"/>
       <c r="Y871" s="2"/>
     </row>
-    <row r="872" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="872" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B872" s="5"/>
       <c r="C872" s="5"/>
       <c r="D872" s="4"/>
@@ -28092,7 +28101,7 @@
       <c r="X872" s="2"/>
       <c r="Y872" s="2"/>
     </row>
-    <row r="873" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="873" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B873" s="5"/>
       <c r="C873" s="5"/>
       <c r="D873" s="4"/>
@@ -28118,7 +28127,7 @@
       <c r="X873" s="2"/>
       <c r="Y873" s="2"/>
     </row>
-    <row r="874" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="874" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B874" s="5"/>
       <c r="C874" s="5"/>
       <c r="D874" s="4"/>
@@ -28144,7 +28153,7 @@
       <c r="X874" s="2"/>
       <c r="Y874" s="2"/>
     </row>
-    <row r="875" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="875" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B875" s="5"/>
       <c r="C875" s="5"/>
       <c r="D875" s="4"/>
@@ -28170,7 +28179,7 @@
       <c r="X875" s="2"/>
       <c r="Y875" s="2"/>
     </row>
-    <row r="876" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="876" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B876" s="5"/>
       <c r="C876" s="5"/>
       <c r="D876" s="4"/>
@@ -28196,7 +28205,7 @@
       <c r="X876" s="2"/>
       <c r="Y876" s="2"/>
     </row>
-    <row r="877" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="877" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B877" s="5"/>
       <c r="C877" s="5"/>
       <c r="D877" s="4"/>
@@ -28222,7 +28231,7 @@
       <c r="X877" s="2"/>
       <c r="Y877" s="2"/>
     </row>
-    <row r="878" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="878" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B878" s="5"/>
       <c r="C878" s="5"/>
       <c r="D878" s="4"/>
@@ -28248,7 +28257,7 @@
       <c r="X878" s="2"/>
       <c r="Y878" s="2"/>
     </row>
-    <row r="879" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="879" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B879" s="5"/>
       <c r="C879" s="5"/>
       <c r="D879" s="4"/>
@@ -28274,7 +28283,7 @@
       <c r="X879" s="2"/>
       <c r="Y879" s="2"/>
     </row>
-    <row r="880" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="880" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B880" s="5"/>
       <c r="C880" s="5"/>
       <c r="D880" s="4"/>
@@ -28300,7 +28309,7 @@
       <c r="X880" s="2"/>
       <c r="Y880" s="2"/>
     </row>
-    <row r="881" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="881" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B881" s="5"/>
       <c r="C881" s="5"/>
       <c r="D881" s="4"/>
@@ -28326,7 +28335,7 @@
       <c r="X881" s="2"/>
       <c r="Y881" s="2"/>
     </row>
-    <row r="882" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="882" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B882" s="5"/>
       <c r="C882" s="5"/>
       <c r="D882" s="4"/>
@@ -28352,7 +28361,7 @@
       <c r="X882" s="2"/>
       <c r="Y882" s="2"/>
     </row>
-    <row r="883" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="883" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B883" s="5"/>
       <c r="C883" s="5"/>
       <c r="D883" s="4"/>
@@ -28378,7 +28387,7 @@
       <c r="X883" s="2"/>
       <c r="Y883" s="2"/>
     </row>
-    <row r="884" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="884" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B884" s="5"/>
       <c r="C884" s="5"/>
       <c r="D884" s="4"/>
@@ -28404,7 +28413,7 @@
       <c r="X884" s="2"/>
       <c r="Y884" s="2"/>
     </row>
-    <row r="885" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="885" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B885" s="5"/>
       <c r="C885" s="5"/>
       <c r="D885" s="4"/>
@@ -28430,7 +28439,7 @@
       <c r="X885" s="2"/>
       <c r="Y885" s="2"/>
     </row>
-    <row r="886" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="886" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B886" s="5"/>
       <c r="C886" s="5"/>
       <c r="D886" s="4"/>
@@ -28456,7 +28465,7 @@
       <c r="X886" s="2"/>
       <c r="Y886" s="2"/>
     </row>
-    <row r="887" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="887" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B887" s="5"/>
       <c r="C887" s="5"/>
       <c r="D887" s="4"/>
@@ -28482,7 +28491,7 @@
       <c r="X887" s="2"/>
       <c r="Y887" s="2"/>
     </row>
-    <row r="888" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="888" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B888" s="5"/>
       <c r="C888" s="5"/>
       <c r="D888" s="4"/>
@@ -28508,7 +28517,7 @@
       <c r="X888" s="2"/>
       <c r="Y888" s="2"/>
     </row>
-    <row r="889" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="889" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B889" s="5"/>
       <c r="C889" s="5"/>
       <c r="D889" s="4"/>
@@ -28534,7 +28543,7 @@
       <c r="X889" s="2"/>
       <c r="Y889" s="2"/>
     </row>
-    <row r="890" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="890" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B890" s="5"/>
       <c r="C890" s="5"/>
       <c r="D890" s="4"/>
@@ -28560,7 +28569,7 @@
       <c r="X890" s="2"/>
       <c r="Y890" s="2"/>
     </row>
-    <row r="891" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="891" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B891" s="5"/>
       <c r="C891" s="5"/>
       <c r="D891" s="4"/>
@@ -28586,7 +28595,7 @@
       <c r="X891" s="2"/>
       <c r="Y891" s="2"/>
     </row>
-    <row r="892" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="892" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B892" s="5"/>
       <c r="C892" s="5"/>
       <c r="D892" s="4"/>
@@ -28612,7 +28621,7 @@
       <c r="X892" s="2"/>
       <c r="Y892" s="2"/>
     </row>
-    <row r="893" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="893" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B893" s="5"/>
       <c r="C893" s="5"/>
       <c r="D893" s="4"/>
@@ -28638,7 +28647,7 @@
       <c r="X893" s="2"/>
       <c r="Y893" s="2"/>
     </row>
-    <row r="894" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="894" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B894" s="5"/>
       <c r="C894" s="5"/>
       <c r="D894" s="4"/>
@@ -28664,7 +28673,7 @@
       <c r="X894" s="2"/>
       <c r="Y894" s="2"/>
     </row>
-    <row r="895" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="895" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B895" s="5"/>
       <c r="C895" s="5"/>
       <c r="D895" s="4"/>
@@ -28690,7 +28699,7 @@
       <c r="X895" s="2"/>
       <c r="Y895" s="2"/>
     </row>
-    <row r="896" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="896" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B896" s="5"/>
       <c r="C896" s="5"/>
       <c r="D896" s="4"/>
@@ -28716,7 +28725,7 @@
       <c r="X896" s="2"/>
       <c r="Y896" s="2"/>
     </row>
-    <row r="897" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="897" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B897" s="5"/>
       <c r="C897" s="5"/>
       <c r="D897" s="4"/>
@@ -28742,7 +28751,7 @@
       <c r="X897" s="2"/>
       <c r="Y897" s="2"/>
     </row>
-    <row r="898" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="898" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B898" s="5"/>
       <c r="C898" s="5"/>
       <c r="D898" s="4"/>
@@ -28768,7 +28777,7 @@
       <c r="X898" s="2"/>
       <c r="Y898" s="2"/>
     </row>
-    <row r="899" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="899" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B899" s="5"/>
       <c r="C899" s="5"/>
       <c r="D899" s="4"/>
@@ -28794,7 +28803,7 @@
       <c r="X899" s="2"/>
       <c r="Y899" s="2"/>
     </row>
-    <row r="900" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="900" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B900" s="5"/>
       <c r="C900" s="5"/>
       <c r="D900" s="4"/>
@@ -28820,7 +28829,7 @@
       <c r="X900" s="2"/>
       <c r="Y900" s="2"/>
     </row>
-    <row r="901" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="901" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B901" s="5"/>
       <c r="C901" s="5"/>
       <c r="D901" s="4"/>
@@ -28846,7 +28855,7 @@
       <c r="X901" s="2"/>
       <c r="Y901" s="2"/>
     </row>
-    <row r="902" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="902" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B902" s="5"/>
       <c r="C902" s="5"/>
       <c r="D902" s="4"/>
@@ -28872,7 +28881,7 @@
       <c r="X902" s="2"/>
       <c r="Y902" s="2"/>
     </row>
-    <row r="903" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="903" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B903" s="5"/>
       <c r="C903" s="5"/>
       <c r="D903" s="4"/>
@@ -28898,7 +28907,7 @@
       <c r="X903" s="2"/>
       <c r="Y903" s="2"/>
     </row>
-    <row r="904" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="904" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B904" s="5"/>
       <c r="C904" s="5"/>
       <c r="D904" s="4"/>
@@ -28924,7 +28933,7 @@
       <c r="X904" s="2"/>
       <c r="Y904" s="2"/>
     </row>
-    <row r="905" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="905" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B905" s="5"/>
       <c r="C905" s="5"/>
       <c r="D905" s="4"/>
@@ -28950,7 +28959,7 @@
       <c r="X905" s="2"/>
       <c r="Y905" s="2"/>
     </row>
-    <row r="906" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="906" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B906" s="5"/>
       <c r="C906" s="5"/>
       <c r="D906" s="4"/>
@@ -28976,7 +28985,7 @@
       <c r="X906" s="2"/>
       <c r="Y906" s="2"/>
     </row>
-    <row r="907" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="907" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B907" s="5"/>
       <c r="C907" s="5"/>
       <c r="D907" s="4"/>
@@ -29002,7 +29011,7 @@
       <c r="X907" s="2"/>
       <c r="Y907" s="2"/>
     </row>
-    <row r="908" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="908" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B908" s="5"/>
       <c r="C908" s="5"/>
       <c r="D908" s="4"/>
@@ -29028,7 +29037,7 @@
       <c r="X908" s="2"/>
       <c r="Y908" s="2"/>
     </row>
-    <row r="909" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="909" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B909" s="5"/>
       <c r="C909" s="5"/>
       <c r="D909" s="4"/>
@@ -29054,7 +29063,7 @@
       <c r="X909" s="2"/>
       <c r="Y909" s="2"/>
     </row>
-    <row r="910" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="910" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B910" s="5"/>
       <c r="C910" s="5"/>
       <c r="D910" s="4"/>
@@ -29080,7 +29089,7 @@
       <c r="X910" s="2"/>
       <c r="Y910" s="2"/>
     </row>
-    <row r="911" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="911" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B911" s="5"/>
       <c r="C911" s="5"/>
       <c r="D911" s="4"/>
@@ -29106,7 +29115,7 @@
       <c r="X911" s="2"/>
       <c r="Y911" s="2"/>
     </row>
-    <row r="912" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="912" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B912" s="5"/>
       <c r="C912" s="5"/>
       <c r="D912" s="4"/>
@@ -29132,7 +29141,7 @@
       <c r="X912" s="2"/>
       <c r="Y912" s="2"/>
     </row>
-    <row r="913" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="913" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B913" s="5"/>
       <c r="C913" s="5"/>
       <c r="D913" s="4"/>
@@ -29158,7 +29167,7 @@
       <c r="X913" s="2"/>
       <c r="Y913" s="2"/>
     </row>
-    <row r="914" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="914" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B914" s="5"/>
       <c r="C914" s="5"/>
       <c r="D914" s="4"/>
@@ -29184,7 +29193,7 @@
       <c r="X914" s="2"/>
       <c r="Y914" s="2"/>
     </row>
-    <row r="915" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="915" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B915" s="5"/>
       <c r="C915" s="5"/>
       <c r="D915" s="4"/>
@@ -29210,7 +29219,7 @@
       <c r="X915" s="2"/>
       <c r="Y915" s="2"/>
     </row>
-    <row r="916" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="916" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B916" s="5"/>
       <c r="C916" s="5"/>
       <c r="D916" s="4"/>
@@ -29236,7 +29245,7 @@
       <c r="X916" s="2"/>
       <c r="Y916" s="2"/>
     </row>
-    <row r="917" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="917" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B917" s="5"/>
       <c r="C917" s="5"/>
       <c r="D917" s="4"/>
@@ -29262,7 +29271,7 @@
       <c r="X917" s="2"/>
       <c r="Y917" s="2"/>
     </row>
-    <row r="918" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="918" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B918" s="5"/>
       <c r="C918" s="5"/>
       <c r="D918" s="4"/>
@@ -29288,7 +29297,7 @@
       <c r="X918" s="2"/>
       <c r="Y918" s="2"/>
     </row>
-    <row r="919" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="919" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B919" s="5"/>
       <c r="C919" s="5"/>
       <c r="D919" s="4"/>
@@ -29314,7 +29323,7 @@
       <c r="X919" s="2"/>
       <c r="Y919" s="2"/>
     </row>
-    <row r="920" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="920" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B920" s="5"/>
       <c r="C920" s="5"/>
       <c r="D920" s="4"/>
@@ -29340,7 +29349,7 @@
       <c r="X920" s="2"/>
       <c r="Y920" s="2"/>
     </row>
-    <row r="921" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="921" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B921" s="5"/>
       <c r="C921" s="5"/>
       <c r="D921" s="4"/>
@@ -29366,7 +29375,7 @@
       <c r="X921" s="2"/>
       <c r="Y921" s="2"/>
     </row>
-    <row r="922" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="922" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B922" s="5"/>
       <c r="C922" s="5"/>
       <c r="D922" s="4"/>
@@ -29392,7 +29401,7 @@
       <c r="X922" s="2"/>
       <c r="Y922" s="2"/>
     </row>
-    <row r="923" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="923" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B923" s="5"/>
       <c r="C923" s="5"/>
       <c r="D923" s="4"/>
@@ -29418,7 +29427,7 @@
       <c r="X923" s="2"/>
       <c r="Y923" s="2"/>
     </row>
-    <row r="924" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="924" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B924" s="5"/>
       <c r="C924" s="5"/>
       <c r="D924" s="4"/>
@@ -29444,7 +29453,7 @@
       <c r="X924" s="2"/>
       <c r="Y924" s="2"/>
     </row>
-    <row r="925" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="925" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B925" s="5"/>
       <c r="C925" s="5"/>
       <c r="D925" s="4"/>
@@ -29470,7 +29479,7 @@
       <c r="X925" s="2"/>
       <c r="Y925" s="2"/>
     </row>
-    <row r="926" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="926" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B926" s="5"/>
       <c r="C926" s="5"/>
       <c r="D926" s="4"/>
@@ -29496,7 +29505,7 @@
       <c r="X926" s="2"/>
       <c r="Y926" s="2"/>
     </row>
-    <row r="927" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="927" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B927" s="5"/>
       <c r="C927" s="5"/>
       <c r="D927" s="4"/>
@@ -29522,7 +29531,7 @@
       <c r="X927" s="2"/>
       <c r="Y927" s="2"/>
     </row>
-    <row r="928" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="928" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B928" s="5"/>
       <c r="C928" s="5"/>
       <c r="D928" s="4"/>
@@ -29548,7 +29557,7 @@
       <c r="X928" s="2"/>
       <c r="Y928" s="2"/>
     </row>
-    <row r="929" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="929" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B929" s="5"/>
       <c r="C929" s="5"/>
       <c r="D929" s="4"/>
@@ -29574,7 +29583,7 @@
       <c r="X929" s="2"/>
       <c r="Y929" s="2"/>
     </row>
-    <row r="930" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="930" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B930" s="5"/>
       <c r="C930" s="5"/>
       <c r="D930" s="4"/>
@@ -29600,7 +29609,7 @@
       <c r="X930" s="2"/>
       <c r="Y930" s="2"/>
     </row>
-    <row r="931" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="931" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B931" s="5"/>
       <c r="C931" s="5"/>
       <c r="D931" s="4"/>
@@ -29626,7 +29635,7 @@
       <c r="X931" s="2"/>
       <c r="Y931" s="2"/>
     </row>
-    <row r="932" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="932" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B932" s="5"/>
       <c r="C932" s="5"/>
       <c r="D932" s="4"/>
@@ -29652,7 +29661,7 @@
       <c r="X932" s="2"/>
       <c r="Y932" s="2"/>
     </row>
-    <row r="933" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="933" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B933" s="5"/>
       <c r="C933" s="5"/>
       <c r="D933" s="4"/>
@@ -29678,7 +29687,7 @@
       <c r="X933" s="2"/>
       <c r="Y933" s="2"/>
     </row>
-    <row r="934" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="934" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B934" s="5"/>
       <c r="C934" s="5"/>
       <c r="D934" s="4"/>
@@ -29704,7 +29713,7 @@
       <c r="X934" s="2"/>
       <c r="Y934" s="2"/>
     </row>
-    <row r="935" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="935" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B935" s="5"/>
       <c r="C935" s="5"/>
       <c r="D935" s="4"/>
@@ -29730,7 +29739,7 @@
       <c r="X935" s="2"/>
       <c r="Y935" s="2"/>
     </row>
-    <row r="936" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="936" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B936" s="5"/>
       <c r="C936" s="5"/>
       <c r="D936" s="4"/>
@@ -29756,7 +29765,7 @@
       <c r="X936" s="2"/>
       <c r="Y936" s="2"/>
     </row>
-    <row r="937" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="937" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B937" s="5"/>
       <c r="C937" s="5"/>
       <c r="D937" s="4"/>
@@ -29782,7 +29791,7 @@
       <c r="X937" s="2"/>
       <c r="Y937" s="2"/>
     </row>
-    <row r="938" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="938" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B938" s="5"/>
       <c r="C938" s="5"/>
       <c r="D938" s="4"/>
@@ -29808,7 +29817,7 @@
       <c r="X938" s="2"/>
       <c r="Y938" s="2"/>
     </row>
-    <row r="939" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="939" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B939" s="5"/>
       <c r="C939" s="5"/>
       <c r="D939" s="4"/>
@@ -29834,7 +29843,7 @@
       <c r="X939" s="2"/>
       <c r="Y939" s="2"/>
     </row>
-    <row r="940" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="940" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B940" s="5"/>
       <c r="C940" s="5"/>
       <c r="D940" s="4"/>
@@ -29860,7 +29869,7 @@
       <c r="X940" s="2"/>
       <c r="Y940" s="2"/>
     </row>
-    <row r="941" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="941" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B941" s="5"/>
       <c r="C941" s="5"/>
       <c r="D941" s="4"/>
@@ -29886,7 +29895,7 @@
       <c r="X941" s="2"/>
       <c r="Y941" s="2"/>
     </row>
-    <row r="942" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="942" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B942" s="5"/>
       <c r="C942" s="5"/>
       <c r="D942" s="4"/>
@@ -29912,7 +29921,7 @@
       <c r="X942" s="2"/>
       <c r="Y942" s="2"/>
     </row>
-    <row r="943" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="943" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B943" s="5"/>
       <c r="C943" s="5"/>
       <c r="D943" s="4"/>
@@ -29938,7 +29947,7 @@
       <c r="X943" s="2"/>
       <c r="Y943" s="2"/>
     </row>
-    <row r="944" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="944" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B944" s="5"/>
       <c r="C944" s="5"/>
       <c r="D944" s="4"/>
@@ -29964,7 +29973,7 @@
       <c r="X944" s="2"/>
       <c r="Y944" s="2"/>
     </row>
-    <row r="945" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="945" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B945" s="5"/>
       <c r="C945" s="5"/>
       <c r="D945" s="4"/>
@@ -29990,7 +29999,7 @@
       <c r="X945" s="2"/>
       <c r="Y945" s="2"/>
     </row>
-    <row r="946" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="946" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B946" s="5"/>
       <c r="C946" s="5"/>
       <c r="D946" s="4"/>
@@ -30016,7 +30025,7 @@
       <c r="X946" s="2"/>
       <c r="Y946" s="2"/>
     </row>
-    <row r="947" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="947" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B947" s="5"/>
       <c r="C947" s="5"/>
       <c r="D947" s="4"/>
@@ -30042,7 +30051,7 @@
       <c r="X947" s="2"/>
       <c r="Y947" s="2"/>
     </row>
-    <row r="948" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="948" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B948" s="5"/>
       <c r="C948" s="5"/>
       <c r="D948" s="4"/>
@@ -30068,7 +30077,7 @@
       <c r="X948" s="2"/>
       <c r="Y948" s="2"/>
     </row>
-    <row r="949" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="949" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B949" s="5"/>
       <c r="C949" s="5"/>
       <c r="D949" s="4"/>
@@ -30094,7 +30103,7 @@
       <c r="X949" s="2"/>
       <c r="Y949" s="2"/>
     </row>
-    <row r="950" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="950" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B950" s="5"/>
       <c r="C950" s="5"/>
       <c r="D950" s="4"/>
@@ -30120,7 +30129,7 @@
       <c r="X950" s="2"/>
       <c r="Y950" s="2"/>
     </row>
-    <row r="951" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="951" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B951" s="5"/>
       <c r="C951" s="5"/>
       <c r="D951" s="4"/>
@@ -30146,7 +30155,7 @@
       <c r="X951" s="2"/>
       <c r="Y951" s="2"/>
     </row>
-    <row r="952" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="952" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B952" s="5"/>
       <c r="C952" s="5"/>
       <c r="D952" s="4"/>
@@ -30172,7 +30181,7 @@
       <c r="X952" s="2"/>
       <c r="Y952" s="2"/>
     </row>
-    <row r="953" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="953" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B953" s="5"/>
       <c r="C953" s="5"/>
       <c r="D953" s="4"/>
@@ -30198,7 +30207,7 @@
       <c r="X953" s="2"/>
       <c r="Y953" s="2"/>
     </row>
-    <row r="954" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="954" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B954" s="5"/>
       <c r="C954" s="5"/>
       <c r="D954" s="4"/>
@@ -30224,7 +30233,7 @@
       <c r="X954" s="2"/>
       <c r="Y954" s="2"/>
     </row>
-    <row r="955" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="955" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B955" s="5"/>
       <c r="C955" s="5"/>
       <c r="D955" s="4"/>
@@ -30250,7 +30259,7 @@
       <c r="X955" s="2"/>
       <c r="Y955" s="2"/>
     </row>
-    <row r="956" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="956" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B956" s="5"/>
       <c r="C956" s="5"/>
       <c r="D956" s="4"/>
@@ -30276,7 +30285,7 @@
       <c r="X956" s="2"/>
       <c r="Y956" s="2"/>
     </row>
-    <row r="957" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="957" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B957" s="5"/>
       <c r="C957" s="5"/>
       <c r="D957" s="4"/>
@@ -30302,7 +30311,7 @@
       <c r="X957" s="2"/>
       <c r="Y957" s="2"/>
     </row>
-    <row r="958" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="958" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B958" s="5"/>
       <c r="C958" s="5"/>
       <c r="D958" s="4"/>
@@ -30328,7 +30337,7 @@
       <c r="X958" s="2"/>
       <c r="Y958" s="2"/>
     </row>
-    <row r="959" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="959" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B959" s="5"/>
       <c r="C959" s="5"/>
       <c r="D959" s="4"/>
@@ -30354,7 +30363,7 @@
       <c r="X959" s="2"/>
       <c r="Y959" s="2"/>
     </row>
-    <row r="960" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="960" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B960" s="5"/>
       <c r="C960" s="5"/>
       <c r="D960" s="4"/>
@@ -30380,7 +30389,7 @@
       <c r="X960" s="2"/>
       <c r="Y960" s="2"/>
     </row>
-    <row r="961" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="961" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B961" s="5"/>
       <c r="C961" s="5"/>
       <c r="D961" s="4"/>
@@ -30406,7 +30415,7 @@
       <c r="X961" s="2"/>
       <c r="Y961" s="2"/>
     </row>
-    <row r="962" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="962" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B962" s="5"/>
       <c r="C962" s="5"/>
       <c r="D962" s="4"/>
@@ -30432,7 +30441,7 @@
       <c r="X962" s="2"/>
       <c r="Y962" s="2"/>
     </row>
-    <row r="963" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="963" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B963" s="5"/>
       <c r="C963" s="5"/>
       <c r="D963" s="4"/>
@@ -30458,7 +30467,7 @@
       <c r="X963" s="2"/>
       <c r="Y963" s="2"/>
     </row>
-    <row r="964" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="964" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B964" s="5"/>
       <c r="C964" s="5"/>
       <c r="D964" s="4"/>
@@ -30484,7 +30493,7 @@
       <c r="X964" s="2"/>
       <c r="Y964" s="2"/>
     </row>
-    <row r="965" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="965" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B965" s="5"/>
       <c r="C965" s="5"/>
       <c r="D965" s="4"/>
@@ -30510,7 +30519,7 @@
       <c r="X965" s="2"/>
       <c r="Y965" s="2"/>
     </row>
-    <row r="966" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="966" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B966" s="5"/>
       <c r="C966" s="5"/>
       <c r="D966" s="4"/>
@@ -30536,7 +30545,7 @@
       <c r="X966" s="2"/>
       <c r="Y966" s="2"/>
     </row>
-    <row r="967" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="967" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B967" s="5"/>
       <c r="C967" s="5"/>
       <c r="D967" s="4"/>
@@ -30562,7 +30571,7 @@
       <c r="X967" s="2"/>
       <c r="Y967" s="2"/>
     </row>
-    <row r="968" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="968" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B968" s="5"/>
       <c r="C968" s="5"/>
       <c r="D968" s="4"/>
@@ -30588,7 +30597,7 @@
       <c r="X968" s="2"/>
       <c r="Y968" s="2"/>
     </row>
-    <row r="969" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="969" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B969" s="5"/>
       <c r="C969" s="5"/>
       <c r="D969" s="4"/>
@@ -30614,7 +30623,7 @@
       <c r="X969" s="2"/>
       <c r="Y969" s="2"/>
     </row>
-    <row r="970" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="970" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B970" s="5"/>
       <c r="C970" s="5"/>
       <c r="D970" s="4"/>
@@ -30640,7 +30649,7 @@
       <c r="X970" s="2"/>
       <c r="Y970" s="2"/>
     </row>
-    <row r="971" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="971" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B971" s="5"/>
       <c r="C971" s="5"/>
       <c r="D971" s="4"/>
@@ -30666,7 +30675,7 @@
       <c r="X971" s="2"/>
       <c r="Y971" s="2"/>
     </row>
-    <row r="972" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="972" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B972" s="5"/>
       <c r="C972" s="5"/>
       <c r="D972" s="4"/>
@@ -30692,7 +30701,7 @@
       <c r="X972" s="2"/>
       <c r="Y972" s="2"/>
     </row>
-    <row r="973" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="973" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B973" s="5"/>
       <c r="C973" s="5"/>
       <c r="D973" s="4"/>
@@ -30718,7 +30727,7 @@
       <c r="X973" s="2"/>
       <c r="Y973" s="2"/>
     </row>
-    <row r="974" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="974" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B974" s="5"/>
       <c r="C974" s="5"/>
       <c r="D974" s="4"/>
@@ -30744,7 +30753,7 @@
       <c r="X974" s="2"/>
       <c r="Y974" s="2"/>
     </row>
-    <row r="975" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="975" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B975" s="5"/>
       <c r="C975" s="5"/>
       <c r="D975" s="4"/>
@@ -30770,7 +30779,7 @@
       <c r="X975" s="2"/>
       <c r="Y975" s="2"/>
     </row>
-    <row r="976" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="976" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B976" s="5"/>
       <c r="C976" s="5"/>
       <c r="D976" s="4"/>
@@ -30796,7 +30805,7 @@
       <c r="X976" s="2"/>
       <c r="Y976" s="2"/>
     </row>
-    <row r="977" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="977" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B977" s="5"/>
       <c r="C977" s="5"/>
       <c r="D977" s="4"/>
@@ -30822,7 +30831,7 @@
       <c r="X977" s="2"/>
       <c r="Y977" s="2"/>
     </row>
-    <row r="978" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="978" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B978" s="5"/>
       <c r="C978" s="5"/>
       <c r="D978" s="4"/>
@@ -30848,7 +30857,7 @@
       <c r="X978" s="2"/>
       <c r="Y978" s="2"/>
     </row>
-    <row r="979" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="979" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B979" s="5"/>
       <c r="C979" s="5"/>
       <c r="D979" s="4"/>
@@ -30874,7 +30883,7 @@
       <c r="X979" s="2"/>
       <c r="Y979" s="2"/>
     </row>
-    <row r="980" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="980" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B980" s="5"/>
       <c r="C980" s="5"/>
       <c r="D980" s="4"/>
@@ -30900,7 +30909,7 @@
       <c r="X980" s="2"/>
       <c r="Y980" s="2"/>
     </row>
-    <row r="981" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="981" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B981" s="5"/>
       <c r="C981" s="5"/>
       <c r="D981" s="4"/>
@@ -30926,7 +30935,7 @@
       <c r="X981" s="2"/>
       <c r="Y981" s="2"/>
     </row>
-    <row r="982" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="982" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B982" s="5"/>
       <c r="C982" s="5"/>
       <c r="D982" s="4"/>
@@ -30952,7 +30961,7 @@
       <c r="X982" s="2"/>
       <c r="Y982" s="2"/>
     </row>
-    <row r="983" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="983" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B983" s="5"/>
       <c r="C983" s="5"/>
       <c r="D983" s="4"/>
@@ -30978,7 +30987,7 @@
       <c r="X983" s="2"/>
       <c r="Y983" s="2"/>
     </row>
-    <row r="984" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="984" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B984" s="5"/>
       <c r="C984" s="5"/>
       <c r="D984" s="4"/>
@@ -31004,7 +31013,7 @@
       <c r="X984" s="2"/>
       <c r="Y984" s="2"/>
     </row>
-    <row r="985" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="985" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B985" s="5"/>
       <c r="C985" s="5"/>
       <c r="D985" s="4"/>
@@ -31030,7 +31039,7 @@
       <c r="X985" s="2"/>
       <c r="Y985" s="2"/>
     </row>
-    <row r="986" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="986" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B986" s="5"/>
       <c r="C986" s="5"/>
       <c r="D986" s="4"/>
@@ -31056,7 +31065,7 @@
       <c r="X986" s="2"/>
       <c r="Y986" s="2"/>
     </row>
-    <row r="987" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="987" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B987" s="5"/>
       <c r="C987" s="5"/>
       <c r="D987" s="4"/>
@@ -31082,7 +31091,7 @@
       <c r="X987" s="2"/>
       <c r="Y987" s="2"/>
     </row>
-    <row r="988" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="988" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B988" s="5"/>
       <c r="C988" s="5"/>
       <c r="D988" s="4"/>
@@ -31108,7 +31117,7 @@
       <c r="X988" s="2"/>
       <c r="Y988" s="2"/>
     </row>
-    <row r="989" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="989" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B989" s="5"/>
       <c r="C989" s="5"/>
       <c r="D989" s="4"/>
@@ -31134,7 +31143,7 @@
       <c r="X989" s="2"/>
       <c r="Y989" s="2"/>
     </row>
-    <row r="990" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="990" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B990" s="5"/>
       <c r="C990" s="5"/>
       <c r="D990" s="4"/>
@@ -31160,7 +31169,7 @@
       <c r="X990" s="2"/>
       <c r="Y990" s="2"/>
     </row>
-    <row r="991" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="991" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B991" s="5"/>
       <c r="C991" s="5"/>
       <c r="D991" s="4"/>
@@ -31186,7 +31195,7 @@
       <c r="X991" s="2"/>
       <c r="Y991" s="2"/>
     </row>
-    <row r="992" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="992" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B992" s="5"/>
       <c r="C992" s="5"/>
       <c r="D992" s="4"/>
@@ -31212,7 +31221,7 @@
       <c r="X992" s="2"/>
       <c r="Y992" s="2"/>
     </row>
-    <row r="993" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="993" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B993" s="5"/>
       <c r="C993" s="5"/>
       <c r="D993" s="4"/>
@@ -31238,7 +31247,7 @@
       <c r="X993" s="2"/>
       <c r="Y993" s="2"/>
     </row>
-    <row r="994" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="994" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B994" s="5"/>
       <c r="C994" s="5"/>
       <c r="D994" s="4"/>
@@ -31264,7 +31273,7 @@
       <c r="X994" s="2"/>
       <c r="Y994" s="2"/>
     </row>
-    <row r="995" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="995" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B995" s="5"/>
       <c r="C995" s="5"/>
       <c r="D995" s="4"/>
@@ -31290,7 +31299,7 @@
       <c r="X995" s="2"/>
       <c r="Y995" s="2"/>
     </row>
-    <row r="996" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="996" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B996" s="5"/>
       <c r="C996" s="5"/>
       <c r="D996" s="4"/>
@@ -31316,7 +31325,7 @@
       <c r="X996" s="2"/>
       <c r="Y996" s="2"/>
     </row>
-    <row r="997" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="997" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B997" s="5"/>
       <c r="C997" s="5"/>
       <c r="D997" s="4"/>
@@ -31342,7 +31351,7 @@
       <c r="X997" s="2"/>
       <c r="Y997" s="2"/>
     </row>
-    <row r="998" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="998" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B998" s="5"/>
       <c r="C998" s="5"/>
       <c r="D998" s="4"/>
@@ -31368,7 +31377,7 @@
       <c r="X998" s="2"/>
       <c r="Y998" s="2"/>
     </row>
-    <row r="999" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="999" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B999" s="5"/>
       <c r="C999" s="5"/>
       <c r="D999" s="4"/>
@@ -31398,7 +31407,7 @@
   <customSheetViews>
     <customSheetView guid="{6EC1DD54-015D-42A8-B0D3-45AB00E90794}" filter="1" showAutoFilter="1">
       <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-      <autoFilter ref="A1:Z192"/>
+      <autoFilter ref="A1:Z192" xr:uid="{A9ACEBDB-BA97-42FF-A890-0215BD6A20D9}"/>
       <extLst>
         <ext uri="GoogleSheetsCustomDataVersion1">
           <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" filterViewId="688025931"/>
